--- a/research/traditional_assets/database/data/netherlands/netherlands_recreation.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtam_bfit" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,34 +590,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.172</v>
+        <v>0.212</v>
+      </c>
+      <c r="E2">
+        <v>0.09669999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.1149664929262844</v>
+        <v>0.2175141242937853</v>
       </c>
       <c r="H2">
-        <v>-0.1149664929262844</v>
+        <v>0.2175141242937853</v>
       </c>
       <c r="I2">
-        <v>-0.09445031657344471</v>
+        <v>0.06368276916500878</v>
       </c>
       <c r="J2">
-        <v>-0.09445031657344471</v>
+        <v>0.0435931533253256</v>
       </c>
       <c r="K2">
-        <v>-54.8</v>
+        <v>19.9</v>
       </c>
       <c r="L2">
-        <v>-0.08160833953834698</v>
+        <v>0.01938437560880577</v>
       </c>
       <c r="M2">
-        <v>1.58</v>
+        <v>0.495</v>
       </c>
       <c r="N2">
-        <v>0.0009150402501882203</v>
+        <v>0.0002409579905563939</v>
       </c>
       <c r="O2">
-        <v>-0.02883211678832117</v>
+        <v>0.02487437185929648</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,82 +629,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1.58</v>
+        <v>0.495</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>42.5</v>
+        <v>48.4</v>
       </c>
       <c r="V2">
-        <v>0.02461342445126542</v>
+        <v>0.02356033685440296</v>
       </c>
       <c r="W2">
-        <v>-0.1062221360728823</v>
+        <v>0.05002513826043237</v>
       </c>
       <c r="X2">
-        <v>0.1546031226124975</v>
+        <v>0.1214310479426295</v>
       </c>
       <c r="Y2">
-        <v>-0.2608252586853798</v>
+        <v>-0.07140590968219712</v>
       </c>
       <c r="Z2">
-        <v>0.2831640397221604</v>
+        <v>0.4061534107717624</v>
       </c>
       <c r="AA2">
-        <v>-0.02674493319397352</v>
+        <v>0.01770550790937739</v>
       </c>
       <c r="AB2">
-        <v>0.08987868958236667</v>
+        <v>0.07332927201895137</v>
       </c>
       <c r="AC2">
-        <v>-0.1166236227763402</v>
+        <v>-0.05562376410957398</v>
       </c>
       <c r="AD2">
-        <v>2157.5</v>
+        <v>2548.5</v>
       </c>
       <c r="AE2">
-        <v>120.1169378953406</v>
+        <v>227.6163458760099</v>
       </c>
       <c r="AF2">
-        <v>2277.61693789534</v>
+        <v>2776.11634587601</v>
       </c>
       <c r="AG2">
-        <v>2235.11693789534</v>
+        <v>2727.71634587601</v>
       </c>
       <c r="AH2">
-        <v>0.5687903762913558</v>
+        <v>0.5747157485184753</v>
       </c>
       <c r="AI2">
-        <v>0.8513128946873844</v>
+        <v>0.8641832337330411</v>
       </c>
       <c r="AJ2">
-        <v>0.5641646176319077</v>
+        <v>0.5704113387710146</v>
       </c>
       <c r="AK2">
-        <v>0.8489128182228235</v>
+        <v>0.8621056428584274</v>
       </c>
       <c r="AL2">
-        <v>59.5</v>
+        <v>75.3</v>
       </c>
       <c r="AM2">
-        <v>59.499</v>
+        <v>75.298</v>
       </c>
       <c r="AN2">
-        <v>19.36714542190305</v>
+        <v>8.444333996023856</v>
       </c>
       <c r="AO2">
-        <v>-0.8</v>
+        <v>1.318725099601594</v>
       </c>
       <c r="AP2">
-        <v>20.06388633658295</v>
+        <v>9.038158866388368</v>
       </c>
       <c r="AQ2">
-        <v>-0.8000134456041278</v>
+        <v>1.318760126430981</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +724,37 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.172</v>
+        <v>0.212</v>
+      </c>
+      <c r="E3">
+        <v>0.09669999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.1149664929262844</v>
+        <v>0.2175141242937853</v>
       </c>
       <c r="H3">
-        <v>-0.1149664929262844</v>
+        <v>0.2175141242937853</v>
       </c>
       <c r="I3">
-        <v>-0.09445031657344471</v>
+        <v>0.06368276916500878</v>
       </c>
       <c r="J3">
-        <v>-0.09445031657344471</v>
+        <v>0.0435931533253256</v>
       </c>
       <c r="K3">
-        <v>-54.8</v>
+        <v>19.9</v>
       </c>
       <c r="L3">
-        <v>-0.08160833953834698</v>
+        <v>0.01938437560880577</v>
       </c>
       <c r="M3">
-        <v>1.58</v>
+        <v>0.495</v>
       </c>
       <c r="N3">
-        <v>0.0009150402501882203</v>
+        <v>0.0002409579905563939</v>
       </c>
       <c r="O3">
-        <v>-0.02883211678832117</v>
+        <v>0.02487437185929648</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,82 +763,8854 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>1.58</v>
+        <v>0.495</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>42.5</v>
+        <v>48.4</v>
       </c>
       <c r="V3">
-        <v>0.02461342445126542</v>
+        <v>0.02356033685440296</v>
       </c>
       <c r="W3">
-        <v>-0.1062221360728823</v>
+        <v>0.05002513826043237</v>
       </c>
       <c r="X3">
-        <v>0.1546031226124975</v>
+        <v>0.1214310479426295</v>
       </c>
       <c r="Y3">
-        <v>-0.2608252586853798</v>
+        <v>-0.07140590968219712</v>
       </c>
       <c r="Z3">
-        <v>0.2831640397221604</v>
+        <v>0.4061534107717624</v>
       </c>
       <c r="AA3">
-        <v>-0.02674493319397352</v>
+        <v>0.01770550790937739</v>
       </c>
       <c r="AB3">
-        <v>0.08987868958236667</v>
+        <v>0.07332927201895137</v>
       </c>
       <c r="AC3">
-        <v>-0.1166236227763402</v>
+        <v>-0.05562376410957398</v>
       </c>
       <c r="AD3">
-        <v>2157.5</v>
+        <v>2548.5</v>
       </c>
       <c r="AE3">
-        <v>120.1169378953406</v>
+        <v>227.6163458760099</v>
       </c>
       <c r="AF3">
-        <v>2277.61693789534</v>
+        <v>2776.11634587601</v>
       </c>
       <c r="AG3">
-        <v>2235.11693789534</v>
+        <v>2727.71634587601</v>
       </c>
       <c r="AH3">
-        <v>0.5687903762913558</v>
+        <v>0.5747157485184753</v>
       </c>
       <c r="AI3">
-        <v>0.8513128946873844</v>
+        <v>0.8641832337330411</v>
       </c>
       <c r="AJ3">
-        <v>0.5641646176319077</v>
+        <v>0.5704113387710146</v>
       </c>
       <c r="AK3">
-        <v>0.8489128182228235</v>
+        <v>0.8621056428584274</v>
       </c>
       <c r="AL3">
-        <v>59.5</v>
+        <v>75.3</v>
       </c>
       <c r="AM3">
-        <v>59.499</v>
+        <v>75.298</v>
       </c>
       <c r="AN3">
-        <v>19.36714542190305</v>
+        <v>8.444333996023856</v>
       </c>
       <c r="AO3">
-        <v>-0.8</v>
+        <v>1.318725099601594</v>
       </c>
       <c r="AP3">
-        <v>20.06388633658295</v>
+        <v>9.038158866388368</v>
       </c>
       <c r="AQ3">
-        <v>-0.8000134456041278</v>
+        <v>1.318760126430981</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Basic-Fit N.V. (ENXTAM:BFIT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTAM:BFIT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-1.22310756972112</v>
+      </c>
+      <c r="F2">
+        <v>4.93037432917363</v>
+      </c>
+      <c r="G2">
+        <v>9.19852997308154</v>
+      </c>
+      <c r="H2">
+        <v>1.44048201169265</v>
+      </c>
+      <c r="I2">
+        <v>0.574715748518475</v>
+      </c>
+      <c r="J2">
+        <v>0.09</v>
+      </c>
+      <c r="K2">
+        <v>2054.3</v>
+      </c>
+      <c r="L2">
+        <v>3720.23927364602</v>
+      </c>
+      <c r="M2">
+        <v>4782.01634587601</v>
+      </c>
+      <c r="N2">
+        <v>4106.57674477486</v>
+      </c>
+      <c r="O2">
+        <v>2776.11634587601</v>
+      </c>
+      <c r="P2">
+        <v>434.737471128841</v>
+      </c>
+      <c r="Q2">
+        <v>0.0733292720189514</v>
+      </c>
+      <c r="R2">
+        <v>0.0790085614048051</v>
+      </c>
+      <c r="S2">
+        <v>0.03773441</v>
+      </c>
+      <c r="T2">
+        <v>0.0377678</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.12143104794263</v>
+      </c>
+      <c r="X2">
+        <v>0.0830873180272583</v>
+      </c>
+      <c r="Y2">
+        <v>1.7963271291876</v>
+      </c>
+      <c r="Z2">
+        <v>0.962767783201268</v>
+      </c>
+      <c r="AA2">
+        <v>2548.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.050855</v>
+      </c>
+      <c r="AC2">
+        <v>-1.223107569721115</v>
+      </c>
+      <c r="AD2">
+        <v>2776.11634587601</v>
+      </c>
+      <c r="AE2">
+        <v>75.3</v>
+      </c>
+      <c r="AF2">
+        <v>393.9</v>
+      </c>
+      <c r="AG2">
+        <v>301.8</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>2054.3</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.258</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>304.48</v>
+      </c>
+      <c r="AR2">
+        <v>75.3</v>
+      </c>
+      <c r="AS2">
+        <v>2548.5</v>
+      </c>
+      <c r="AT2">
+        <v>48.4</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08005950511354153</v>
+      </c>
+      <c r="C2">
+        <v>4050.375853841053</v>
+      </c>
+      <c r="D2">
+        <v>4001.975853841052</v>
+      </c>
+      <c r="E2">
+        <v>-2776.11634587601</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>48.4</v>
+      </c>
+      <c r="H2">
+        <v>2054.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K2">
+        <v>393.9</v>
+      </c>
+      <c r="L2">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="O2">
+        <v>28.14780000000002</v>
+      </c>
+      <c r="P2">
+        <v>80.95220000000006</v>
+      </c>
+      <c r="Q2">
+        <v>474.8522</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08005950511354153</v>
+      </c>
+      <c r="T2">
+        <v>0.8969457633378592</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.258</v>
+      </c>
+      <c r="W2">
+        <v>0.0331674</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.0798967295903486</v>
+      </c>
+      <c r="C3">
+        <v>4017.92267706439</v>
+      </c>
+      <c r="D3">
+        <v>4017.826840523151</v>
+      </c>
+      <c r="E3">
+        <v>-2727.812182417249</v>
+      </c>
+      <c r="F3">
+        <v>48.30416345876011</v>
+      </c>
+      <c r="G3">
+        <v>48.4</v>
+      </c>
+      <c r="H3">
+        <v>2054.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K3">
+        <v>393.9</v>
+      </c>
+      <c r="L3">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M3">
+        <v>2.159196106606577</v>
+      </c>
+      <c r="N3">
+        <v>106.9408038933935</v>
+      </c>
+      <c r="O3">
+        <v>27.59072740449552</v>
+      </c>
+      <c r="P3">
+        <v>79.35007648889798</v>
+      </c>
+      <c r="Q3">
+        <v>473.2500764888979</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08036874302055413</v>
+      </c>
+      <c r="T3">
+        <v>0.9036683265337854</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.258</v>
+      </c>
+      <c r="W3">
+        <v>0.0331674</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>50.52806443388006</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07973395406715564</v>
+      </c>
+      <c r="C4">
+        <v>3985.595564466438</v>
+      </c>
+      <c r="D4">
+        <v>4033.803891383958</v>
+      </c>
+      <c r="E4">
+        <v>-2679.50801895849</v>
+      </c>
+      <c r="F4">
+        <v>96.60832691752022</v>
+      </c>
+      <c r="G4">
+        <v>48.4</v>
+      </c>
+      <c r="H4">
+        <v>2054.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K4">
+        <v>393.9</v>
+      </c>
+      <c r="L4">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M4">
+        <v>4.318392213213154</v>
+      </c>
+      <c r="N4">
+        <v>104.7816077867869</v>
+      </c>
+      <c r="O4">
+        <v>27.03365480899103</v>
+      </c>
+      <c r="P4">
+        <v>77.74795297779589</v>
+      </c>
+      <c r="Q4">
+        <v>471.6479529777959</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08068429190526086</v>
+      </c>
+      <c r="T4">
+        <v>0.9105280848969753</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.258</v>
+      </c>
+      <c r="W4">
+        <v>0.0331674</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>25.26403221694003</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07957117854396271</v>
+      </c>
+      <c r="C5">
+        <v>3953.396025949281</v>
+      </c>
+      <c r="D5">
+        <v>4049.908516325562</v>
+      </c>
+      <c r="E5">
+        <v>-2631.203855499729</v>
+      </c>
+      <c r="F5">
+        <v>144.9124903762803</v>
+      </c>
+      <c r="G5">
+        <v>48.4</v>
+      </c>
+      <c r="H5">
+        <v>2054.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K5">
+        <v>393.9</v>
+      </c>
+      <c r="L5">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M5">
+        <v>6.477588319819731</v>
+      </c>
+      <c r="N5">
+        <v>102.6224116801803</v>
+      </c>
+      <c r="O5">
+        <v>26.47658221348653</v>
+      </c>
+      <c r="P5">
+        <v>76.14582946669381</v>
+      </c>
+      <c r="Q5">
+        <v>470.0458294666938</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08100634695253889</v>
+      </c>
+      <c r="T5">
+        <v>0.9175292815769321</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.258</v>
+      </c>
+      <c r="W5">
+        <v>0.0331674</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>16.84268814462668</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07944105102076977</v>
+      </c>
+      <c r="C6">
+        <v>3918.059159131499</v>
+      </c>
+      <c r="D6">
+        <v>4062.875812966539</v>
+      </c>
+      <c r="E6">
+        <v>-2582.89969204097</v>
+      </c>
+      <c r="F6">
+        <v>193.2166538350404</v>
+      </c>
+      <c r="G6">
+        <v>48.4</v>
+      </c>
+      <c r="H6">
+        <v>2054.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K6">
+        <v>393.9</v>
+      </c>
+      <c r="L6">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M6">
+        <v>8.849322745644852</v>
+      </c>
+      <c r="N6">
+        <v>100.2506772543552</v>
+      </c>
+      <c r="O6">
+        <v>25.86467473162365</v>
+      </c>
+      <c r="P6">
+        <v>74.38600252273157</v>
+      </c>
+      <c r="Q6">
+        <v>468.2860025227316</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08133511147996852</v>
+      </c>
+      <c r="T6">
+        <v>0.9246763365210547</v>
+      </c>
+      <c r="U6">
+        <v>0.0458</v>
+      </c>
+      <c r="V6">
+        <v>0.258</v>
+      </c>
+      <c r="W6">
+        <v>0.0339836</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>12.32862707529715</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07936805749757683</v>
+      </c>
+      <c r="C7">
+        <v>3877.065269769583</v>
+      </c>
+      <c r="D7">
+        <v>4070.186087063383</v>
+      </c>
+      <c r="E7">
+        <v>-2534.595528582209</v>
+      </c>
+      <c r="F7">
+        <v>241.5208172938005</v>
+      </c>
+      <c r="G7">
+        <v>48.4</v>
+      </c>
+      <c r="H7">
+        <v>2054.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K7">
+        <v>393.9</v>
+      </c>
+      <c r="L7">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M7">
+        <v>11.59299923010242</v>
+      </c>
+      <c r="N7">
+        <v>97.50700076989766</v>
+      </c>
+      <c r="O7">
+        <v>25.1568061986336</v>
+      </c>
+      <c r="P7">
+        <v>72.35019457126407</v>
+      </c>
+      <c r="Q7">
+        <v>466.250194571264</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08167079736587035</v>
+      </c>
+      <c r="T7">
+        <v>0.9319738557797904</v>
+      </c>
+      <c r="U7">
+        <v>0.048</v>
+      </c>
+      <c r="V7">
+        <v>0.258</v>
+      </c>
+      <c r="W7">
+        <v>0.035616</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>9.410852000810163</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.0792297679743839</v>
+      </c>
+      <c r="C8">
+        <v>3842.683127670013</v>
+      </c>
+      <c r="D8">
+        <v>4084.108108422574</v>
+      </c>
+      <c r="E8">
+        <v>-2486.291365123449</v>
+      </c>
+      <c r="F8">
+        <v>289.8249807525606</v>
+      </c>
+      <c r="G8">
+        <v>48.4</v>
+      </c>
+      <c r="H8">
+        <v>2054.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K8">
+        <v>393.9</v>
+      </c>
+      <c r="L8">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M8">
+        <v>13.91159907612291</v>
+      </c>
+      <c r="N8">
+        <v>95.18840092387717</v>
+      </c>
+      <c r="O8">
+        <v>24.55860743836031</v>
+      </c>
+      <c r="P8">
+        <v>70.62979348551686</v>
+      </c>
+      <c r="Q8">
+        <v>464.5297934855168</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08201362550466373</v>
+      </c>
+      <c r="T8">
+        <v>0.9394266414057332</v>
+      </c>
+      <c r="U8">
+        <v>0.048</v>
+      </c>
+      <c r="V8">
+        <v>0.258</v>
+      </c>
+      <c r="W8">
+        <v>0.035616</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>7.842376667341801</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07916938845119097</v>
+      </c>
+      <c r="C9">
+        <v>3800.487466462981</v>
+      </c>
+      <c r="D9">
+        <v>4090.216610674302</v>
+      </c>
+      <c r="E9">
+        <v>-2437.987201664689</v>
+      </c>
+      <c r="F9">
+        <v>338.1291442113207</v>
+      </c>
+      <c r="G9">
+        <v>48.4</v>
+      </c>
+      <c r="H9">
+        <v>2054.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K9">
+        <v>393.9</v>
+      </c>
+      <c r="L9">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M9">
+        <v>16.73739263846038</v>
+      </c>
+      <c r="N9">
+        <v>92.3626073615397</v>
+      </c>
+      <c r="O9">
+        <v>23.82955269927724</v>
+      </c>
+      <c r="P9">
+        <v>68.53305466226246</v>
+      </c>
+      <c r="Q9">
+        <v>462.4330546622624</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08236382629160319</v>
+      </c>
+      <c r="T9">
+        <v>0.9470397019913737</v>
+      </c>
+      <c r="U9">
+        <v>0.0495</v>
+      </c>
+      <c r="V9">
+        <v>0.258</v>
+      </c>
+      <c r="W9">
+        <v>0.036729</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>6.518339048180199</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07912533292799802</v>
+      </c>
+      <c r="C10">
+        <v>3756.651874487002</v>
+      </c>
+      <c r="D10">
+        <v>4094.685182157084</v>
+      </c>
+      <c r="E10">
+        <v>-2389.683038205929</v>
+      </c>
+      <c r="F10">
+        <v>386.4333076700809</v>
+      </c>
+      <c r="G10">
+        <v>48.4</v>
+      </c>
+      <c r="H10">
+        <v>2054.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K10">
+        <v>393.9</v>
+      </c>
+      <c r="L10">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M10">
+        <v>19.66945536040712</v>
+      </c>
+      <c r="N10">
+        <v>89.43054463959297</v>
+      </c>
+      <c r="O10">
+        <v>23.07308051701499</v>
+      </c>
+      <c r="P10">
+        <v>66.35746412257798</v>
+      </c>
+      <c r="Q10">
+        <v>460.257464122578</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08272164013912828</v>
+      </c>
+      <c r="T10">
+        <v>0.9548182638940932</v>
+      </c>
+      <c r="U10">
+        <v>0.0509</v>
+      </c>
+      <c r="V10">
+        <v>0.258</v>
+      </c>
+      <c r="W10">
+        <v>0.0377678</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>5.546671120320331</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.0790085614048051</v>
+      </c>
+      <c r="C11">
+        <v>3720.239273646019</v>
+      </c>
+      <c r="D11">
+        <v>4106.57674477486</v>
+      </c>
+      <c r="E11">
+        <v>-2341.378874747169</v>
+      </c>
+      <c r="F11">
+        <v>434.7374711288409</v>
+      </c>
+      <c r="G11">
+        <v>48.4</v>
+      </c>
+      <c r="H11">
+        <v>2054.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K11">
+        <v>393.9</v>
+      </c>
+      <c r="L11">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M11">
+        <v>22.128137280458</v>
+      </c>
+      <c r="N11">
+        <v>86.97186271954207</v>
+      </c>
+      <c r="O11">
+        <v>22.43874058164186</v>
+      </c>
+      <c r="P11">
+        <v>64.53312213790022</v>
+      </c>
+      <c r="Q11">
+        <v>458.4331221379002</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08308731802725834</v>
+      </c>
+      <c r="T11">
+        <v>0.9627677832012683</v>
+      </c>
+      <c r="U11">
+        <v>0.0509</v>
+      </c>
+      <c r="V11">
+        <v>0.258</v>
+      </c>
+      <c r="W11">
+        <v>0.0377678</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>4.930374329173628</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.07908470988161218</v>
+      </c>
+      <c r="C12">
+        <v>3664.172622510794</v>
+      </c>
+      <c r="D12">
+        <v>4098.814257098396</v>
+      </c>
+      <c r="E12">
+        <v>-2293.074711288409</v>
+      </c>
+      <c r="F12">
+        <v>483.041634587601</v>
+      </c>
+      <c r="G12">
+        <v>48.4</v>
+      </c>
+      <c r="H12">
+        <v>2054.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K12">
+        <v>393.9</v>
+      </c>
+      <c r="L12">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M12">
+        <v>25.84272745043666</v>
+      </c>
+      <c r="N12">
+        <v>83.25727254956342</v>
+      </c>
+      <c r="O12">
+        <v>21.48037631778736</v>
+      </c>
+      <c r="P12">
+        <v>61.77689623177606</v>
+      </c>
+      <c r="Q12">
+        <v>455.676896231776</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08346112209068018</v>
+      </c>
+      <c r="T12">
+        <v>0.9708939584930473</v>
+      </c>
+      <c r="U12">
+        <v>0.0535</v>
+      </c>
+      <c r="V12">
+        <v>0.258</v>
+      </c>
+      <c r="W12">
+        <v>0.039697</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>4.221690617185867</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.07920760435841921</v>
+      </c>
+      <c r="C13">
+        <v>3603.402448219339</v>
+      </c>
+      <c r="D13">
+        <v>4086.3482462657</v>
+      </c>
+      <c r="E13">
+        <v>-2244.770547829648</v>
+      </c>
+      <c r="F13">
+        <v>531.3457980463611</v>
+      </c>
+      <c r="G13">
+        <v>48.4</v>
+      </c>
+      <c r="H13">
+        <v>2054.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K13">
+        <v>393.9</v>
+      </c>
+      <c r="L13">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M13">
+        <v>29.86163385020549</v>
+      </c>
+      <c r="N13">
+        <v>79.23836614979459</v>
+      </c>
+      <c r="O13">
+        <v>20.443498466647</v>
+      </c>
+      <c r="P13">
+        <v>58.79486768314759</v>
+      </c>
+      <c r="Q13">
+        <v>452.6948676831475</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08384332624541485</v>
+      </c>
+      <c r="T13">
+        <v>0.9792027444655401</v>
+      </c>
+      <c r="U13">
+        <v>0.0562</v>
+      </c>
+      <c r="V13">
+        <v>0.258</v>
+      </c>
+      <c r="W13">
+        <v>0.0417004</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>3.653517438036945</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.07954864683522631</v>
+      </c>
+      <c r="C14">
+        <v>3520.897926337927</v>
+      </c>
+      <c r="D14">
+        <v>4052.147887843049</v>
+      </c>
+      <c r="E14">
+        <v>-2196.466384370889</v>
+      </c>
+      <c r="F14">
+        <v>579.6499615051213</v>
+      </c>
+      <c r="G14">
+        <v>48.4</v>
+      </c>
+      <c r="H14">
+        <v>2054.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K14">
+        <v>393.9</v>
+      </c>
+      <c r="L14">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M14">
+        <v>35.30068265566189</v>
+      </c>
+      <c r="N14">
+        <v>73.79931734433819</v>
+      </c>
+      <c r="O14">
+        <v>19.04022387483925</v>
+      </c>
+      <c r="P14">
+        <v>54.75909346949894</v>
+      </c>
+      <c r="Q14">
+        <v>448.6590934694989</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.0842342168582117</v>
+      </c>
+      <c r="T14">
+        <v>0.9877003664828627</v>
+      </c>
+      <c r="U14">
+        <v>0.0609</v>
+      </c>
+      <c r="V14">
+        <v>0.258</v>
+      </c>
+      <c r="W14">
+        <v>0.0451878</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>3.090591790085439</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08085651531203335</v>
+      </c>
+      <c r="C15">
+        <v>3346.58055311726</v>
+      </c>
+      <c r="D15">
+        <v>3926.134678081141</v>
+      </c>
+      <c r="E15">
+        <v>-2148.162220912128</v>
+      </c>
+      <c r="F15">
+        <v>627.9541249638813</v>
+      </c>
+      <c r="G15">
+        <v>48.4</v>
+      </c>
+      <c r="H15">
+        <v>2054.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K15">
+        <v>393.9</v>
+      </c>
+      <c r="L15">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M15">
+        <v>47.0337639597947</v>
+      </c>
+      <c r="N15">
+        <v>62.06623604020537</v>
+      </c>
+      <c r="O15">
+        <v>16.01308889837299</v>
+      </c>
+      <c r="P15">
+        <v>46.05314714183238</v>
+      </c>
+      <c r="Q15">
+        <v>439.9531471418323</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08463409346210729</v>
+      </c>
+      <c r="T15">
+        <v>0.9963933361327671</v>
+      </c>
+      <c r="U15">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V15">
+        <v>0.258</v>
+      </c>
+      <c r="W15">
+        <v>0.05557579999999999</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>2.319610229223005</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08091782378884041</v>
+      </c>
+      <c r="C16">
+        <v>3292.561342792372</v>
+      </c>
+      <c r="D16">
+        <v>3920.419631215013</v>
+      </c>
+      <c r="E16">
+        <v>-2099.858057453368</v>
+      </c>
+      <c r="F16">
+        <v>676.2582884226415</v>
+      </c>
+      <c r="G16">
+        <v>48.4</v>
+      </c>
+      <c r="H16">
+        <v>2054.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K16">
+        <v>393.9</v>
+      </c>
+      <c r="L16">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M16">
+        <v>50.65174580285584</v>
+      </c>
+      <c r="N16">
+        <v>58.44825419714424</v>
+      </c>
+      <c r="O16">
+        <v>15.07964958286321</v>
+      </c>
+      <c r="P16">
+        <v>43.36860461428103</v>
+      </c>
+      <c r="Q16">
+        <v>437.268604614281</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08504326952190745</v>
+      </c>
+      <c r="T16">
+        <v>1.005288467867553</v>
+      </c>
+      <c r="U16">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V16">
+        <v>0.258</v>
+      </c>
+      <c r="W16">
+        <v>0.05557579999999999</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>2.153923784278504</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08097913226564747</v>
+      </c>
+      <c r="C17">
+        <v>3238.558746408995</v>
+      </c>
+      <c r="D17">
+        <v>3914.721198290396</v>
+      </c>
+      <c r="E17">
+        <v>-2051.553893994608</v>
+      </c>
+      <c r="F17">
+        <v>724.5624518814016</v>
+      </c>
+      <c r="G17">
+        <v>48.4</v>
+      </c>
+      <c r="H17">
+        <v>2054.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K17">
+        <v>393.9</v>
+      </c>
+      <c r="L17">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M17">
+        <v>54.26972764591697</v>
+      </c>
+      <c r="N17">
+        <v>54.83027235408311</v>
+      </c>
+      <c r="O17">
+        <v>14.14621026735344</v>
+      </c>
+      <c r="P17">
+        <v>40.68406208672967</v>
+      </c>
+      <c r="Q17">
+        <v>434.5840620867297</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08546207325370292</v>
+      </c>
+      <c r="T17">
+        <v>1.014392896819629</v>
+      </c>
+      <c r="U17">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V17">
+        <v>0.258</v>
+      </c>
+      <c r="W17">
+        <v>0.05557579999999999</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>2.010328865326604</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08297557674245452</v>
+      </c>
+      <c r="C18">
+        <v>3013.335024884674</v>
+      </c>
+      <c r="D18">
+        <v>3737.801640224835</v>
+      </c>
+      <c r="E18">
+        <v>-2003.249730535848</v>
+      </c>
+      <c r="F18">
+        <v>772.8666153401617</v>
+      </c>
+      <c r="G18">
+        <v>48.4</v>
+      </c>
+      <c r="H18">
+        <v>2054.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K18">
+        <v>393.9</v>
+      </c>
+      <c r="L18">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M18">
+        <v>70.48543531902276</v>
+      </c>
+      <c r="N18">
+        <v>38.61456468097732</v>
+      </c>
+      <c r="O18">
+        <v>9.962557687692151</v>
+      </c>
+      <c r="P18">
+        <v>28.65200699328517</v>
+      </c>
+      <c r="Q18">
+        <v>422.5520069932851</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08589084850292206</v>
+      </c>
+      <c r="T18">
+        <v>1.02371409788961</v>
+      </c>
+      <c r="U18">
+        <v>0.0912</v>
+      </c>
+      <c r="V18">
+        <v>0.258</v>
+      </c>
+      <c r="W18">
+        <v>0.06767040000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>1.54783750013325</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09272300944992641</v>
+      </c>
+      <c r="C19">
+        <v>2289.36438187227</v>
+      </c>
+      <c r="D19">
+        <v>3062.135160671192</v>
+      </c>
+      <c r="E19">
+        <v>-1954.945567077088</v>
+      </c>
+      <c r="F19">
+        <v>821.1707787989218</v>
+      </c>
+      <c r="G19">
+        <v>48.4</v>
+      </c>
+      <c r="H19">
+        <v>2054.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K19">
+        <v>393.9</v>
+      </c>
+      <c r="L19">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M19">
+        <v>128.5953439599112</v>
+      </c>
+      <c r="N19">
+        <v>-19.49534395991108</v>
+      </c>
+      <c r="O19">
+        <v>-5.02979874165706</v>
+      </c>
+      <c r="P19">
+        <v>-14.46554521825402</v>
+      </c>
+      <c r="Q19">
+        <v>379.434454781746</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08666049278172056</v>
+      </c>
+      <c r="T19">
+        <v>1.040445495254795</v>
+      </c>
+      <c r="U19">
+        <v>0.1566</v>
+      </c>
+      <c r="V19">
+        <v>0.2188866185448746</v>
+      </c>
+      <c r="W19">
+        <v>0.1223223555358727</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.8483977462979636</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09390100944992642</v>
+      </c>
+      <c r="C20">
+        <v>2175.595079838349</v>
+      </c>
+      <c r="D20">
+        <v>2996.670022096031</v>
+      </c>
+      <c r="E20">
+        <v>-1906.641403618328</v>
+      </c>
+      <c r="F20">
+        <v>869.4749422576818</v>
+      </c>
+      <c r="G20">
+        <v>48.4</v>
+      </c>
+      <c r="H20">
+        <v>2054.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K20">
+        <v>393.9</v>
+      </c>
+      <c r="L20">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M20">
+        <v>136.159775957553</v>
+      </c>
+      <c r="N20">
+        <v>-27.05977595755292</v>
+      </c>
+      <c r="O20">
+        <v>-6.981422197048652</v>
+      </c>
+      <c r="P20">
+        <v>-20.07835376050426</v>
+      </c>
+      <c r="Q20">
+        <v>373.8216462394957</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08724415732783911</v>
+      </c>
+      <c r="T20">
+        <v>1.053133854953024</v>
+      </c>
+      <c r="U20">
+        <v>0.1566</v>
+      </c>
+      <c r="V20">
+        <v>0.2067262508479371</v>
+      </c>
+      <c r="W20">
+        <v>0.1242266691172131</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.801264538170299</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1053808334761048</v>
+      </c>
+      <c r="C21">
+        <v>1610.607019195683</v>
+      </c>
+      <c r="D21">
+        <v>2479.986124912125</v>
+      </c>
+      <c r="E21">
+        <v>-1858.337240159568</v>
+      </c>
+      <c r="F21">
+        <v>917.779105716442</v>
+      </c>
+      <c r="G21">
+        <v>48.4</v>
+      </c>
+      <c r="H21">
+        <v>2054.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K21">
+        <v>393.9</v>
+      </c>
+      <c r="L21">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M21">
+        <v>191.6322772735931</v>
+      </c>
+      <c r="N21">
+        <v>-82.53227727359302</v>
+      </c>
+      <c r="O21">
+        <v>-21.293327536587</v>
+      </c>
+      <c r="P21">
+        <v>-61.23894973700602</v>
+      </c>
+      <c r="Q21">
+        <v>332.661050262994</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.0883160901666746</v>
+      </c>
+      <c r="T21">
+        <v>1.076436742753796</v>
+      </c>
+      <c r="U21">
+        <v>0.2088</v>
+      </c>
+      <c r="V21">
+        <v>0.1468844413919553</v>
+      </c>
+      <c r="W21">
+        <v>0.1781305286373597</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.5693195402788966</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1070808334761048</v>
+      </c>
+      <c r="C22">
+        <v>1500.558202109841</v>
+      </c>
+      <c r="D22">
+        <v>2418.241471285043</v>
+      </c>
+      <c r="E22">
+        <v>-1810.033076700808</v>
+      </c>
+      <c r="F22">
+        <v>966.0832691752021</v>
+      </c>
+      <c r="G22">
+        <v>48.4</v>
+      </c>
+      <c r="H22">
+        <v>2054.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K22">
+        <v>393.9</v>
+      </c>
+      <c r="L22">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M22">
+        <v>201.7181866037822</v>
+      </c>
+      <c r="N22">
+        <v>-92.61818660378214</v>
+      </c>
+      <c r="O22">
+        <v>-23.89549214377579</v>
+      </c>
+      <c r="P22">
+        <v>-68.72269446000635</v>
+      </c>
+      <c r="Q22">
+        <v>325.1773055399937</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08893504129375804</v>
+      </c>
+      <c r="T22">
+        <v>1.089892202038218</v>
+      </c>
+      <c r="U22">
+        <v>0.2088</v>
+      </c>
+      <c r="V22">
+        <v>0.1395402193223576</v>
+      </c>
+      <c r="W22">
+        <v>0.1796640022054918</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.5408535632649518</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1087808334761048</v>
+      </c>
+      <c r="C23">
+        <v>1393.509232437986</v>
+      </c>
+      <c r="D23">
+        <v>2359.496665071948</v>
+      </c>
+      <c r="E23">
+        <v>-1761.728913242048</v>
+      </c>
+      <c r="F23">
+        <v>1014.387432633962</v>
+      </c>
+      <c r="G23">
+        <v>48.4</v>
+      </c>
+      <c r="H23">
+        <v>2054.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K23">
+        <v>393.9</v>
+      </c>
+      <c r="L23">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M23">
+        <v>211.8040959339713</v>
+      </c>
+      <c r="N23">
+        <v>-102.7040959339712</v>
+      </c>
+      <c r="O23">
+        <v>-26.49765675096457</v>
+      </c>
+      <c r="P23">
+        <v>-76.20643918300664</v>
+      </c>
+      <c r="Q23">
+        <v>317.6935608169933</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08956966206962838</v>
+      </c>
+      <c r="T23">
+        <v>1.103688305861487</v>
+      </c>
+      <c r="U23">
+        <v>0.2088</v>
+      </c>
+      <c r="V23">
+        <v>0.1328954469736739</v>
+      </c>
+      <c r="W23">
+        <v>0.1810514306718969</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.5150986316809065</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1172254907724032</v>
+      </c>
+      <c r="C24">
+        <v>1091.140471715617</v>
+      </c>
+      <c r="D24">
+        <v>2105.432067808339</v>
+      </c>
+      <c r="E24">
+        <v>-1713.424749783288</v>
+      </c>
+      <c r="F24">
+        <v>1062.691596092722</v>
+      </c>
+      <c r="G24">
+        <v>48.4</v>
+      </c>
+      <c r="H24">
+        <v>2054.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K24">
+        <v>393.9</v>
+      </c>
+      <c r="L24">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M24">
+        <v>253.7707531469421</v>
+      </c>
+      <c r="N24">
+        <v>-144.670753146942</v>
+      </c>
+      <c r="O24">
+        <v>-37.32505431191103</v>
+      </c>
+      <c r="P24">
+        <v>-107.345698835031</v>
+      </c>
+      <c r="Q24">
+        <v>286.554301164969</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09040601324526257</v>
+      </c>
+      <c r="T24">
+        <v>1.121869853157882</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.1109182191050261</v>
+      </c>
+      <c r="W24">
+        <v>0.2123127292777198</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.4299155779264578</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1192254907724032</v>
+      </c>
+      <c r="C25">
+        <v>990.4789760829935</v>
+      </c>
+      <c r="D25">
+        <v>2053.074735634476</v>
+      </c>
+      <c r="E25">
+        <v>-1665.120586324527</v>
+      </c>
+      <c r="F25">
+        <v>1110.995759551482</v>
+      </c>
+      <c r="G25">
+        <v>48.4</v>
+      </c>
+      <c r="H25">
+        <v>2054.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K25">
+        <v>393.9</v>
+      </c>
+      <c r="L25">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M25">
+        <v>265.305787380894</v>
+      </c>
+      <c r="N25">
+        <v>-156.2057873808939</v>
+      </c>
+      <c r="O25">
+        <v>-40.30109314427063</v>
+      </c>
+      <c r="P25">
+        <v>-115.9046942366233</v>
+      </c>
+      <c r="Q25">
+        <v>277.9953057633767</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09107622120948675</v>
+      </c>
+      <c r="T25">
+        <v>1.136439591510582</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.1060956878395902</v>
+      </c>
+      <c r="W25">
+        <v>0.2134643497439059</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.4112235962774814</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1212254907724031</v>
+      </c>
+      <c r="C26">
+        <v>892.3583125004186</v>
+      </c>
+      <c r="D26">
+        <v>2003.258235510661</v>
+      </c>
+      <c r="E26">
+        <v>-1616.816422865767</v>
+      </c>
+      <c r="F26">
+        <v>1159.299923010243</v>
+      </c>
+      <c r="G26">
+        <v>48.4</v>
+      </c>
+      <c r="H26">
+        <v>2054.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K26">
+        <v>393.9</v>
+      </c>
+      <c r="L26">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M26">
+        <v>276.8408216148459</v>
+      </c>
+      <c r="N26">
+        <v>-167.7408216148459</v>
+      </c>
+      <c r="O26">
+        <v>-43.27713197663023</v>
+      </c>
+      <c r="P26">
+        <v>-124.4636896382156</v>
+      </c>
+      <c r="Q26">
+        <v>269.4363103617844</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09176406622540105</v>
+      </c>
+      <c r="T26">
+        <v>1.151392744030458</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.1016750341796073</v>
+      </c>
+      <c r="W26">
+        <v>0.2145200018379098</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3940892797659197</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1232254907724031</v>
+      </c>
+      <c r="C27">
+        <v>796.5979076344013</v>
+      </c>
+      <c r="D27">
+        <v>1955.801994103404</v>
+      </c>
+      <c r="E27">
+        <v>-1568.512259407007</v>
+      </c>
+      <c r="F27">
+        <v>1207.604086469003</v>
+      </c>
+      <c r="G27">
+        <v>48.4</v>
+      </c>
+      <c r="H27">
+        <v>2054.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K27">
+        <v>393.9</v>
+      </c>
+      <c r="L27">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M27">
+        <v>288.3758558487978</v>
+      </c>
+      <c r="N27">
+        <v>-179.2758558487977</v>
+      </c>
+      <c r="O27">
+        <v>-46.25317080898981</v>
+      </c>
+      <c r="P27">
+        <v>-133.0226850398079</v>
+      </c>
+      <c r="Q27">
+        <v>260.8773149601921</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09247025377507306</v>
+      </c>
+      <c r="T27">
+        <v>1.166744647284197</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.097608032812423</v>
+      </c>
+      <c r="W27">
+        <v>0.2154912017643934</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3783257085752829</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1252254907724031</v>
+      </c>
+      <c r="C28">
+        <v>703.0339029731451</v>
+      </c>
+      <c r="D28">
+        <v>1910.542152900908</v>
+      </c>
+      <c r="E28">
+        <v>-1520.208095948247</v>
+      </c>
+      <c r="F28">
+        <v>1255.908249927763</v>
+      </c>
+      <c r="G28">
+        <v>48.4</v>
+      </c>
+      <c r="H28">
+        <v>2054.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K28">
+        <v>393.9</v>
+      </c>
+      <c r="L28">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M28">
+        <v>299.9108900827497</v>
+      </c>
+      <c r="N28">
+        <v>-190.8108900827497</v>
+      </c>
+      <c r="O28">
+        <v>-49.22920964134941</v>
+      </c>
+      <c r="P28">
+        <v>-141.5816804414002</v>
+      </c>
+      <c r="Q28">
+        <v>252.3183195585997</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09319552747473622</v>
+      </c>
+      <c r="T28">
+        <v>1.182511466842092</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.09385387770425288</v>
+      </c>
+      <c r="W28">
+        <v>0.2163876940042244</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3637747197839258</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1272254907724032</v>
+      </c>
+      <c r="C29">
+        <v>611.517264554682</v>
+      </c>
+      <c r="D29">
+        <v>1867.329677941205</v>
+      </c>
+      <c r="E29">
+        <v>-1471.903932489487</v>
+      </c>
+      <c r="F29">
+        <v>1304.212413386523</v>
+      </c>
+      <c r="G29">
+        <v>48.4</v>
+      </c>
+      <c r="H29">
+        <v>2054.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K29">
+        <v>393.9</v>
+      </c>
+      <c r="L29">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M29">
+        <v>311.4459243167017</v>
+      </c>
+      <c r="N29">
+        <v>-202.3459243167016</v>
+      </c>
+      <c r="O29">
+        <v>-52.20524847370901</v>
+      </c>
+      <c r="P29">
+        <v>-150.1406758429926</v>
+      </c>
+      <c r="Q29">
+        <v>243.7593241570074</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09394067168671891</v>
+      </c>
+      <c r="T29">
+        <v>1.198710254059107</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.09037780815965091</v>
+      </c>
+      <c r="W29">
+        <v>0.2172177794114754</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3503015820141508</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1292254907724032</v>
+      </c>
+      <c r="C30">
+        <v>521.9121435453305</v>
+      </c>
+      <c r="D30">
+        <v>1826.028720390613</v>
+      </c>
+      <c r="E30">
+        <v>-1423.599769030727</v>
+      </c>
+      <c r="F30">
+        <v>1352.516576845283</v>
+      </c>
+      <c r="G30">
+        <v>48.4</v>
+      </c>
+      <c r="H30">
+        <v>2054.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K30">
+        <v>393.9</v>
+      </c>
+      <c r="L30">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M30">
+        <v>322.9809585506536</v>
+      </c>
+      <c r="N30">
+        <v>-213.8809585506535</v>
+      </c>
+      <c r="O30">
+        <v>-55.18128730606861</v>
+      </c>
+      <c r="P30">
+        <v>-158.6996712445849</v>
+      </c>
+      <c r="Q30">
+        <v>235.2003287554151</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09470651434903446</v>
+      </c>
+      <c r="T30">
+        <v>1.215359007587705</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.08715002929680624</v>
+      </c>
+      <c r="W30">
+        <v>0.2179885730039227</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3377908112279311</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1312254907724031</v>
+      </c>
+      <c r="C31">
+        <v>434.0944496713057</v>
+      </c>
+      <c r="D31">
+        <v>1786.515189975348</v>
+      </c>
+      <c r="E31">
+        <v>-1375.295605571967</v>
+      </c>
+      <c r="F31">
+        <v>1400.820740304043</v>
+      </c>
+      <c r="G31">
+        <v>48.4</v>
+      </c>
+      <c r="H31">
+        <v>2054.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K31">
+        <v>393.9</v>
+      </c>
+      <c r="L31">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M31">
+        <v>334.5159927846054</v>
+      </c>
+      <c r="N31">
+        <v>-225.4159927846054</v>
+      </c>
+      <c r="O31">
+        <v>-58.15732613842818</v>
+      </c>
+      <c r="P31">
+        <v>-167.2586666461772</v>
+      </c>
+      <c r="Q31">
+        <v>226.6413333538228</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09549393004409126</v>
+      </c>
+      <c r="T31">
+        <v>1.232476740088941</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.08414485587277845</v>
+      </c>
+      <c r="W31">
+        <v>0.2187062084175805</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3261428522200716</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1332254907724031</v>
+      </c>
+      <c r="C32">
+        <v>347.9506059448206</v>
+      </c>
+      <c r="D32">
+        <v>1748.675509707624</v>
+      </c>
+      <c r="E32">
+        <v>-1326.991442113207</v>
+      </c>
+      <c r="F32">
+        <v>1449.124903762803</v>
+      </c>
+      <c r="G32">
+        <v>48.4</v>
+      </c>
+      <c r="H32">
+        <v>2054.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K32">
+        <v>393.9</v>
+      </c>
+      <c r="L32">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M32">
+        <v>346.0510270185574</v>
+      </c>
+      <c r="N32">
+        <v>-236.9510270185573</v>
+      </c>
+      <c r="O32">
+        <v>-61.1333649707878</v>
+      </c>
+      <c r="P32">
+        <v>-175.8176620477695</v>
+      </c>
+      <c r="Q32">
+        <v>218.0823379522304</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09630384333043543</v>
+      </c>
+      <c r="T32">
+        <v>1.25008355066164</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.08134002734368581</v>
+      </c>
+      <c r="W32">
+        <v>0.2193760014703278</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.3152714238127358</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1352254907724031</v>
+      </c>
+      <c r="C33">
+        <v>263.3764583625662</v>
+      </c>
+      <c r="D33">
+        <v>1712.405525584129</v>
+      </c>
+      <c r="E33">
+        <v>-1278.687278654447</v>
+      </c>
+      <c r="F33">
+        <v>1497.429067221563</v>
+      </c>
+      <c r="G33">
+        <v>48.4</v>
+      </c>
+      <c r="H33">
+        <v>2054.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K33">
+        <v>393.9</v>
+      </c>
+      <c r="L33">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M33">
+        <v>357.5860612525093</v>
+      </c>
+      <c r="N33">
+        <v>-248.4860612525092</v>
+      </c>
+      <c r="O33">
+        <v>-64.10940380314737</v>
+      </c>
+      <c r="P33">
+        <v>-184.3766574493619</v>
+      </c>
+      <c r="Q33">
+        <v>209.5233425506381</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09713723236420986</v>
+      </c>
+      <c r="T33">
+        <v>1.26820070356978</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.07871615549388951</v>
+      </c>
+      <c r="W33">
+        <v>0.2200025820680592</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.3051013778832927</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1372254907724031</v>
+      </c>
+      <c r="C34">
+        <v>180.2763185333376</v>
+      </c>
+      <c r="D34">
+        <v>1677.609549213661</v>
+      </c>
+      <c r="E34">
+        <v>-1230.383115195686</v>
+      </c>
+      <c r="F34">
+        <v>1545.733230680323</v>
+      </c>
+      <c r="G34">
+        <v>48.4</v>
+      </c>
+      <c r="H34">
+        <v>2054.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K34">
+        <v>393.9</v>
+      </c>
+      <c r="L34">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M34">
+        <v>369.1210954864613</v>
+      </c>
+      <c r="N34">
+        <v>-260.0210954864612</v>
+      </c>
+      <c r="O34">
+        <v>-67.08544263550699</v>
+      </c>
+      <c r="P34">
+        <v>-192.9356528509542</v>
+      </c>
+      <c r="Q34">
+        <v>200.9643471490458</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09799513284015413</v>
+      </c>
+      <c r="T34">
+        <v>1.286850713916394</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.07625627563470544</v>
+      </c>
+      <c r="W34">
+        <v>0.2205900013784324</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2955669598244397</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1392254907724031</v>
+      </c>
+      <c r="C35">
+        <v>98.56212070360948</v>
+      </c>
+      <c r="D35">
+        <v>1644.199514842693</v>
+      </c>
+      <c r="E35">
+        <v>-1182.078951736926</v>
+      </c>
+      <c r="F35">
+        <v>1594.037394139084</v>
+      </c>
+      <c r="G35">
+        <v>48.4</v>
+      </c>
+      <c r="H35">
+        <v>2054.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K35">
+        <v>393.9</v>
+      </c>
+      <c r="L35">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M35">
+        <v>380.6561297204132</v>
+      </c>
+      <c r="N35">
+        <v>-271.5561297204131</v>
+      </c>
+      <c r="O35">
+        <v>-70.06148146786657</v>
+      </c>
+      <c r="P35">
+        <v>-201.4946482525465</v>
+      </c>
+      <c r="Q35">
+        <v>192.4053517474535</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09887864228552956</v>
+      </c>
+      <c r="T35">
+        <v>1.306057440989773</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.07394547940335075</v>
+      </c>
+      <c r="W35">
+        <v>0.2211418195184799</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2866103852843052</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1412254907724032</v>
+      </c>
+      <c r="C36">
+        <v>18.15267754458</v>
+      </c>
+      <c r="D36">
+        <v>1612.094235142423</v>
+      </c>
+      <c r="E36">
+        <v>-1133.774788278166</v>
+      </c>
+      <c r="F36">
+        <v>1642.341557597844</v>
+      </c>
+      <c r="G36">
+        <v>48.4</v>
+      </c>
+      <c r="H36">
+        <v>2054.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K36">
+        <v>393.9</v>
+      </c>
+      <c r="L36">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M36">
+        <v>392.191163954365</v>
+      </c>
+      <c r="N36">
+        <v>-283.091163954365</v>
+      </c>
+      <c r="O36">
+        <v>-73.03752030022616</v>
+      </c>
+      <c r="P36">
+        <v>-210.0536436541388</v>
+      </c>
+      <c r="Q36">
+        <v>183.8463563458612</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09978892474440121</v>
+      </c>
+      <c r="T36">
+        <v>1.325846190095679</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.07177061236207573</v>
+      </c>
+      <c r="W36">
+        <v>0.2216611777679363</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2781806680700609</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1432254907724032</v>
+      </c>
+      <c r="C37">
+        <v>-61.02697853994164</v>
+      </c>
+      <c r="D37">
+        <v>1581.218742516662</v>
+      </c>
+      <c r="E37">
+        <v>-1085.470624819406</v>
+      </c>
+      <c r="F37">
+        <v>1690.645721056604</v>
+      </c>
+      <c r="G37">
+        <v>48.4</v>
+      </c>
+      <c r="H37">
+        <v>2054.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K37">
+        <v>393.9</v>
+      </c>
+      <c r="L37">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M37">
+        <v>403.726198188317</v>
+      </c>
+      <c r="N37">
+        <v>-294.6261981883169</v>
+      </c>
+      <c r="O37">
+        <v>-76.01355913258577</v>
+      </c>
+      <c r="P37">
+        <v>-218.6126390557312</v>
+      </c>
+      <c r="Q37">
+        <v>175.2873609442688</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1007272158943151</v>
+      </c>
+      <c r="T37">
+        <v>1.346243823789458</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.06972002343744499</v>
+      </c>
+      <c r="W37">
+        <v>0.2221508584031381</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2702326489823449</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1452254907724032</v>
+      </c>
+      <c r="C38">
+        <v>-139.0461798348567</v>
+      </c>
+      <c r="D38">
+        <v>1551.503704680507</v>
+      </c>
+      <c r="E38">
+        <v>-1037.166461360646</v>
+      </c>
+      <c r="F38">
+        <v>1738.949884515364</v>
+      </c>
+      <c r="G38">
+        <v>48.4</v>
+      </c>
+      <c r="H38">
+        <v>2054.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K38">
+        <v>393.9</v>
+      </c>
+      <c r="L38">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M38">
+        <v>415.2612324222688</v>
+      </c>
+      <c r="N38">
+        <v>-306.1612324222688</v>
+      </c>
+      <c r="O38">
+        <v>-78.98959796494535</v>
+      </c>
+      <c r="P38">
+        <v>-227.1716344573234</v>
+      </c>
+      <c r="Q38">
+        <v>166.7283655426766</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1016948286426638</v>
+      </c>
+      <c r="T38">
+        <v>1.367278883536169</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.06778335611973819</v>
+      </c>
+      <c r="W38">
+        <v>0.2226133345586065</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2627261865106132</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1472254907724032</v>
+      </c>
+      <c r="C39">
+        <v>-215.9691430542241</v>
+      </c>
+      <c r="D39">
+        <v>1522.8849049199</v>
+      </c>
+      <c r="E39">
+        <v>-988.862297901886</v>
+      </c>
+      <c r="F39">
+        <v>1787.254047974124</v>
+      </c>
+      <c r="G39">
+        <v>48.4</v>
+      </c>
+      <c r="H39">
+        <v>2054.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K39">
+        <v>393.9</v>
+      </c>
+      <c r="L39">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M39">
+        <v>426.7962666562208</v>
+      </c>
+      <c r="N39">
+        <v>-317.6962666562207</v>
+      </c>
+      <c r="O39">
+        <v>-81.96563679730494</v>
+      </c>
+      <c r="P39">
+        <v>-235.7306298589158</v>
+      </c>
+      <c r="Q39">
+        <v>158.1693701410842</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1026931592560394</v>
+      </c>
+      <c r="T39">
+        <v>1.388981722957378</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.06595137352190743</v>
+      </c>
+      <c r="W39">
+        <v>0.2230508120029685</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2556254787670831</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1492254907724032</v>
+      </c>
+      <c r="C40">
+        <v>-291.8554326012211</v>
+      </c>
+      <c r="D40">
+        <v>1495.302778831663</v>
+      </c>
+      <c r="E40">
+        <v>-940.5581344431257</v>
+      </c>
+      <c r="F40">
+        <v>1835.558211432884</v>
+      </c>
+      <c r="G40">
+        <v>48.4</v>
+      </c>
+      <c r="H40">
+        <v>2054.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K40">
+        <v>393.9</v>
+      </c>
+      <c r="L40">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M40">
+        <v>438.3313008901727</v>
+      </c>
+      <c r="N40">
+        <v>-329.2313008901726</v>
+      </c>
+      <c r="O40">
+        <v>-84.94167562966454</v>
+      </c>
+      <c r="P40">
+        <v>-244.2896252605081</v>
+      </c>
+      <c r="Q40">
+        <v>149.6103747394919</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1037236940827497</v>
+      </c>
+      <c r="T40">
+        <v>1.411384653972819</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.0642158110608046</v>
+      </c>
+      <c r="W40">
+        <v>0.2234652643186799</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2488984924837387</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1512254907724032</v>
+      </c>
+      <c r="C41">
+        <v>-366.7603743809543</v>
+      </c>
+      <c r="D41">
+        <v>1468.70200051069</v>
+      </c>
+      <c r="E41">
+        <v>-892.2539709843657</v>
+      </c>
+      <c r="F41">
+        <v>1883.862374891644</v>
+      </c>
+      <c r="G41">
+        <v>48.4</v>
+      </c>
+      <c r="H41">
+        <v>2054.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K41">
+        <v>393.9</v>
+      </c>
+      <c r="L41">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M41">
+        <v>449.8663351241246</v>
+      </c>
+      <c r="N41">
+        <v>-340.7663351241246</v>
+      </c>
+      <c r="O41">
+        <v>-87.91771446202414</v>
+      </c>
+      <c r="P41">
+        <v>-252.8486206621004</v>
+      </c>
+      <c r="Q41">
+        <v>141.0513793378996</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1047880169365653</v>
+      </c>
+      <c r="T41">
+        <v>1.434522107316636</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.06256925180283525</v>
+      </c>
+      <c r="W41">
+        <v>0.2238584626694829</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2425164798559506</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1532254907724032</v>
+      </c>
+      <c r="C42">
+        <v>-440.7354262160113</v>
+      </c>
+      <c r="D42">
+        <v>1443.031112134393</v>
+      </c>
+      <c r="E42">
+        <v>-843.9498075256056</v>
+      </c>
+      <c r="F42">
+        <v>1932.166538350404</v>
+      </c>
+      <c r="G42">
+        <v>48.4</v>
+      </c>
+      <c r="H42">
+        <v>2054.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K42">
+        <v>393.9</v>
+      </c>
+      <c r="L42">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M42">
+        <v>461.4013693580765</v>
+      </c>
+      <c r="N42">
+        <v>-352.3013693580764</v>
+      </c>
+      <c r="O42">
+        <v>-90.89375329438373</v>
+      </c>
+      <c r="P42">
+        <v>-261.4076160636927</v>
+      </c>
+      <c r="Q42">
+        <v>132.4923839363072</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1058878172188413</v>
+      </c>
+      <c r="T42">
+        <v>1.458430809105246</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06100502050776437</v>
+      </c>
+      <c r="W42">
+        <v>0.2242320011027459</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2364535678595518</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1552254907724032</v>
+      </c>
+      <c r="C43">
+        <v>-513.8285100831954</v>
+      </c>
+      <c r="D43">
+        <v>1418.242191725969</v>
+      </c>
+      <c r="E43">
+        <v>-795.6456440668453</v>
+      </c>
+      <c r="F43">
+        <v>1980.470701809164</v>
+      </c>
+      <c r="G43">
+        <v>48.4</v>
+      </c>
+      <c r="H43">
+        <v>2054.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K43">
+        <v>393.9</v>
+      </c>
+      <c r="L43">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M43">
+        <v>472.9364035920285</v>
+      </c>
+      <c r="N43">
+        <v>-363.8364035920284</v>
+      </c>
+      <c r="O43">
+        <v>-93.86979212674333</v>
+      </c>
+      <c r="P43">
+        <v>-269.9666114652851</v>
+      </c>
+      <c r="Q43">
+        <v>123.9333885347149</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1070248988666183</v>
+      </c>
+      <c r="T43">
+        <v>1.483149975361268</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.0595170931783067</v>
+      </c>
+      <c r="W43">
+        <v>0.2245873181490204</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2306864076678554</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1572254907724032</v>
+      </c>
+      <c r="C44">
+        <v>-586.0843106848681</v>
+      </c>
+      <c r="D44">
+        <v>1394.290554583056</v>
+      </c>
+      <c r="E44">
+        <v>-747.3414806080855</v>
+      </c>
+      <c r="F44">
+        <v>2028.774865267924</v>
+      </c>
+      <c r="G44">
+        <v>48.4</v>
+      </c>
+      <c r="H44">
+        <v>2054.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K44">
+        <v>393.9</v>
+      </c>
+      <c r="L44">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M44">
+        <v>484.4714378259803</v>
+      </c>
+      <c r="N44">
+        <v>-375.3714378259803</v>
+      </c>
+      <c r="O44">
+        <v>-96.84583095910291</v>
+      </c>
+      <c r="P44">
+        <v>-278.5256068668774</v>
+      </c>
+      <c r="Q44">
+        <v>115.3743931331226</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1082011902263876</v>
+      </c>
+      <c r="T44">
+        <v>1.5087215266606</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.05810001953120417</v>
+      </c>
+      <c r="W44">
+        <v>0.2249257153359485</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2251938741519541</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1592254907724032</v>
+      </c>
+      <c r="C45">
+        <v>-657.5445442686519</v>
+      </c>
+      <c r="D45">
+        <v>1371.134484458033</v>
+      </c>
+      <c r="E45">
+        <v>-699.0373171493252</v>
+      </c>
+      <c r="F45">
+        <v>2077.079028726685</v>
+      </c>
+      <c r="G45">
+        <v>48.4</v>
+      </c>
+      <c r="H45">
+        <v>2054.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K45">
+        <v>393.9</v>
+      </c>
+      <c r="L45">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M45">
+        <v>496.0064720599323</v>
+      </c>
+      <c r="N45">
+        <v>-386.9064720599322</v>
+      </c>
+      <c r="O45">
+        <v>-99.82186979146252</v>
+      </c>
+      <c r="P45">
+        <v>-287.0846022684697</v>
+      </c>
+      <c r="Q45">
+        <v>106.8153977315303</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1094187549672014</v>
+      </c>
+      <c r="T45">
+        <v>1.535190325373944</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.05674885628629243</v>
+      </c>
+      <c r="W45">
+        <v>0.2252483731188334</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2199568073112109</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1612254907724031</v>
+      </c>
+      <c r="C46">
+        <v>-728.2482010977433</v>
+      </c>
+      <c r="D46">
+        <v>1348.734991087701</v>
+      </c>
+      <c r="E46">
+        <v>-650.7331536905654</v>
+      </c>
+      <c r="F46">
+        <v>2125.383192185444</v>
+      </c>
+      <c r="G46">
+        <v>48.4</v>
+      </c>
+      <c r="H46">
+        <v>2054.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K46">
+        <v>393.9</v>
+      </c>
+      <c r="L46">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M46">
+        <v>507.5415062938841</v>
+      </c>
+      <c r="N46">
+        <v>-398.4415062938841</v>
+      </c>
+      <c r="O46">
+        <v>-102.7979086238221</v>
+      </c>
+      <c r="P46">
+        <v>-295.643597670062</v>
+      </c>
+      <c r="Q46">
+        <v>98.256402329938</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1106798041630443</v>
+      </c>
+      <c r="T46">
+        <v>1.56260443832705</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.05545910955251307</v>
+      </c>
+      <c r="W46">
+        <v>0.2255563646388599</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2149577889632289</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1632254907724032</v>
+      </c>
+      <c r="C47">
+        <v>-798.2317645366054</v>
+      </c>
+      <c r="D47">
+        <v>1327.055591107599</v>
+      </c>
+      <c r="E47">
+        <v>-602.4289902318051</v>
+      </c>
+      <c r="F47">
+        <v>2173.687355644205</v>
+      </c>
+      <c r="G47">
+        <v>48.4</v>
+      </c>
+      <c r="H47">
+        <v>2054.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K47">
+        <v>393.9</v>
+      </c>
+      <c r="L47">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M47">
+        <v>519.0765405278361</v>
+      </c>
+      <c r="N47">
+        <v>-409.976540527836</v>
+      </c>
+      <c r="O47">
+        <v>-105.7739474561817</v>
+      </c>
+      <c r="P47">
+        <v>-304.2025930716543</v>
+      </c>
+      <c r="Q47">
+        <v>89.69740692834569</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1119867096932814</v>
+      </c>
+      <c r="T47">
+        <v>1.591015428114814</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05422668489579055</v>
+      </c>
+      <c r="W47">
+        <v>0.2258506676468852</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2101809492084905</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1652254907724032</v>
+      </c>
+      <c r="C48">
+        <v>-867.5294093415703</v>
+      </c>
+      <c r="D48">
+        <v>1306.062109761395</v>
+      </c>
+      <c r="E48">
+        <v>-554.1248267730448</v>
+      </c>
+      <c r="F48">
+        <v>2221.991519102965</v>
+      </c>
+      <c r="G48">
+        <v>48.4</v>
+      </c>
+      <c r="H48">
+        <v>2054.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K48">
+        <v>393.9</v>
+      </c>
+      <c r="L48">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M48">
+        <v>530.611574761788</v>
+      </c>
+      <c r="N48">
+        <v>-421.5115747617879</v>
+      </c>
+      <c r="O48">
+        <v>-108.7499862885413</v>
+      </c>
+      <c r="P48">
+        <v>-312.7615884732467</v>
+      </c>
+      <c r="Q48">
+        <v>81.13841152675332</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1133420191320459</v>
+      </c>
+      <c r="T48">
+        <v>1.620478676783607</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.0530478439197951</v>
+      </c>
+      <c r="W48">
+        <v>0.2261321748719529</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2056117981387408</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1672254907724032</v>
+      </c>
+      <c r="C49">
+        <v>-936.1731814232949</v>
+      </c>
+      <c r="D49">
+        <v>1285.72250113843</v>
+      </c>
+      <c r="E49">
+        <v>-505.8206633142845</v>
+      </c>
+      <c r="F49">
+        <v>2270.295682561725</v>
+      </c>
+      <c r="G49">
+        <v>48.4</v>
+      </c>
+      <c r="H49">
+        <v>2054.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K49">
+        <v>393.9</v>
+      </c>
+      <c r="L49">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M49">
+        <v>542.1466089957401</v>
+      </c>
+      <c r="N49">
+        <v>-433.04660899574</v>
+      </c>
+      <c r="O49">
+        <v>-111.7260251209009</v>
+      </c>
+      <c r="P49">
+        <v>-321.320583874839</v>
+      </c>
+      <c r="Q49">
+        <v>72.57941612516095</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1147484723232166</v>
+      </c>
+      <c r="T49">
+        <v>1.651053746156883</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05191916638958669</v>
+      </c>
+      <c r="W49">
+        <v>0.2264017030661667</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2012370790294058</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1692254907724031</v>
+      </c>
+      <c r="C50">
+        <v>-1004.193161069889</v>
+      </c>
+      <c r="D50">
+        <v>1266.006684950596</v>
+      </c>
+      <c r="E50">
+        <v>-457.5164998555247</v>
+      </c>
+      <c r="F50">
+        <v>2318.599846020485</v>
+      </c>
+      <c r="G50">
+        <v>48.4</v>
+      </c>
+      <c r="H50">
+        <v>2054.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K50">
+        <v>393.9</v>
+      </c>
+      <c r="L50">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M50">
+        <v>553.6816432296919</v>
+      </c>
+      <c r="N50">
+        <v>-444.5816432296918</v>
+      </c>
+      <c r="O50">
+        <v>-114.7020639532605</v>
+      </c>
+      <c r="P50">
+        <v>-329.8795792764313</v>
+      </c>
+      <c r="Q50">
+        <v>64.02042072356869</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1162090198678939</v>
+      </c>
+      <c r="T50">
+        <v>1.682804779736823</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05083751708980364</v>
+      </c>
+      <c r="W50">
+        <v>0.2266600009189549</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1970446398829598</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1712254907724031</v>
+      </c>
+      <c r="C51">
+        <v>-1071.61761137926</v>
+      </c>
+      <c r="D51">
+        <v>1246.886398099985</v>
+      </c>
+      <c r="E51">
+        <v>-409.2123363967648</v>
+      </c>
+      <c r="F51">
+        <v>2366.904009479245</v>
+      </c>
+      <c r="G51">
+        <v>48.4</v>
+      </c>
+      <c r="H51">
+        <v>2054.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K51">
+        <v>393.9</v>
+      </c>
+      <c r="L51">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M51">
+        <v>565.2166774636437</v>
+      </c>
+      <c r="N51">
+        <v>-456.1166774636436</v>
+      </c>
+      <c r="O51">
+        <v>-117.6781027856201</v>
+      </c>
+      <c r="P51">
+        <v>-338.4385746780235</v>
+      </c>
+      <c r="Q51">
+        <v>55.46142532197644</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1177268437868721</v>
+      </c>
+      <c r="T51">
+        <v>1.715800951888525</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.04980001674103214</v>
+      </c>
+      <c r="W51">
+        <v>0.2269077560022415</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1930233207016749</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1732254907724032</v>
+      </c>
+      <c r="C52">
+        <v>-1138.473113441069</v>
+      </c>
+      <c r="D52">
+        <v>1228.335059496936</v>
+      </c>
+      <c r="E52">
+        <v>-360.9081729380046</v>
+      </c>
+      <c r="F52">
+        <v>2415.208172938005</v>
+      </c>
+      <c r="G52">
+        <v>48.4</v>
+      </c>
+      <c r="H52">
+        <v>2054.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K52">
+        <v>393.9</v>
+      </c>
+      <c r="L52">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M52">
+        <v>576.7517116975956</v>
+      </c>
+      <c r="N52">
+        <v>-467.6517116975955</v>
+      </c>
+      <c r="O52">
+        <v>-120.6541416179796</v>
+      </c>
+      <c r="P52">
+        <v>-346.9975700796159</v>
+      </c>
+      <c r="Q52">
+        <v>46.90242992038407</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1193053806626096</v>
+      </c>
+      <c r="T52">
+        <v>1.750116970926296</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.0488040164062115</v>
+      </c>
+      <c r="W52">
+        <v>0.2271456008821967</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1891628542876415</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1752254907724032</v>
+      </c>
+      <c r="C53">
+        <v>-1204.784689628088</v>
+      </c>
+      <c r="D53">
+        <v>1210.327646768677</v>
+      </c>
+      <c r="E53">
+        <v>-312.6040094792443</v>
+      </c>
+      <c r="F53">
+        <v>2463.512336396765</v>
+      </c>
+      <c r="G53">
+        <v>48.4</v>
+      </c>
+      <c r="H53">
+        <v>2054.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K53">
+        <v>393.9</v>
+      </c>
+      <c r="L53">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M53">
+        <v>588.2867459315477</v>
+      </c>
+      <c r="N53">
+        <v>-479.1867459315476</v>
+      </c>
+      <c r="O53">
+        <v>-123.6301804503393</v>
+      </c>
+      <c r="P53">
+        <v>-355.5565654812083</v>
+      </c>
+      <c r="Q53">
+        <v>38.3434345187917</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1209483476149078</v>
+      </c>
+      <c r="T53">
+        <v>1.785833643802343</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04784707490805048</v>
+      </c>
+      <c r="W53">
+        <v>0.2273741185119575</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.185453778713374</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1772254907724032</v>
+      </c>
+      <c r="C54">
+        <v>-1270.575916199504</v>
+      </c>
+      <c r="D54">
+        <v>1192.840583656021</v>
+      </c>
+      <c r="E54">
+        <v>-264.2998460204844</v>
+      </c>
+      <c r="F54">
+        <v>2511.816499855525</v>
+      </c>
+      <c r="G54">
+        <v>48.4</v>
+      </c>
+      <c r="H54">
+        <v>2054.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K54">
+        <v>393.9</v>
+      </c>
+      <c r="L54">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M54">
+        <v>599.8217801654995</v>
+      </c>
+      <c r="N54">
+        <v>-490.7217801654994</v>
+      </c>
+      <c r="O54">
+        <v>-126.6062192826988</v>
+      </c>
+      <c r="P54">
+        <v>-364.1155608828005</v>
+      </c>
+      <c r="Q54">
+        <v>29.78443911719944</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1226597715235517</v>
+      </c>
+      <c r="T54">
+        <v>1.823038511381558</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.04692693885212644</v>
+      </c>
+      <c r="W54">
+        <v>0.2275938470021122</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1818873598919629</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1792254907724032</v>
+      </c>
+      <c r="C55">
+        <v>-1335.86902628177</v>
+      </c>
+      <c r="D55">
+        <v>1175.851637032515</v>
+      </c>
+      <c r="E55">
+        <v>-215.9956825617242</v>
+      </c>
+      <c r="F55">
+        <v>2560.120663314286</v>
+      </c>
+      <c r="G55">
+        <v>48.4</v>
+      </c>
+      <c r="H55">
+        <v>2054.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K55">
+        <v>393.9</v>
+      </c>
+      <c r="L55">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M55">
+        <v>611.3568143994514</v>
+      </c>
+      <c r="N55">
+        <v>-502.2568143994513</v>
+      </c>
+      <c r="O55">
+        <v>-129.5822581150584</v>
+      </c>
+      <c r="P55">
+        <v>-372.6745562843929</v>
+      </c>
+      <c r="Q55">
+        <v>21.22544371560707</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1244440219814996</v>
+      </c>
+      <c r="T55">
+        <v>1.861826564815208</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04604152491152028</v>
+      </c>
+      <c r="W55">
+        <v>0.227805283851129</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1784555229128693</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1812254907724032</v>
+      </c>
+      <c r="C56">
+        <v>-1400.685004172843</v>
+      </c>
+      <c r="D56">
+        <v>1159.339822600202</v>
+      </c>
+      <c r="E56">
+        <v>-167.6915191029639</v>
+      </c>
+      <c r="F56">
+        <v>2608.424826773046</v>
+      </c>
+      <c r="G56">
+        <v>48.4</v>
+      </c>
+      <c r="H56">
+        <v>2054.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K56">
+        <v>393.9</v>
+      </c>
+      <c r="L56">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M56">
+        <v>622.8918486334034</v>
+      </c>
+      <c r="N56">
+        <v>-513.7918486334033</v>
+      </c>
+      <c r="O56">
+        <v>-132.5582969474181</v>
+      </c>
+      <c r="P56">
+        <v>-381.2335516859853</v>
+      </c>
+      <c r="Q56">
+        <v>12.6664483140147</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1263058485463148</v>
+      </c>
+      <c r="T56">
+        <v>1.90230105535467</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.04518890407982545</v>
+      </c>
+      <c r="W56">
+        <v>0.2280088897057377</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1751507910070753</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1832254907724032</v>
+      </c>
+      <c r="C57">
+        <v>-1465.043671810886</v>
+      </c>
+      <c r="D57">
+        <v>1143.28531842092</v>
+      </c>
+      <c r="E57">
+        <v>-119.387355644204</v>
+      </c>
+      <c r="F57">
+        <v>2656.728990231806</v>
+      </c>
+      <c r="G57">
+        <v>48.4</v>
+      </c>
+      <c r="H57">
+        <v>2054.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K57">
+        <v>393.9</v>
+      </c>
+      <c r="L57">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M57">
+        <v>634.4268828673553</v>
+      </c>
+      <c r="N57">
+        <v>-525.3268828673552</v>
+      </c>
+      <c r="O57">
+        <v>-135.5343357797776</v>
+      </c>
+      <c r="P57">
+        <v>-389.7925470875775</v>
+      </c>
+      <c r="Q57">
+        <v>4.107452912422445</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1282504229584551</v>
+      </c>
+      <c r="T57">
+        <v>1.944574412140329</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04436728764201045</v>
+      </c>
+      <c r="W57">
+        <v>0.2282050917110879</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1719662311705832</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1852254907724032</v>
+      </c>
+      <c r="C58">
+        <v>-1528.963768156605</v>
+      </c>
+      <c r="D58">
+        <v>1127.669385533961</v>
+      </c>
+      <c r="E58">
+        <v>-71.08319218544375</v>
+      </c>
+      <c r="F58">
+        <v>2705.033153690566</v>
+      </c>
+      <c r="G58">
+        <v>48.4</v>
+      </c>
+      <c r="H58">
+        <v>2054.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K58">
+        <v>393.9</v>
+      </c>
+      <c r="L58">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M58">
+        <v>645.9619171013072</v>
+      </c>
+      <c r="N58">
+        <v>-536.8619171013072</v>
+      </c>
+      <c r="O58">
+        <v>-138.5103746121373</v>
+      </c>
+      <c r="P58">
+        <v>-398.3515424891699</v>
+      </c>
+      <c r="Q58">
+        <v>-4.451542489169924</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1302833871166018</v>
+      </c>
+      <c r="T58">
+        <v>1.988769285143518</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04357501464840312</v>
+      </c>
+      <c r="W58">
+        <v>0.2283942865019614</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1688954056139654</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1872254907724032</v>
+      </c>
+      <c r="C59">
+        <v>-1592.463022157638</v>
+      </c>
+      <c r="D59">
+        <v>1112.474294991689</v>
+      </c>
+      <c r="E59">
+        <v>-22.77902872668346</v>
+      </c>
+      <c r="F59">
+        <v>2753.337317149326</v>
+      </c>
+      <c r="G59">
+        <v>48.4</v>
+      </c>
+      <c r="H59">
+        <v>2054.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K59">
+        <v>393.9</v>
+      </c>
+      <c r="L59">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M59">
+        <v>657.4969513352592</v>
+      </c>
+      <c r="N59">
+        <v>-548.396951335259</v>
+      </c>
+      <c r="O59">
+        <v>-141.4864134444968</v>
+      </c>
+      <c r="P59">
+        <v>-406.9105378907622</v>
+      </c>
+      <c r="Q59">
+        <v>-13.01053789076218</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1324109077472205</v>
+      </c>
+      <c r="T59">
+        <v>2.035019733635228</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04281054070720306</v>
+      </c>
+      <c r="W59">
+        <v>0.2285768428791199</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1659323283224926</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1892254907724032</v>
+      </c>
+      <c r="C60">
+        <v>-1655.558219892295</v>
+      </c>
+      <c r="D60">
+        <v>1097.683260715791</v>
+      </c>
+      <c r="E60">
+        <v>25.52513473207591</v>
+      </c>
+      <c r="F60">
+        <v>2801.641480608086</v>
+      </c>
+      <c r="G60">
+        <v>48.4</v>
+      </c>
+      <c r="H60">
+        <v>2054.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K60">
+        <v>393.9</v>
+      </c>
+      <c r="L60">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M60">
+        <v>669.0319855692109</v>
+      </c>
+      <c r="N60">
+        <v>-559.9319855692108</v>
+      </c>
+      <c r="O60">
+        <v>-144.4624522768564</v>
+      </c>
+      <c r="P60">
+        <v>-415.4695332923544</v>
+      </c>
+      <c r="Q60">
+        <v>-21.56953329235444</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1346397388840591</v>
+      </c>
+      <c r="T60">
+        <v>2.083472584436066</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04207242793638923</v>
+      </c>
+      <c r="W60">
+        <v>0.2287531042087903</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1630714261100357</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1912254907724032</v>
+      </c>
+      <c r="C61">
+        <v>-1718.265266427283</v>
+      </c>
+      <c r="D61">
+        <v>1083.280377639563</v>
+      </c>
+      <c r="E61">
+        <v>73.8292981908362</v>
+      </c>
+      <c r="F61">
+        <v>2849.945644066846</v>
+      </c>
+      <c r="G61">
+        <v>48.4</v>
+      </c>
+      <c r="H61">
+        <v>2054.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K61">
+        <v>393.9</v>
+      </c>
+      <c r="L61">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M61">
+        <v>680.5670198031628</v>
+      </c>
+      <c r="N61">
+        <v>-571.4670198031627</v>
+      </c>
+      <c r="O61">
+        <v>-147.438491109216</v>
+      </c>
+      <c r="P61">
+        <v>-424.0285286939467</v>
+      </c>
+      <c r="Q61">
+        <v>-30.12852869394669</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1369772934909873</v>
+      </c>
+      <c r="T61">
+        <v>2.134288988934507</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04135933593746737</v>
+      </c>
+      <c r="W61">
+        <v>0.2289233905781328</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1603075036335946</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1932254907724032</v>
+      </c>
+      <c r="C62">
+        <v>-1780.599242868618</v>
+      </c>
+      <c r="D62">
+        <v>1069.250564656988</v>
+      </c>
+      <c r="E62">
+        <v>122.1334616495965</v>
+      </c>
+      <c r="F62">
+        <v>2898.249807525606</v>
+      </c>
+      <c r="G62">
+        <v>48.4</v>
+      </c>
+      <c r="H62">
+        <v>2054.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K62">
+        <v>393.9</v>
+      </c>
+      <c r="L62">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M62">
+        <v>692.1020540371148</v>
+      </c>
+      <c r="N62">
+        <v>-583.0020540371147</v>
+      </c>
+      <c r="O62">
+        <v>-150.4145299415756</v>
+      </c>
+      <c r="P62">
+        <v>-432.5875240955391</v>
+      </c>
+      <c r="Q62">
+        <v>-38.68752409553912</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.139431725828262</v>
+      </c>
+      <c r="T62">
+        <v>2.18764621365787</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04067001367184291</v>
+      </c>
+      <c r="W62">
+        <v>0.2290880007351639</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1576357119063679</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1952254907724031</v>
+      </c>
+      <c r="C63">
+        <v>-1842.574459035951</v>
+      </c>
+      <c r="D63">
+        <v>1055.579511948415</v>
+      </c>
+      <c r="E63">
+        <v>170.4376251083563</v>
+      </c>
+      <c r="F63">
+        <v>2946.553970984366</v>
+      </c>
+      <c r="G63">
+        <v>48.4</v>
+      </c>
+      <c r="H63">
+        <v>2054.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K63">
+        <v>393.9</v>
+      </c>
+      <c r="L63">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M63">
+        <v>703.6370882710667</v>
+      </c>
+      <c r="N63">
+        <v>-594.5370882710665</v>
+      </c>
+      <c r="O63">
+        <v>-153.3905687739352</v>
+      </c>
+      <c r="P63">
+        <v>-441.1465194971314</v>
+      </c>
+      <c r="Q63">
+        <v>-47.24651949713137</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1420120264905251</v>
+      </c>
+      <c r="T63">
+        <v>2.243739706315763</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04000329213623893</v>
+      </c>
+      <c r="W63">
+        <v>0.2292472138378661</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1550515199079029</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1972254907724031</v>
+      </c>
+      <c r="C64">
+        <v>-1904.204502147057</v>
+      </c>
+      <c r="D64">
+        <v>1042.253632296069</v>
+      </c>
+      <c r="E64">
+        <v>218.7417885671166</v>
+      </c>
+      <c r="F64">
+        <v>2994.858134443126</v>
+      </c>
+      <c r="G64">
+        <v>48.4</v>
+      </c>
+      <c r="H64">
+        <v>2054.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K64">
+        <v>393.9</v>
+      </c>
+      <c r="L64">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M64">
+        <v>715.1721225050186</v>
+      </c>
+      <c r="N64">
+        <v>-606.0721225050186</v>
+      </c>
+      <c r="O64">
+        <v>-156.3666076062948</v>
+      </c>
+      <c r="P64">
+        <v>-449.7055148987238</v>
+      </c>
+      <c r="Q64">
+        <v>-55.8055148987238</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1447281324508021</v>
+      </c>
+      <c r="T64">
+        <v>2.302785488060915</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03935807774694475</v>
+      </c>
+      <c r="W64">
+        <v>0.2294012910340296</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1525506889416463</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1992254907724032</v>
+      </c>
+      <c r="C65">
+        <v>-1965.502281860665</v>
+      </c>
+      <c r="D65">
+        <v>1029.260016041222</v>
+      </c>
+      <c r="E65">
+        <v>267.0459520258769</v>
+      </c>
+      <c r="F65">
+        <v>3043.162297901887</v>
+      </c>
+      <c r="G65">
+        <v>48.4</v>
+      </c>
+      <c r="H65">
+        <v>2054.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K65">
+        <v>393.9</v>
+      </c>
+      <c r="L65">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M65">
+        <v>726.7071567389705</v>
+      </c>
+      <c r="N65">
+        <v>-617.6071567389704</v>
+      </c>
+      <c r="O65">
+        <v>-159.3426464386544</v>
+      </c>
+      <c r="P65">
+        <v>-458.264510300316</v>
+      </c>
+      <c r="Q65">
+        <v>-64.36451030031606</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1475910549494724</v>
+      </c>
+      <c r="T65">
+        <v>2.365022933684183</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.0387333463541361</v>
+      </c>
+      <c r="W65">
+        <v>0.2295504768906323</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1501292494346361</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2012254907724032</v>
+      </c>
+      <c r="C66">
+        <v>-2026.480071991527</v>
+      </c>
+      <c r="D66">
+        <v>1016.58638936912</v>
+      </c>
+      <c r="E66">
+        <v>315.3501154846372</v>
+      </c>
+      <c r="F66">
+        <v>3091.466461360647</v>
+      </c>
+      <c r="G66">
+        <v>48.4</v>
+      </c>
+      <c r="H66">
+        <v>2054.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K66">
+        <v>393.9</v>
+      </c>
+      <c r="L66">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M66">
+        <v>738.2421909729226</v>
+      </c>
+      <c r="N66">
+        <v>-629.1421909729224</v>
+      </c>
+      <c r="O66">
+        <v>-162.318685271014</v>
+      </c>
+      <c r="P66">
+        <v>-466.8235057019084</v>
+      </c>
+      <c r="Q66">
+        <v>-72.92350570190843</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1506130286980689</v>
+      </c>
+      <c r="T66">
+        <v>2.430718015175411</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03812813781735272</v>
+      </c>
+      <c r="W66">
+        <v>0.2296950006892162</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.14778347991222</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2032254907724032</v>
+      </c>
+      <c r="C67">
+        <v>-2087.149549181067</v>
+      </c>
+      <c r="D67">
+        <v>1004.221075638339</v>
+      </c>
+      <c r="E67">
+        <v>363.654278943397</v>
+      </c>
+      <c r="F67">
+        <v>3139.770624819407</v>
+      </c>
+      <c r="G67">
+        <v>48.4</v>
+      </c>
+      <c r="H67">
+        <v>2054.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K67">
+        <v>393.9</v>
+      </c>
+      <c r="L67">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M67">
+        <v>749.7772252068744</v>
+      </c>
+      <c r="N67">
+        <v>-640.6772252068743</v>
+      </c>
+      <c r="O67">
+        <v>-165.2947241033736</v>
+      </c>
+      <c r="P67">
+        <v>-475.3825011035007</v>
+      </c>
+      <c r="Q67">
+        <v>-81.48250110350068</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1538076866608709</v>
+      </c>
+      <c r="T67">
+        <v>2.50016710132328</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03754155108170115</v>
+      </c>
+      <c r="W67">
+        <v>0.2298350776016898</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1455098879135704</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2052254907724032</v>
+      </c>
+      <c r="C68">
+        <v>-2147.5218287797</v>
+      </c>
+      <c r="D68">
+        <v>992.152959498467</v>
+      </c>
+      <c r="E68">
+        <v>411.9584424021573</v>
+      </c>
+      <c r="F68">
+        <v>3188.074788278167</v>
+      </c>
+      <c r="G68">
+        <v>48.4</v>
+      </c>
+      <c r="H68">
+        <v>2054.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K68">
+        <v>393.9</v>
+      </c>
+      <c r="L68">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M68">
+        <v>761.3122594408263</v>
+      </c>
+      <c r="N68">
+        <v>-652.2122594408263</v>
+      </c>
+      <c r="O68">
+        <v>-168.2707629357332</v>
+      </c>
+      <c r="P68">
+        <v>-483.9414965050931</v>
+      </c>
+      <c r="Q68">
+        <v>-90.04149650509316</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1571902656803082</v>
+      </c>
+      <c r="T68">
+        <v>2.573701427832788</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03697273970167538</v>
+      </c>
+      <c r="W68">
+        <v>0.2299709097592399</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1433051926421526</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2072254907724032</v>
+      </c>
+      <c r="C69">
+        <v>-2207.607498172609</v>
+      </c>
+      <c r="D69">
+        <v>980.3714535643185</v>
+      </c>
+      <c r="E69">
+        <v>460.2626058609176</v>
+      </c>
+      <c r="F69">
+        <v>3236.378951736927</v>
+      </c>
+      <c r="G69">
+        <v>48.4</v>
+      </c>
+      <c r="H69">
+        <v>2054.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K69">
+        <v>393.9</v>
+      </c>
+      <c r="L69">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M69">
+        <v>772.8472936747783</v>
+      </c>
+      <c r="N69">
+        <v>-663.7472936747781</v>
+      </c>
+      <c r="O69">
+        <v>-171.2468017680928</v>
+      </c>
+      <c r="P69">
+        <v>-492.5004919066854</v>
+      </c>
+      <c r="Q69">
+        <v>-98.60049190668542</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1607778494888024</v>
+      </c>
+      <c r="T69">
+        <v>2.651692380191357</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03642090776582946</v>
+      </c>
+      <c r="W69">
+        <v>0.2301026872255199</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1411663091698817</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2092254907724032</v>
+      </c>
+      <c r="C70">
+        <v>-2267.416647758984</v>
+      </c>
+      <c r="D70">
+        <v>968.8664674367028</v>
+      </c>
+      <c r="E70">
+        <v>508.5667693196774</v>
+      </c>
+      <c r="F70">
+        <v>3284.683115195687</v>
+      </c>
+      <c r="G70">
+        <v>48.4</v>
+      </c>
+      <c r="H70">
+        <v>2054.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K70">
+        <v>393.9</v>
+      </c>
+      <c r="L70">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M70">
+        <v>784.3823279087301</v>
+      </c>
+      <c r="N70">
+        <v>-675.2823279087299</v>
+      </c>
+      <c r="O70">
+        <v>-174.2228406004523</v>
+      </c>
+      <c r="P70">
+        <v>-501.0594873082777</v>
+      </c>
+      <c r="Q70">
+        <v>-107.1594873082777</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1645896572853275</v>
+      </c>
+      <c r="T70">
+        <v>2.734557767072337</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03588530618103786</v>
+      </c>
+      <c r="W70">
+        <v>0.2302305888839682</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1390903340350306</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2112254907724032</v>
+      </c>
+      <c r="C71">
+        <v>-2326.958899775261</v>
+      </c>
+      <c r="D71">
+        <v>957.6283788791868</v>
+      </c>
+      <c r="E71">
+        <v>556.8709327784377</v>
+      </c>
+      <c r="F71">
+        <v>3332.987278654447</v>
+      </c>
+      <c r="G71">
+        <v>48.4</v>
+      </c>
+      <c r="H71">
+        <v>2054.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K71">
+        <v>393.9</v>
+      </c>
+      <c r="L71">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M71">
+        <v>795.9173621426821</v>
+      </c>
+      <c r="N71">
+        <v>-686.817362142682</v>
+      </c>
+      <c r="O71">
+        <v>-177.198879432812</v>
+      </c>
+      <c r="P71">
+        <v>-509.61848270987</v>
+      </c>
+      <c r="Q71">
+        <v>-115.71848270987</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1686473881654994</v>
+      </c>
+      <c r="T71">
+        <v>2.822769307945639</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0353652292798634</v>
+      </c>
+      <c r="W71">
+        <v>0.2303547832479686</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1370745320924939</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2132254907724032</v>
+      </c>
+      <c r="C72">
+        <v>-2386.243435135382</v>
+      </c>
+      <c r="D72">
+        <v>946.6480069778256</v>
+      </c>
+      <c r="E72">
+        <v>605.175096237198</v>
+      </c>
+      <c r="F72">
+        <v>3381.291442113208</v>
+      </c>
+      <c r="G72">
+        <v>48.4</v>
+      </c>
+      <c r="H72">
+        <v>2054.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K72">
+        <v>393.9</v>
+      </c>
+      <c r="L72">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M72">
+        <v>807.4523963766341</v>
+      </c>
+      <c r="N72">
+        <v>-698.352396376634</v>
+      </c>
+      <c r="O72">
+        <v>-180.1749182651716</v>
+      </c>
+      <c r="P72">
+        <v>-518.1774781114625</v>
+      </c>
+      <c r="Q72">
+        <v>-124.2774781114625</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1729756344376827</v>
+      </c>
+      <c r="T72">
+        <v>2.916861618210493</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03486001171872249</v>
+      </c>
+      <c r="W72">
+        <v>0.2304754292015691</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1351163244911724</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2152254907724031</v>
+      </c>
+      <c r="C73">
+        <v>-2445.279018445472</v>
+      </c>
+      <c r="D73">
+        <v>935.9165871264955</v>
+      </c>
+      <c r="E73">
+        <v>653.4792596959574</v>
+      </c>
+      <c r="F73">
+        <v>3429.595605571967</v>
+      </c>
+      <c r="G73">
+        <v>48.4</v>
+      </c>
+      <c r="H73">
+        <v>2054.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K73">
+        <v>393.9</v>
+      </c>
+      <c r="L73">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M73">
+        <v>818.9874306105858</v>
+      </c>
+      <c r="N73">
+        <v>-709.8874306105856</v>
+      </c>
+      <c r="O73">
+        <v>-183.1509570975311</v>
+      </c>
+      <c r="P73">
+        <v>-526.7364735130545</v>
+      </c>
+      <c r="Q73">
+        <v>-132.8364735130546</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1776023804527752</v>
+      </c>
+      <c r="T73">
+        <v>3.017443053321199</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03436902563817711</v>
+      </c>
+      <c r="W73">
+        <v>0.2305926766776033</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1332132776673532</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2172254907724031</v>
+      </c>
+      <c r="C74">
+        <v>-2504.074021336141</v>
+      </c>
+      <c r="D74">
+        <v>925.4257476945858</v>
+      </c>
+      <c r="E74">
+        <v>701.7834231547176</v>
+      </c>
+      <c r="F74">
+        <v>3477.899769030727</v>
+      </c>
+      <c r="G74">
+        <v>48.4</v>
+      </c>
+      <c r="H74">
+        <v>2054.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K74">
+        <v>393.9</v>
+      </c>
+      <c r="L74">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M74">
+        <v>830.5224648445377</v>
+      </c>
+      <c r="N74">
+        <v>-721.4224648445377</v>
+      </c>
+      <c r="O74">
+        <v>-186.1269959298907</v>
+      </c>
+      <c r="P74">
+        <v>-535.295468914647</v>
+      </c>
+      <c r="Q74">
+        <v>-141.395468914647</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1825596083260886</v>
+      </c>
+      <c r="T74">
+        <v>3.125208876654099</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0338916780598691</v>
+      </c>
+      <c r="W74">
+        <v>0.2307066672793033</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1313630932553065</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2192254907724032</v>
+      </c>
+      <c r="C75">
+        <v>-2562.636444242975</v>
+      </c>
+      <c r="D75">
+        <v>915.167488246513</v>
+      </c>
+      <c r="E75">
+        <v>750.0875866134779</v>
+      </c>
+      <c r="F75">
+        <v>3526.203932489488</v>
+      </c>
+      <c r="G75">
+        <v>48.4</v>
+      </c>
+      <c r="H75">
+        <v>2054.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K75">
+        <v>393.9</v>
+      </c>
+      <c r="L75">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M75">
+        <v>842.0574990784897</v>
+      </c>
+      <c r="N75">
+        <v>-732.9574990784897</v>
+      </c>
+      <c r="O75">
+        <v>-189.1030347622504</v>
+      </c>
+      <c r="P75">
+        <v>-543.8544643162394</v>
+      </c>
+      <c r="Q75">
+        <v>-149.9544643162394</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1878840382640918</v>
+      </c>
+      <c r="T75">
+        <v>3.240957353567214</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03342740849740513</v>
+      </c>
+      <c r="W75">
+        <v>0.2308175348508197</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1295635988271516</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2212254907724032</v>
+      </c>
+      <c r="C76">
+        <v>-2620.973936754288</v>
+      </c>
+      <c r="D76">
+        <v>905.1341591939596</v>
+      </c>
+      <c r="E76">
+        <v>798.3917500722378</v>
+      </c>
+      <c r="F76">
+        <v>3574.508095948248</v>
+      </c>
+      <c r="G76">
+        <v>48.4</v>
+      </c>
+      <c r="H76">
+        <v>2054.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K76">
+        <v>393.9</v>
+      </c>
+      <c r="L76">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M76">
+        <v>853.5925333124416</v>
+      </c>
+      <c r="N76">
+        <v>-744.4925333124415</v>
+      </c>
+      <c r="O76">
+        <v>-192.0790735946099</v>
+      </c>
+      <c r="P76">
+        <v>-552.4134597178316</v>
+      </c>
+      <c r="Q76">
+        <v>-158.5134597178317</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1936180397357877</v>
+      </c>
+      <c r="T76">
+        <v>3.365609559473645</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03297568676095371</v>
+      </c>
+      <c r="W76">
+        <v>0.2309254060014843</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1278127393835414</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2232254907724031</v>
+      </c>
+      <c r="C77">
+        <v>-2679.093816634927</v>
+      </c>
+      <c r="D77">
+        <v>895.3184427720804</v>
+      </c>
+      <c r="E77">
+        <v>846.695913530998</v>
+      </c>
+      <c r="F77">
+        <v>3622.812259407008</v>
+      </c>
+      <c r="G77">
+        <v>48.4</v>
+      </c>
+      <c r="H77">
+        <v>2054.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K77">
+        <v>393.9</v>
+      </c>
+      <c r="L77">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M77">
+        <v>865.1275675463935</v>
+      </c>
+      <c r="N77">
+        <v>-756.0275675463934</v>
+      </c>
+      <c r="O77">
+        <v>-195.0551124269695</v>
+      </c>
+      <c r="P77">
+        <v>-560.9724551194239</v>
+      </c>
+      <c r="Q77">
+        <v>-167.0724551194239</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1998107613252192</v>
+      </c>
+      <c r="T77">
+        <v>3.500233941852591</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03253601093747433</v>
+      </c>
+      <c r="W77">
+        <v>0.2310304005881311</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1261085695250944</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2252254907724032</v>
+      </c>
+      <c r="C78">
+        <v>-2737.003087625524</v>
+      </c>
+      <c r="D78">
+        <v>885.7133352402444</v>
+      </c>
+      <c r="E78">
+        <v>895.0000769897583</v>
+      </c>
+      <c r="F78">
+        <v>3671.116422865768</v>
+      </c>
+      <c r="G78">
+        <v>48.4</v>
+      </c>
+      <c r="H78">
+        <v>2054.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K78">
+        <v>393.9</v>
+      </c>
+      <c r="L78">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M78">
+        <v>876.6626017803454</v>
+      </c>
+      <c r="N78">
+        <v>-767.5626017803454</v>
+      </c>
+      <c r="O78">
+        <v>-198.0311512593291</v>
+      </c>
+      <c r="P78">
+        <v>-569.5314505210163</v>
+      </c>
+      <c r="Q78">
+        <v>-175.6314505210163</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2065195430471033</v>
+      </c>
+      <c r="T78">
+        <v>3.646077022763116</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.0321079055304023</v>
+      </c>
+      <c r="W78">
+        <v>0.2311326321593399</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1244492462418693</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2272254907724032</v>
+      </c>
+      <c r="C79">
+        <v>-2794.708456108185</v>
+      </c>
+      <c r="D79">
+        <v>876.3121302163433</v>
+      </c>
+      <c r="E79">
+        <v>943.3042404485182</v>
+      </c>
+      <c r="F79">
+        <v>3719.420586324528</v>
+      </c>
+      <c r="G79">
+        <v>48.4</v>
+      </c>
+      <c r="H79">
+        <v>2054.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K79">
+        <v>393.9</v>
+      </c>
+      <c r="L79">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M79">
+        <v>888.1976360142974</v>
+      </c>
+      <c r="N79">
+        <v>-779.0976360142972</v>
+      </c>
+      <c r="O79">
+        <v>-201.0071900916887</v>
+      </c>
+      <c r="P79">
+        <v>-578.0904459226085</v>
+      </c>
+      <c r="Q79">
+        <v>-184.1904459226085</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2138116970926296</v>
+      </c>
+      <c r="T79">
+        <v>3.804602110709339</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03169091974429317</v>
+      </c>
+      <c r="W79">
+        <v>0.2312322083650628</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1228330222647023</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2292254907724032</v>
+      </c>
+      <c r="C80">
+        <v>-2852.216346721979</v>
+      </c>
+      <c r="D80">
+        <v>867.1084030613093</v>
+      </c>
+      <c r="E80">
+        <v>991.6084039072784</v>
+      </c>
+      <c r="F80">
+        <v>3767.724749783288</v>
+      </c>
+      <c r="G80">
+        <v>48.4</v>
+      </c>
+      <c r="H80">
+        <v>2054.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K80">
+        <v>393.9</v>
+      </c>
+      <c r="L80">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M80">
+        <v>899.7326702482493</v>
+      </c>
+      <c r="N80">
+        <v>-790.6326702482493</v>
+      </c>
+      <c r="O80">
+        <v>-203.9832289240483</v>
+      </c>
+      <c r="P80">
+        <v>-586.649441324201</v>
+      </c>
+      <c r="Q80">
+        <v>-192.749441324201</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2217667742332037</v>
+      </c>
+      <c r="T80">
+        <v>3.977538570287036</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03128462590141762</v>
+      </c>
+      <c r="W80">
+        <v>0.2313292313347415</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1212582399279752</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2312254907724032</v>
+      </c>
+      <c r="C81">
+        <v>-2909.532917004603</v>
+      </c>
+      <c r="D81">
+        <v>858.095996237445</v>
+      </c>
+      <c r="E81">
+        <v>1039.912567366039</v>
+      </c>
+      <c r="F81">
+        <v>3816.028913242048</v>
+      </c>
+      <c r="G81">
+        <v>48.4</v>
+      </c>
+      <c r="H81">
+        <v>2054.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K81">
+        <v>393.9</v>
+      </c>
+      <c r="L81">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M81">
+        <v>911.2677044822012</v>
+      </c>
+      <c r="N81">
+        <v>-802.1677044822011</v>
+      </c>
+      <c r="O81">
+        <v>-206.9592677564079</v>
+      </c>
+      <c r="P81">
+        <v>-595.2084367257933</v>
+      </c>
+      <c r="Q81">
+        <v>-201.3084367257933</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2304794777681181</v>
+      </c>
+      <c r="T81">
+        <v>4.166945168872133</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03088861797861487</v>
+      </c>
+      <c r="W81">
+        <v>0.2314237980267068</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1197233254985073</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2332254907724032</v>
+      </c>
+      <c r="C82">
+        <v>-2966.664071130363</v>
+      </c>
+      <c r="D82">
+        <v>849.2690055704453</v>
+      </c>
+      <c r="E82">
+        <v>1088.216730824799</v>
+      </c>
+      <c r="F82">
+        <v>3864.333076700808</v>
+      </c>
+      <c r="G82">
+        <v>48.4</v>
+      </c>
+      <c r="H82">
+        <v>2054.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K82">
+        <v>393.9</v>
+      </c>
+      <c r="L82">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M82">
+        <v>922.802738716153</v>
+      </c>
+      <c r="N82">
+        <v>-813.7027387161529</v>
+      </c>
+      <c r="O82">
+        <v>-209.9353065887674</v>
+      </c>
+      <c r="P82">
+        <v>-603.7674321273855</v>
+      </c>
+      <c r="Q82">
+        <v>-209.8674321273855</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.240063451656524</v>
+      </c>
+      <c r="T82">
+        <v>4.37529242731574</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03050251025388219</v>
+      </c>
+      <c r="W82">
+        <v>0.2315160005513729</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1182267839297759</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2352254907724032</v>
+      </c>
+      <c r="C83">
+        <v>-3023.615472808876</v>
+      </c>
+      <c r="D83">
+        <v>840.6217673506923</v>
+      </c>
+      <c r="E83">
+        <v>1136.520894283559</v>
+      </c>
+      <c r="F83">
+        <v>3912.637240159569</v>
+      </c>
+      <c r="G83">
+        <v>48.4</v>
+      </c>
+      <c r="H83">
+        <v>2054.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K83">
+        <v>393.9</v>
+      </c>
+      <c r="L83">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M83">
+        <v>934.337772950105</v>
+      </c>
+      <c r="N83">
+        <v>-825.237772950105</v>
+      </c>
+      <c r="O83">
+        <v>-212.9113454211271</v>
+      </c>
+      <c r="P83">
+        <v>-612.3264275289779</v>
+      </c>
+      <c r="Q83">
+        <v>-218.4264275289779</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2506562649016043</v>
+      </c>
+      <c r="T83">
+        <v>4.605570976121832</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03012593605321697</v>
+      </c>
+      <c r="W83">
+        <v>0.2316059264704918</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1167671940047169</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2372254907724032</v>
+      </c>
+      <c r="C84">
+        <v>-3080.392557403711</v>
+      </c>
+      <c r="D84">
+        <v>832.1488462146181</v>
+      </c>
+      <c r="E84">
+        <v>1184.825057742319</v>
+      </c>
+      <c r="F84">
+        <v>3960.941403618329</v>
+      </c>
+      <c r="G84">
+        <v>48.4</v>
+      </c>
+      <c r="H84">
+        <v>2054.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K84">
+        <v>393.9</v>
+      </c>
+      <c r="L84">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M84">
+        <v>945.872807184057</v>
+      </c>
+      <c r="N84">
+        <v>-836.772807184057</v>
+      </c>
+      <c r="O84">
+        <v>-215.8873842534867</v>
+      </c>
+      <c r="P84">
+        <v>-620.8854229305703</v>
+      </c>
+      <c r="Q84">
+        <v>-226.9854229305703</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2624260573961379</v>
+      </c>
+      <c r="T84">
+        <v>4.861436030350824</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02975854658915335</v>
+      </c>
+      <c r="W84">
+        <v>0.2316936590745102</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1153432038339276</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2392254907724032</v>
+      </c>
+      <c r="C85">
+        <v>-3137.000543325449</v>
+      </c>
+      <c r="D85">
+        <v>823.84502375164</v>
+      </c>
+      <c r="E85">
+        <v>1233.129221201079</v>
+      </c>
+      <c r="F85">
+        <v>4009.245567077089</v>
+      </c>
+      <c r="G85">
+        <v>48.4</v>
+      </c>
+      <c r="H85">
+        <v>2054.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K85">
+        <v>393.9</v>
+      </c>
+      <c r="L85">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M85">
+        <v>957.407841418009</v>
+      </c>
+      <c r="N85">
+        <v>-848.3078414180088</v>
+      </c>
+      <c r="O85">
+        <v>-218.8634230858463</v>
+      </c>
+      <c r="P85">
+        <v>-629.4444183321625</v>
+      </c>
+      <c r="Q85">
+        <v>-235.5444183321625</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2755805313606166</v>
+      </c>
+      <c r="T85">
+        <v>5.147402855665577</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02940000988325993</v>
+      </c>
+      <c r="W85">
+        <v>0.2317792776398775</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1139535266793021</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2412254907724031</v>
+      </c>
+      <c r="C86">
+        <v>-3193.444442749358</v>
+      </c>
+      <c r="D86">
+        <v>815.7052877864902</v>
+      </c>
+      <c r="E86">
+        <v>1281.433384659839</v>
+      </c>
+      <c r="F86">
+        <v>4057.549730535849</v>
+      </c>
+      <c r="G86">
+        <v>48.4</v>
+      </c>
+      <c r="H86">
+        <v>2054.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K86">
+        <v>393.9</v>
+      </c>
+      <c r="L86">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M86">
+        <v>968.9428756519607</v>
+      </c>
+      <c r="N86">
+        <v>-859.8428756519606</v>
+      </c>
+      <c r="O86">
+        <v>-221.8394619182058</v>
+      </c>
+      <c r="P86">
+        <v>-638.0034137337548</v>
+      </c>
+      <c r="Q86">
+        <v>-244.1034137337548</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.290379314570655</v>
+      </c>
+      <c r="T86">
+        <v>5.469115534144673</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02905000976560208</v>
+      </c>
+      <c r="W86">
+        <v>0.2318628576679742</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.112596937075977</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2432254907724031</v>
+      </c>
+      <c r="C87">
+        <v>-3249.729071703927</v>
+      </c>
+      <c r="D87">
+        <v>807.7248222906815</v>
+      </c>
+      <c r="E87">
+        <v>1329.737548118599</v>
+      </c>
+      <c r="F87">
+        <v>4105.853893994608</v>
+      </c>
+      <c r="G87">
+        <v>48.4</v>
+      </c>
+      <c r="H87">
+        <v>2054.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K87">
+        <v>393.9</v>
+      </c>
+      <c r="L87">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M87">
+        <v>980.4779098859125</v>
+      </c>
+      <c r="N87">
+        <v>-871.3779098859125</v>
+      </c>
+      <c r="O87">
+        <v>-224.8155007505654</v>
+      </c>
+      <c r="P87">
+        <v>-646.562409135347</v>
+      </c>
+      <c r="Q87">
+        <v>-252.662409135347</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3071512688753653</v>
+      </c>
+      <c r="T87">
+        <v>5.833723236420985</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02870824494483029</v>
+      </c>
+      <c r="W87">
+        <v>0.2319444711071745</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1112722672280243</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2452254907724032</v>
+      </c>
+      <c r="C88">
+        <v>-3305.859059572923</v>
+      </c>
+      <c r="D88">
+        <v>799.898997880446</v>
+      </c>
+      <c r="E88">
+        <v>1378.041711577359</v>
+      </c>
+      <c r="F88">
+        <v>4154.158057453369</v>
+      </c>
+      <c r="G88">
+        <v>48.4</v>
+      </c>
+      <c r="H88">
+        <v>2054.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K88">
+        <v>393.9</v>
+      </c>
+      <c r="L88">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M88">
+        <v>992.0129441198646</v>
+      </c>
+      <c r="N88">
+        <v>-882.9129441198645</v>
+      </c>
+      <c r="O88">
+        <v>-227.7915395829251</v>
+      </c>
+      <c r="P88">
+        <v>-655.1214045369395</v>
+      </c>
+      <c r="Q88">
+        <v>-261.2214045369395</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3263192166521771</v>
+      </c>
+      <c r="T88">
+        <v>6.250417753308199</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02837442814314622</v>
+      </c>
+      <c r="W88">
+        <v>0.2320241865594167</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1099784036556055</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2472254907724031</v>
+      </c>
+      <c r="C89">
+        <v>-3361.838858050375</v>
+      </c>
+      <c r="D89">
+        <v>792.2233628617537</v>
+      </c>
+      <c r="E89">
+        <v>1426.345875036119</v>
+      </c>
+      <c r="F89">
+        <v>4202.462220912129</v>
+      </c>
+      <c r="G89">
+        <v>48.4</v>
+      </c>
+      <c r="H89">
+        <v>2054.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K89">
+        <v>393.9</v>
+      </c>
+      <c r="L89">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M89">
+        <v>1003.547978353816</v>
+      </c>
+      <c r="N89">
+        <v>-894.4479783538163</v>
+      </c>
+      <c r="O89">
+        <v>-230.7675784152846</v>
+      </c>
+      <c r="P89">
+        <v>-663.6803999385318</v>
+      </c>
+      <c r="Q89">
+        <v>-269.7803999385318</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3484360794715753</v>
+      </c>
+      <c r="T89">
+        <v>6.731219118947291</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02804828529092614</v>
+      </c>
+      <c r="W89">
+        <v>0.2321020694725268</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1087142840733573</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2492254907724032</v>
+      </c>
+      <c r="C90">
+        <v>-3417.67274958489</v>
+      </c>
+      <c r="D90">
+        <v>784.6936347859983</v>
+      </c>
+      <c r="E90">
+        <v>1474.650038494879</v>
+      </c>
+      <c r="F90">
+        <v>4250.766384370889</v>
+      </c>
+      <c r="G90">
+        <v>48.4</v>
+      </c>
+      <c r="H90">
+        <v>2054.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K90">
+        <v>393.9</v>
+      </c>
+      <c r="L90">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M90">
+        <v>1015.083012587768</v>
+      </c>
+      <c r="N90">
+        <v>-905.9830125877681</v>
+      </c>
+      <c r="O90">
+        <v>-233.7436172476442</v>
+      </c>
+      <c r="P90">
+        <v>-672.239395340124</v>
+      </c>
+      <c r="Q90">
+        <v>-278.339395340124</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3742390860942066</v>
+      </c>
+      <c r="T90">
+        <v>7.292154045526232</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02772955477625653</v>
+      </c>
+      <c r="W90">
+        <v>0.23217818231943</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1074788944816145</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2512254907724031</v>
+      </c>
+      <c r="C91">
+        <v>-3473.364855346928</v>
+      </c>
+      <c r="D91">
+        <v>777.3056924827209</v>
+      </c>
+      <c r="E91">
+        <v>1522.95420195364</v>
+      </c>
+      <c r="F91">
+        <v>4299.07054782965</v>
+      </c>
+      <c r="G91">
+        <v>48.4</v>
+      </c>
+      <c r="H91">
+        <v>2054.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K91">
+        <v>393.9</v>
+      </c>
+      <c r="L91">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M91">
+        <v>1026.61804682172</v>
+      </c>
+      <c r="N91">
+        <v>-917.5180468217202</v>
+      </c>
+      <c r="O91">
+        <v>-236.7196560800038</v>
+      </c>
+      <c r="P91">
+        <v>-680.7983907417164</v>
+      </c>
+      <c r="Q91">
+        <v>-286.8983907417164</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4047335484664073</v>
+      </c>
+      <c r="T91">
+        <v>7.955077140574072</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02741798674506264</v>
+      </c>
+      <c r="W91">
+        <v>0.232252584765279</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1062712664537312</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2532254907724031</v>
+      </c>
+      <c r="C92">
+        <v>-3528.919142750214</v>
+      </c>
+      <c r="D92">
+        <v>770.0555685381959</v>
+      </c>
+      <c r="E92">
+        <v>1571.2583654124</v>
+      </c>
+      <c r="F92">
+        <v>4347.374711288409</v>
+      </c>
+      <c r="G92">
+        <v>48.4</v>
+      </c>
+      <c r="H92">
+        <v>2054.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K92">
+        <v>393.9</v>
+      </c>
+      <c r="L92">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M92">
+        <v>1038.153081055672</v>
+      </c>
+      <c r="N92">
+        <v>-929.053081055672</v>
+      </c>
+      <c r="O92">
+        <v>-239.6956949123634</v>
+      </c>
+      <c r="P92">
+        <v>-689.3573861433086</v>
+      </c>
+      <c r="Q92">
+        <v>-295.4573861433087</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4413269033130481</v>
+      </c>
+      <c r="T92">
+        <v>8.75058485463148</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02711334244789528</v>
+      </c>
+      <c r="W92">
+        <v>0.2323253338234426</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1050904746042454</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2552254907724031</v>
+      </c>
+      <c r="C93">
+        <v>-3584.339432556105</v>
+      </c>
+      <c r="D93">
+        <v>762.9394421910644</v>
+      </c>
+      <c r="E93">
+        <v>1619.562528871159</v>
+      </c>
+      <c r="F93">
+        <v>4395.678874747169</v>
+      </c>
+      <c r="G93">
+        <v>48.4</v>
+      </c>
+      <c r="H93">
+        <v>2054.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K93">
+        <v>393.9</v>
+      </c>
+      <c r="L93">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M93">
+        <v>1049.688115289624</v>
+      </c>
+      <c r="N93">
+        <v>-940.5881152896238</v>
+      </c>
+      <c r="O93">
+        <v>-242.671733744723</v>
+      </c>
+      <c r="P93">
+        <v>-697.9163815449009</v>
+      </c>
+      <c r="Q93">
+        <v>-304.0163815449009</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4860521147922757</v>
+      </c>
+      <c r="T93">
+        <v>9.722872060701645</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02681539362978654</v>
+      </c>
+      <c r="W93">
+        <v>0.232396484001207</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1039356342239789</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2572254907724032</v>
+      </c>
+      <c r="C94">
+        <v>-3639.629405587669</v>
+      </c>
+      <c r="D94">
+        <v>755.9536326182608</v>
+      </c>
+      <c r="E94">
+        <v>1667.86669232992</v>
+      </c>
+      <c r="F94">
+        <v>4443.98303820593</v>
+      </c>
+      <c r="G94">
+        <v>48.4</v>
+      </c>
+      <c r="H94">
+        <v>2054.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K94">
+        <v>393.9</v>
+      </c>
+      <c r="L94">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M94">
+        <v>1061.223149523576</v>
+      </c>
+      <c r="N94">
+        <v>-952.1231495235759</v>
+      </c>
+      <c r="O94">
+        <v>-245.6477725770826</v>
+      </c>
+      <c r="P94">
+        <v>-706.4753769464933</v>
+      </c>
+      <c r="Q94">
+        <v>-312.5753769464933</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5419586291413103</v>
+      </c>
+      <c r="T94">
+        <v>10.93823106828936</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02652392195989755</v>
+      </c>
+      <c r="W94">
+        <v>0.2324660874359765</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1028058990693704</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2592254907724032</v>
+      </c>
+      <c r="C95">
+        <v>-3694.792609078227</v>
+      </c>
+      <c r="D95">
+        <v>749.0945925864631</v>
+      </c>
+      <c r="E95">
+        <v>1716.17085578868</v>
+      </c>
+      <c r="F95">
+        <v>4492.28720166469</v>
+      </c>
+      <c r="G95">
+        <v>48.4</v>
+      </c>
+      <c r="H95">
+        <v>2054.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K95">
+        <v>393.9</v>
+      </c>
+      <c r="L95">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M95">
+        <v>1072.758183757528</v>
+      </c>
+      <c r="N95">
+        <v>-963.6581837575279</v>
+      </c>
+      <c r="O95">
+        <v>-248.6238114094422</v>
+      </c>
+      <c r="P95">
+        <v>-715.0343723480858</v>
+      </c>
+      <c r="Q95">
+        <v>-321.1343723480858</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6138384333043547</v>
+      </c>
+      <c r="T95">
+        <v>12.50083550661641</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02623871849796316</v>
+      </c>
+      <c r="W95">
+        <v>0.2325341940226864</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1017004592944309</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2612254907724031</v>
+      </c>
+      <c r="C96">
+        <v>-3749.832462677403</v>
+      </c>
+      <c r="D96">
+        <v>742.3589024460472</v>
+      </c>
+      <c r="E96">
+        <v>1764.475019247441</v>
+      </c>
+      <c r="F96">
+        <v>4540.59136512345</v>
+      </c>
+      <c r="G96">
+        <v>48.4</v>
+      </c>
+      <c r="H96">
+        <v>2054.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K96">
+        <v>393.9</v>
+      </c>
+      <c r="L96">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M96">
+        <v>1084.29321799148</v>
+      </c>
+      <c r="N96">
+        <v>-975.19321799148</v>
+      </c>
+      <c r="O96">
+        <v>-251.5998502418018</v>
+      </c>
+      <c r="P96">
+        <v>-723.5933677496781</v>
+      </c>
+      <c r="Q96">
+        <v>-329.6933677496781</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7096781721884138</v>
+      </c>
+      <c r="T96">
+        <v>14.58430809105248</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02595958319479334</v>
+      </c>
+      <c r="W96">
+        <v>0.2326008515330834</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1006185395147029</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2632254907724032</v>
+      </c>
+      <c r="C97">
+        <v>-3804.752264136028</v>
+      </c>
+      <c r="D97">
+        <v>735.7432644461825</v>
+      </c>
+      <c r="E97">
+        <v>1812.779182706201</v>
+      </c>
+      <c r="F97">
+        <v>4588.89552858221</v>
+      </c>
+      <c r="G97">
+        <v>48.4</v>
+      </c>
+      <c r="H97">
+        <v>2054.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K97">
+        <v>393.9</v>
+      </c>
+      <c r="L97">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M97">
+        <v>1095.828252225432</v>
+      </c>
+      <c r="N97">
+        <v>-986.7282522254318</v>
+      </c>
+      <c r="O97">
+        <v>-254.5758890741614</v>
+      </c>
+      <c r="P97">
+        <v>-732.1523631512704</v>
+      </c>
+      <c r="Q97">
+        <v>-338.2523631512704</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8438538066260972</v>
+      </c>
+      <c r="T97">
+        <v>17.50116970926298</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02568632442432184</v>
+      </c>
+      <c r="W97">
+        <v>0.232666105727472</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.09955939699349559</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2652254907724031</v>
+      </c>
+      <c r="C98">
+        <v>-3859.555194689749</v>
+      </c>
+      <c r="D98">
+        <v>729.244497351221</v>
+      </c>
+      <c r="E98">
+        <v>1861.08334616496</v>
+      </c>
+      <c r="F98">
+        <v>4637.19969204097</v>
+      </c>
+      <c r="G98">
+        <v>48.4</v>
+      </c>
+      <c r="H98">
+        <v>2054.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K98">
+        <v>393.9</v>
+      </c>
+      <c r="L98">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M98">
+        <v>1107.363286459384</v>
+      </c>
+      <c r="N98">
+        <v>-998.2632864593836</v>
+      </c>
+      <c r="O98">
+        <v>-257.551927906521</v>
+      </c>
+      <c r="P98">
+        <v>-740.7113585528626</v>
+      </c>
+      <c r="Q98">
+        <v>-346.8113585528627</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.045117258282619</v>
+      </c>
+      <c r="T98">
+        <v>21.87646213657868</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02541875854490182</v>
+      </c>
+      <c r="W98">
+        <v>0.2327300004594774</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.09852231994147997</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2672254907724032</v>
+      </c>
+      <c r="C99">
+        <v>-3914.244324159836</v>
+      </c>
+      <c r="D99">
+        <v>722.859531339894</v>
+      </c>
+      <c r="E99">
+        <v>1909.38750962372</v>
+      </c>
+      <c r="F99">
+        <v>4685.50385549973</v>
+      </c>
+      <c r="G99">
+        <v>48.4</v>
+      </c>
+      <c r="H99">
+        <v>2054.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K99">
+        <v>393.9</v>
+      </c>
+      <c r="L99">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M99">
+        <v>1118.898320693336</v>
+      </c>
+      <c r="N99">
+        <v>-1009.798320693335</v>
+      </c>
+      <c r="O99">
+        <v>-260.5279667388805</v>
+      </c>
+      <c r="P99">
+        <v>-749.2703539544549</v>
+      </c>
+      <c r="Q99">
+        <v>-355.3703539544549</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.380556344376826</v>
+      </c>
+      <c r="T99">
+        <v>29.16861618210491</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02515670948773788</v>
+      </c>
+      <c r="W99">
+        <v>0.2327925777743282</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.09750662592146475</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2692254907724032</v>
+      </c>
+      <c r="C100">
+        <v>-3968.822615788329</v>
+      </c>
+      <c r="D100">
+        <v>716.5854031701605</v>
+      </c>
+      <c r="E100">
+        <v>1957.69167308248</v>
+      </c>
+      <c r="F100">
+        <v>4733.80801895849</v>
+      </c>
+      <c r="G100">
+        <v>48.4</v>
+      </c>
+      <c r="H100">
+        <v>2054.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K100">
+        <v>393.9</v>
+      </c>
+      <c r="L100">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M100">
+        <v>1130.433354927287</v>
+      </c>
+      <c r="N100">
+        <v>-1021.333354927287</v>
+      </c>
+      <c r="O100">
+        <v>-263.5040055712401</v>
+      </c>
+      <c r="P100">
+        <v>-757.8293493560471</v>
+      </c>
+      <c r="Q100">
+        <v>-363.9293493560472</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.051434516565239</v>
+      </c>
+      <c r="T100">
+        <v>43.75292427315735</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02490000837051607</v>
+      </c>
+      <c r="W100">
+        <v>0.2328538780011208</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.09651166035083758</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2712254907724032</v>
+      </c>
+      <c r="C101">
+        <v>-4023.29293082357</v>
+      </c>
+      <c r="D101">
+        <v>710.4192515936807</v>
+      </c>
+      <c r="E101">
+        <v>2005.995836541241</v>
+      </c>
+      <c r="F101">
+        <v>4782.112182417251</v>
+      </c>
+      <c r="G101">
+        <v>48.4</v>
+      </c>
+      <c r="H101">
+        <v>2054.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>503.0000000000001</v>
+      </c>
+      <c r="K101">
+        <v>393.9</v>
+      </c>
+      <c r="L101">
+        <v>109.1000000000001</v>
+      </c>
+      <c r="M101">
+        <v>1141.968389161239</v>
+      </c>
+      <c r="N101">
+        <v>-1032.868389161239</v>
+      </c>
+      <c r="O101">
+        <v>-266.4800444035997</v>
+      </c>
+      <c r="P101">
+        <v>-766.3883447576395</v>
+      </c>
+      <c r="Q101">
+        <v>-372.4883447576395</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.064069033130477</v>
+      </c>
+      <c r="T101">
+        <v>87.50584854631471</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02464849313445025</v>
+      </c>
+      <c r="W101">
+        <v>0.2329139398394933</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.09553679509476842</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_recreation.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_recreation.xlsx
@@ -1133,7 +1133,7 @@
         <v>-0.992407407407408</v>
       </c>
       <c r="F2">
-        <v>4.6224100912622</v>
+        <v>4.62241009126221</v>
       </c>
       <c r="G2">
         <v>9.106452172188041</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08463775155252931</v>
+        <v>0.08445277615352378</v>
       </c>
       <c r="C2">
-        <v>3457.942536023189</v>
+        <v>3428.110722367624</v>
       </c>
       <c r="D2">
-        <v>3420.642536023189</v>
+        <v>3437.012245547882</v>
       </c>
       <c r="E2">
-        <v>-3077.252318025784</v>
+        <v>-3031.050794845526</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>46.20152318025784</v>
       </c>
       <c r="G2">
         <v>37.3</v>
@@ -1451,28 +1451,28 @@
         <v>118.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.32393661596697</v>
       </c>
       <c r="N2">
-        <v>118.1</v>
+        <v>115.7760633840331</v>
       </c>
       <c r="O2">
-        <v>30.46980000000001</v>
+        <v>29.87022435308053</v>
       </c>
       <c r="P2">
-        <v>87.63020000000002</v>
+        <v>85.90583903095252</v>
       </c>
       <c r="Q2">
-        <v>532.7302000000001</v>
+        <v>531.0058390309525</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08463775155252931</v>
+        <v>0.08492883853891291</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378594</v>
+        <v>0.9036683265337855</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>50.8189419576143</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08445277615352378</v>
+        <v>0.08426780075451824</v>
       </c>
       <c r="C3">
-        <v>3428.110722367624</v>
+        <v>3398.436338744012</v>
       </c>
       <c r="D3">
-        <v>3437.012245547882</v>
+        <v>3453.539385104527</v>
       </c>
       <c r="E3">
-        <v>-3031.050794845526</v>
+        <v>-2984.849271665268</v>
       </c>
       <c r="F3">
-        <v>46.20152318025784</v>
+        <v>92.40304636051569</v>
       </c>
       <c r="G3">
         <v>37.3</v>
@@ -1533,28 +1533,28 @@
         <v>118.1</v>
       </c>
       <c r="M3">
-        <v>2.32393661596697</v>
+        <v>4.647873231933939</v>
       </c>
       <c r="N3">
-        <v>115.7760633840331</v>
+        <v>113.4521267680661</v>
       </c>
       <c r="O3">
-        <v>29.87022435308053</v>
+        <v>29.27064870616105</v>
       </c>
       <c r="P3">
-        <v>85.90583903095252</v>
+        <v>84.18147806190503</v>
       </c>
       <c r="Q3">
-        <v>531.0058390309525</v>
+        <v>529.2814780619051</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08492883853891291</v>
+        <v>0.08522586607603903</v>
       </c>
       <c r="T3">
-        <v>0.9036683265337855</v>
+        <v>0.9105280848969755</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>50.8189419576143</v>
+        <v>25.40947097880715</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08426780075451824</v>
+        <v>0.08408282535551273</v>
       </c>
       <c r="C4">
-        <v>3398.436338744012</v>
+        <v>3368.921667169104</v>
       </c>
       <c r="D4">
-        <v>3453.539385104527</v>
+        <v>3470.226236709877</v>
       </c>
       <c r="E4">
-        <v>-2984.849271665268</v>
+        <v>-2938.647748485011</v>
       </c>
       <c r="F4">
-        <v>92.40304636051569</v>
+        <v>138.6045695407735</v>
       </c>
       <c r="G4">
         <v>37.3</v>
@@ -1615,28 +1615,28 @@
         <v>118.1</v>
       </c>
       <c r="M4">
-        <v>4.647873231933939</v>
+        <v>6.971809847900908</v>
       </c>
       <c r="N4">
-        <v>113.4521267680661</v>
+        <v>111.1281901520991</v>
       </c>
       <c r="O4">
-        <v>29.27064870616105</v>
+        <v>28.67107305924157</v>
       </c>
       <c r="P4">
-        <v>84.18147806190503</v>
+        <v>82.45711709285754</v>
       </c>
       <c r="Q4">
-        <v>529.2814780619051</v>
+        <v>527.5571170928575</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08522586607603903</v>
+        <v>0.08552901789228116</v>
       </c>
       <c r="T4">
-        <v>0.9105280848969755</v>
+        <v>0.9175292815769323</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>25.40947097880715</v>
+        <v>16.93964731920477</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08408282535551273</v>
+        <v>0.08394236995650721</v>
       </c>
       <c r="C5">
-        <v>3368.921667169104</v>
+        <v>3335.498899249002</v>
       </c>
       <c r="D5">
-        <v>3470.226236709877</v>
+        <v>3483.004991970033</v>
       </c>
       <c r="E5">
-        <v>-2938.647748485011</v>
+        <v>-2892.446225304753</v>
       </c>
       <c r="F5">
-        <v>138.6045695407735</v>
+        <v>184.8060927210314</v>
       </c>
       <c r="G5">
         <v>37.3</v>
@@ -1697,45 +1697,45 @@
         <v>118.1</v>
       </c>
       <c r="M5">
-        <v>6.971809847900908</v>
+        <v>9.572955602949426</v>
       </c>
       <c r="N5">
-        <v>111.1281901520991</v>
+        <v>108.5270443970506</v>
       </c>
       <c r="O5">
-        <v>28.67107305924157</v>
+        <v>27.99997745443905</v>
       </c>
       <c r="P5">
-        <v>82.45711709285754</v>
+        <v>80.52706694261155</v>
       </c>
       <c r="Q5">
-        <v>527.5571170928575</v>
+        <v>525.6270669426116</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08552901789228116</v>
+        <v>0.08583848537136168</v>
       </c>
       <c r="T5">
-        <v>0.9175292815769323</v>
+        <v>0.9246763365210549</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>16.93964731920477</v>
+        <v>12.33683774357143</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08394236995650721</v>
+        <v>0.08376852455750168</v>
       </c>
       <c r="C6">
-        <v>3335.498899249002</v>
+        <v>3305.244911550411</v>
       </c>
       <c r="D6">
-        <v>3483.004991970033</v>
+        <v>3498.9525274517</v>
       </c>
       <c r="E6">
-        <v>-2892.446225304753</v>
+        <v>-2846.244702124495</v>
       </c>
       <c r="F6">
-        <v>184.8060927210314</v>
+        <v>231.0076159012892</v>
       </c>
       <c r="G6">
         <v>37.3</v>
@@ -1779,28 +1779,28 @@
         <v>118.1</v>
       </c>
       <c r="M6">
-        <v>9.572955602949426</v>
+        <v>11.96619450368678</v>
       </c>
       <c r="N6">
-        <v>108.5270443970506</v>
+        <v>106.1338054963132</v>
       </c>
       <c r="O6">
-        <v>27.99997745443905</v>
+        <v>27.38252181804882</v>
       </c>
       <c r="P6">
-        <v>80.52706694261155</v>
+        <v>78.75128367826443</v>
       </c>
       <c r="Q6">
-        <v>525.6270669426116</v>
+        <v>523.8512836782645</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08583848537136168</v>
+        <v>0.08615446795526494</v>
       </c>
       <c r="T6">
-        <v>0.9246763365210549</v>
+        <v>0.9319738557797905</v>
       </c>
       <c r="U6">
         <v>0.0518</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>12.33683774357143</v>
+        <v>9.869470194857142</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08376852455750168</v>
+        <v>0.08367036315849613</v>
       </c>
       <c r="C7">
-        <v>3305.244911550411</v>
+        <v>3268.112804306598</v>
       </c>
       <c r="D7">
-        <v>3498.9525274517</v>
+        <v>3508.021943388145</v>
       </c>
       <c r="E7">
-        <v>-2846.244702124495</v>
+        <v>-2800.043178944237</v>
       </c>
       <c r="F7">
-        <v>231.0076159012892</v>
+        <v>277.2091390815471</v>
       </c>
       <c r="G7">
         <v>37.3</v>
@@ -1861,45 +1861,45 @@
         <v>118.1</v>
       </c>
       <c r="M7">
-        <v>11.96619450368678</v>
+        <v>14.83068894086277</v>
       </c>
       <c r="N7">
-        <v>106.1338054963132</v>
+        <v>103.2693110591373</v>
       </c>
       <c r="O7">
-        <v>27.38252181804882</v>
+        <v>26.64348225325741</v>
       </c>
       <c r="P7">
-        <v>78.75128367826443</v>
+        <v>76.62582880587985</v>
       </c>
       <c r="Q7">
-        <v>523.8512836782645</v>
+        <v>521.7258288058799</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08615446795526494</v>
+        <v>0.08647717357286824</v>
       </c>
       <c r="T7">
-        <v>0.9319738557797905</v>
+        <v>0.9394266414057333</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>9.869470194857142</v>
+        <v>7.963217384635511</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08367036315849613</v>
+        <v>0.08355068375949064</v>
       </c>
       <c r="C8">
-        <v>3268.112804306598</v>
+        <v>3233.032614995617</v>
       </c>
       <c r="D8">
-        <v>3508.021943388145</v>
+        <v>3519.143277257422</v>
       </c>
       <c r="E8">
-        <v>-2800.043178944237</v>
+        <v>-2753.841655763979</v>
       </c>
       <c r="F8">
-        <v>277.2091390815471</v>
+        <v>323.4106622618049</v>
       </c>
       <c r="G8">
         <v>37.3</v>
@@ -1943,45 +1943,45 @@
         <v>118.1</v>
       </c>
       <c r="M8">
-        <v>14.83068894086277</v>
+        <v>17.561198960816</v>
       </c>
       <c r="N8">
-        <v>103.2693110591373</v>
+        <v>100.538801039184</v>
       </c>
       <c r="O8">
-        <v>26.64348225325741</v>
+        <v>25.93901066810948</v>
       </c>
       <c r="P8">
-        <v>76.62582880587985</v>
+        <v>74.59979037107455</v>
       </c>
       <c r="Q8">
-        <v>521.7258288058799</v>
+        <v>519.6997903710745</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08647717357286824</v>
+        <v>0.08680681909622648</v>
       </c>
       <c r="T8">
-        <v>0.9394266414057333</v>
+        <v>0.9470397019913738</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>7.963217384635512</v>
+        <v>6.72505335561168</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08355068375949062</v>
+        <v>0.08345474836048512</v>
       </c>
       <c r="C9">
-        <v>3233.032614995618</v>
+        <v>3195.797037125342</v>
       </c>
       <c r="D9">
-        <v>3519.143277257423</v>
+        <v>3528.109222567405</v>
       </c>
       <c r="E9">
-        <v>-2753.841655763979</v>
+        <v>-2707.640132583721</v>
       </c>
       <c r="F9">
-        <v>323.4106622618049</v>
+        <v>369.6121854420628</v>
       </c>
       <c r="G9">
         <v>37.3</v>
@@ -2025,45 +2025,45 @@
         <v>118.1</v>
       </c>
       <c r="M9">
-        <v>17.56119896081601</v>
+        <v>20.43955385494607</v>
       </c>
       <c r="N9">
-        <v>100.538801039184</v>
+        <v>97.66044614505395</v>
       </c>
       <c r="O9">
-        <v>25.93901066810948</v>
+        <v>25.19639510542392</v>
       </c>
       <c r="P9">
-        <v>74.59979037107455</v>
+        <v>72.46405103963004</v>
       </c>
       <c r="Q9">
-        <v>519.6997903710745</v>
+        <v>517.56405103963</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08680681909622648</v>
+        <v>0.08714363082661425</v>
       </c>
       <c r="T9">
-        <v>0.9470397019913738</v>
+        <v>0.9548182638940933</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.72505335561168</v>
+        <v>5.778012614077756</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08345474836048512</v>
+        <v>0.08330687296147957</v>
       </c>
       <c r="C10">
-        <v>3195.797037125342</v>
+        <v>3163.505512775383</v>
       </c>
       <c r="D10">
-        <v>3528.109222567405</v>
+        <v>3542.019221397703</v>
       </c>
       <c r="E10">
-        <v>-2707.640132583721</v>
+        <v>-2661.438609403463</v>
       </c>
       <c r="F10">
-        <v>369.6121854420628</v>
+        <v>415.8137086223206</v>
       </c>
       <c r="G10">
         <v>37.3</v>
@@ -2107,28 +2107,28 @@
         <v>118.1</v>
       </c>
       <c r="M10">
-        <v>20.43955385494607</v>
+        <v>22.99449808681433</v>
       </c>
       <c r="N10">
-        <v>97.66044614505395</v>
+        <v>95.10550191318569</v>
       </c>
       <c r="O10">
-        <v>25.19639510542392</v>
+        <v>24.53721949360191</v>
       </c>
       <c r="P10">
-        <v>72.46405103963004</v>
+        <v>70.56828241958378</v>
       </c>
       <c r="Q10">
-        <v>517.56405103963</v>
+        <v>515.6682824195838</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08714363082661425</v>
+        <v>0.08748784501261492</v>
       </c>
       <c r="T10">
-        <v>0.9548182638940933</v>
+        <v>0.9627677832012684</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.778012614077756</v>
+        <v>5.136011212513561</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08330687296147957</v>
+        <v>0.08315899756247405</v>
       </c>
       <c r="C11">
-        <v>3163.505512775383</v>
+        <v>3131.324106295887</v>
       </c>
       <c r="D11">
-        <v>3542.019221397703</v>
+        <v>3556.039338098466</v>
       </c>
       <c r="E11">
-        <v>-2661.438609403463</v>
+        <v>-2615.237086223206</v>
       </c>
       <c r="F11">
-        <v>415.8137086223206</v>
+        <v>462.0152318025784</v>
       </c>
       <c r="G11">
         <v>37.3</v>
@@ -2189,28 +2189,28 @@
         <v>118.1</v>
       </c>
       <c r="M11">
-        <v>22.99449808681433</v>
+        <v>25.54944231868259</v>
       </c>
       <c r="N11">
-        <v>95.10550191318569</v>
+        <v>92.55055768131743</v>
       </c>
       <c r="O11">
-        <v>24.53721949360191</v>
+        <v>23.8780438817799</v>
       </c>
       <c r="P11">
-        <v>70.56828241958378</v>
+        <v>68.67251379953753</v>
       </c>
       <c r="Q11">
-        <v>515.6682824195838</v>
+        <v>513.7725137995376</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08748784501261492</v>
+        <v>0.08783970840274895</v>
       </c>
       <c r="T11">
-        <v>0.9627677832012684</v>
+        <v>0.9708939584930474</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.136011212513561</v>
+        <v>4.622410091262205</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08315899756247405</v>
+        <v>0.08321517216346852</v>
       </c>
       <c r="C12">
-        <v>3131.324106295887</v>
+        <v>3079.783596833125</v>
       </c>
       <c r="D12">
-        <v>3556.039338098466</v>
+        <v>3550.700351815961</v>
       </c>
       <c r="E12">
-        <v>-2615.237086223206</v>
+        <v>-2569.035563042948</v>
       </c>
       <c r="F12">
-        <v>462.0152318025785</v>
+        <v>508.2167549828363</v>
       </c>
       <c r="G12">
         <v>37.3</v>
@@ -2271,45 +2271,45 @@
         <v>118.1</v>
       </c>
       <c r="M12">
-        <v>25.54944231868259</v>
+        <v>29.37492843800794</v>
       </c>
       <c r="N12">
-        <v>92.55055768131743</v>
+        <v>88.72507156199208</v>
       </c>
       <c r="O12">
-        <v>23.8780438817799</v>
+        <v>22.89106846299396</v>
       </c>
       <c r="P12">
-        <v>68.67251379953753</v>
+        <v>65.83400309899812</v>
       </c>
       <c r="Q12">
-        <v>513.7725137995376</v>
+        <v>510.9340030989981</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08783970840274895</v>
+        <v>0.08819947883535789</v>
       </c>
       <c r="T12">
-        <v>0.9708939584930474</v>
+        <v>0.9792027444655402</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.622410091262204</v>
+        <v>4.020435326310159</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08321517216346852</v>
+        <v>0.083646798764463</v>
       </c>
       <c r="C13">
-        <v>3079.783596833125</v>
+        <v>2993.087850256534</v>
       </c>
       <c r="D13">
-        <v>3550.700351815961</v>
+        <v>3510.206128419627</v>
       </c>
       <c r="E13">
-        <v>-2569.035563042948</v>
+        <v>-2522.83403986269</v>
       </c>
       <c r="F13">
-        <v>508.2167549828363</v>
+        <v>554.4182781630941</v>
       </c>
       <c r="G13">
         <v>37.3</v>
@@ -2353,45 +2353,45 @@
         <v>118.1</v>
       </c>
       <c r="M13">
-        <v>29.37492843800794</v>
+        <v>35.53821163025433</v>
       </c>
       <c r="N13">
-        <v>88.72507156199208</v>
+        <v>82.5617883697457</v>
       </c>
       <c r="O13">
-        <v>22.89106846299396</v>
+        <v>21.30094139939439</v>
       </c>
       <c r="P13">
-        <v>65.83400309899812</v>
+        <v>61.26084697035131</v>
       </c>
       <c r="Q13">
-        <v>510.9340030989981</v>
+        <v>506.3608469703513</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08819947883535789</v>
+        <v>0.08856742586870796</v>
       </c>
       <c r="T13">
-        <v>0.9792027444655402</v>
+        <v>0.9877003664828629</v>
       </c>
       <c r="U13">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0428876</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.020435326310159</v>
+        <v>3.323183541950077</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.083646798764463</v>
+        <v>0.08356421936545748</v>
       </c>
       <c r="C14">
-        <v>2993.087850256534</v>
+        <v>2954.56213018676</v>
       </c>
       <c r="D14">
-        <v>3510.206128419627</v>
+        <v>3517.881931530112</v>
       </c>
       <c r="E14">
-        <v>-2522.83403986269</v>
+        <v>-2476.632516682432</v>
       </c>
       <c r="F14">
-        <v>554.4182781630941</v>
+        <v>600.619801343352</v>
       </c>
       <c r="G14">
         <v>37.3</v>
@@ -2435,28 +2435,28 @@
         <v>118.1</v>
       </c>
       <c r="M14">
-        <v>35.53821163025433</v>
+        <v>38.49972926610887</v>
       </c>
       <c r="N14">
-        <v>82.5617883697457</v>
+        <v>79.60027073389116</v>
       </c>
       <c r="O14">
-        <v>21.30094139939439</v>
+        <v>20.53686984934392</v>
       </c>
       <c r="P14">
-        <v>61.26084697035131</v>
+        <v>59.06340088454724</v>
       </c>
       <c r="Q14">
-        <v>506.3608469703513</v>
+        <v>504.1634008845473</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08856742586870796</v>
+        <v>0.08894383145454882</v>
       </c>
       <c r="T14">
-        <v>0.9877003664828629</v>
+        <v>0.9963933361327673</v>
       </c>
       <c r="U14">
         <v>0.0641</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.323183541950077</v>
+        <v>3.067554038723148</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08356421936545748</v>
+        <v>0.08429190396645196</v>
       </c>
       <c r="C15">
-        <v>2954.56213018676</v>
+        <v>2841.855491751037</v>
       </c>
       <c r="D15">
-        <v>3517.881931530112</v>
+        <v>3451.376816274647</v>
       </c>
       <c r="E15">
-        <v>-2476.632516682432</v>
+        <v>-2430.430993502174</v>
       </c>
       <c r="F15">
-        <v>600.619801343352</v>
+        <v>646.8213245236099</v>
       </c>
       <c r="G15">
         <v>37.3</v>
@@ -2517,45 +2517,45 @@
         <v>118.1</v>
       </c>
       <c r="M15">
-        <v>38.49972926610887</v>
+        <v>46.50645323324756</v>
       </c>
       <c r="N15">
-        <v>79.60027073389116</v>
+        <v>71.59354676675247</v>
       </c>
       <c r="O15">
-        <v>20.53686984934392</v>
+        <v>18.47113506582214</v>
       </c>
       <c r="P15">
-        <v>59.06340088454724</v>
+        <v>53.12241170093033</v>
       </c>
       <c r="Q15">
-        <v>504.1634008845473</v>
+        <v>498.2224117009304</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08894383145454882</v>
+        <v>0.08932899065866506</v>
       </c>
       <c r="T15">
-        <v>0.9963933361327673</v>
+        <v>1.005288467867553</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.067554038723148</v>
+        <v>2.539432525797734</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08429190396645196</v>
+        <v>0.08470127056744643</v>
       </c>
       <c r="C16">
-        <v>2841.855491751037</v>
+        <v>2759.33437346707</v>
       </c>
       <c r="D16">
-        <v>3451.376816274647</v>
+        <v>3415.057221170938</v>
       </c>
       <c r="E16">
-        <v>-2430.430993502174</v>
+        <v>-2384.229470321916</v>
       </c>
       <c r="F16">
-        <v>646.8213245236099</v>
+        <v>693.0228477038678</v>
       </c>
       <c r="G16">
         <v>37.3</v>
@@ -2599,45 +2599,45 @@
         <v>118.1</v>
       </c>
       <c r="M16">
-        <v>46.50645323324756</v>
+        <v>52.53113185595318</v>
       </c>
       <c r="N16">
-        <v>71.59354676675247</v>
+        <v>65.56886814404683</v>
       </c>
       <c r="O16">
-        <v>18.47113506582214</v>
+        <v>16.91676798116408</v>
       </c>
       <c r="P16">
-        <v>53.12241170093033</v>
+        <v>48.65210016288275</v>
       </c>
       <c r="Q16">
-        <v>498.2224117009304</v>
+        <v>493.7521001628828</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08932899065866506</v>
+        <v>0.08972321243228992</v>
       </c>
       <c r="T16">
-        <v>1.005288467867553</v>
+        <v>1.014392896819629</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.539432525797734</v>
+        <v>2.248190660042215</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08470127056744643</v>
+        <v>0.0847055051684409</v>
       </c>
       <c r="C17">
-        <v>2759.33437346707</v>
+        <v>2712.761144415309</v>
       </c>
       <c r="D17">
-        <v>3415.057221170938</v>
+        <v>3414.685515299434</v>
       </c>
       <c r="E17">
-        <v>-2384.229470321916</v>
+        <v>-2338.027947141658</v>
       </c>
       <c r="F17">
-        <v>693.0228477038677</v>
+        <v>739.2243708841255</v>
       </c>
       <c r="G17">
         <v>37.3</v>
@@ -2681,28 +2681,28 @@
         <v>118.1</v>
       </c>
       <c r="M17">
-        <v>52.53113185595318</v>
+        <v>56.03320731301672</v>
       </c>
       <c r="N17">
-        <v>65.56886814404685</v>
+        <v>62.06679268698331</v>
       </c>
       <c r="O17">
-        <v>16.91676798116409</v>
+        <v>16.01323251324169</v>
       </c>
       <c r="P17">
-        <v>48.65210016288276</v>
+        <v>46.05356017374162</v>
       </c>
       <c r="Q17">
-        <v>493.7521001628828</v>
+        <v>491.1535601737417</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08972321243228992</v>
+        <v>0.09012682043862012</v>
       </c>
       <c r="T17">
-        <v>1.014392896819629</v>
+        <v>1.02371409788961</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.248190660042216</v>
+        <v>2.107678743789577</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0847055051684409</v>
+        <v>0.08650092776943538</v>
       </c>
       <c r="C18">
-        <v>2712.761144415309</v>
+        <v>2515.929061062389</v>
       </c>
       <c r="D18">
-        <v>3414.685515299434</v>
+        <v>3264.054955126772</v>
       </c>
       <c r="E18">
-        <v>-2338.027947141658</v>
+        <v>-2291.8264239614</v>
       </c>
       <c r="F18">
-        <v>739.2243708841255</v>
+        <v>785.4258940643834</v>
       </c>
       <c r="G18">
         <v>37.3</v>
@@ -2763,45 +2763,45 @@
         <v>118.1</v>
       </c>
       <c r="M18">
-        <v>56.03320731301672</v>
+        <v>70.68833046579451</v>
       </c>
       <c r="N18">
-        <v>62.06679268698331</v>
+        <v>47.41166953420552</v>
       </c>
       <c r="O18">
-        <v>16.01323251324169</v>
+        <v>12.23221073982502</v>
       </c>
       <c r="P18">
-        <v>46.05356017374162</v>
+        <v>35.17945879438049</v>
       </c>
       <c r="Q18">
-        <v>491.1535601737417</v>
+        <v>480.2794587943805</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09012682043862012</v>
+        <v>0.09054015393907877</v>
       </c>
       <c r="T18">
-        <v>1.02371409788961</v>
+        <v>1.03325990621429</v>
       </c>
       <c r="U18">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.107678743789577</v>
+        <v>1.670714235599999</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08650092776943538</v>
+        <v>0.08661052637042985</v>
       </c>
       <c r="C19">
-        <v>2515.929061062389</v>
+        <v>2460.961763743278</v>
       </c>
       <c r="D19">
-        <v>3264.054955126772</v>
+        <v>3255.289180987918</v>
       </c>
       <c r="E19">
-        <v>-2291.8264239614</v>
+        <v>-2245.624900781143</v>
       </c>
       <c r="F19">
-        <v>785.4258940643834</v>
+        <v>831.6274172446413</v>
       </c>
       <c r="G19">
         <v>37.3</v>
@@ -2845,28 +2845,28 @@
         <v>118.1</v>
       </c>
       <c r="M19">
-        <v>70.68833046579451</v>
+        <v>74.84646755201771</v>
       </c>
       <c r="N19">
-        <v>47.41166953420552</v>
+        <v>43.25353244798231</v>
       </c>
       <c r="O19">
-        <v>12.23221073982502</v>
+        <v>11.15941137157944</v>
       </c>
       <c r="P19">
-        <v>35.17945879438049</v>
+        <v>32.09412107640287</v>
       </c>
       <c r="Q19">
-        <v>480.2794587943805</v>
+        <v>477.1941210764029</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09054015393907877</v>
+        <v>0.09096356874442664</v>
       </c>
       <c r="T19">
-        <v>1.03325990621429</v>
+        <v>1.043038539132255</v>
       </c>
       <c r="U19">
         <v>0.09</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.670714235599999</v>
+        <v>1.577896778066666</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08661052637042985</v>
+        <v>0.09548799153089246</v>
       </c>
       <c r="C20">
-        <v>2460.961763743278</v>
+        <v>1833.156609563285</v>
       </c>
       <c r="D20">
-        <v>3255.289180987918</v>
+        <v>2673.685549988184</v>
       </c>
       <c r="E20">
-        <v>-2245.624900781143</v>
+        <v>-2199.423377600885</v>
       </c>
       <c r="F20">
-        <v>831.6274172446412</v>
+        <v>877.8289404248991</v>
       </c>
       <c r="G20">
         <v>37.3</v>
@@ -2927,45 +2927,45 @@
         <v>118.1</v>
       </c>
       <c r="M20">
-        <v>74.8464675520177</v>
+        <v>128.8652884543752</v>
       </c>
       <c r="N20">
-        <v>43.25353244798232</v>
+        <v>-10.76528845437517</v>
       </c>
       <c r="O20">
-        <v>11.15941137157944</v>
+        <v>-2.777444421228793</v>
       </c>
       <c r="P20">
-        <v>32.09412107640289</v>
+        <v>-7.987844033146374</v>
       </c>
       <c r="Q20">
-        <v>477.1941210764029</v>
+        <v>437.1121559668537</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09096356874442664</v>
+        <v>0.09159378877098752</v>
       </c>
       <c r="T20">
-        <v>1.043038539132255</v>
+        <v>1.057593274156756</v>
       </c>
       <c r="U20">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V20">
-        <v>0.258</v>
+        <v>0.2364469157323762</v>
       </c>
       <c r="W20">
-        <v>0.06677999999999999</v>
+        <v>0.1120895927704872</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.577896778066666</v>
+        <v>0.9164609136913807</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09548799153089246</v>
+        <v>0.09649799153089247</v>
       </c>
       <c r="C21">
-        <v>1833.156609563285</v>
+        <v>1733.690206967782</v>
       </c>
       <c r="D21">
-        <v>2673.685549988184</v>
+        <v>2620.420670572939</v>
       </c>
       <c r="E21">
-        <v>-2199.423377600885</v>
+        <v>-2153.221854420627</v>
       </c>
       <c r="F21">
-        <v>877.8289404248991</v>
+        <v>924.0304636051569</v>
       </c>
       <c r="G21">
         <v>37.3</v>
@@ -3009,37 +3009,37 @@
         <v>118.1</v>
       </c>
       <c r="M21">
-        <v>128.8652884543752</v>
+        <v>135.6476720572371</v>
       </c>
       <c r="N21">
-        <v>-10.76528845437517</v>
+        <v>-17.54767205723704</v>
       </c>
       <c r="O21">
-        <v>-2.777444421228793</v>
+        <v>-4.527299390767156</v>
       </c>
       <c r="P21">
-        <v>-7.987844033146374</v>
+        <v>-13.02037266646988</v>
       </c>
       <c r="Q21">
-        <v>437.1121559668537</v>
+        <v>432.0796273335301</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09159378877098752</v>
+        <v>0.09216621113062487</v>
       </c>
       <c r="T21">
-        <v>1.057593274156756</v>
+        <v>1.070813190083715</v>
       </c>
       <c r="U21">
         <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.2364469157323762</v>
+        <v>0.2246245699457574</v>
       </c>
       <c r="W21">
-        <v>0.1120895927704872</v>
+        <v>0.1138251131319628</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.9164609136913807</v>
+        <v>0.8706378680068116</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09649799153089247</v>
+        <v>0.09750799153089247</v>
       </c>
       <c r="C22">
-        <v>1733.690206967782</v>
+        <v>1636.30462501979</v>
       </c>
       <c r="D22">
-        <v>2620.420670572939</v>
+        <v>2569.236611805205</v>
       </c>
       <c r="E22">
-        <v>-2153.221854420627</v>
+        <v>-2107.020331240369</v>
       </c>
       <c r="F22">
-        <v>924.0304636051569</v>
+        <v>970.2319867854148</v>
       </c>
       <c r="G22">
         <v>37.3</v>
@@ -3091,37 +3091,37 @@
         <v>118.1</v>
       </c>
       <c r="M22">
-        <v>135.6476720572371</v>
+        <v>142.4300556600989</v>
       </c>
       <c r="N22">
-        <v>-17.54767205723704</v>
+        <v>-24.33005566009888</v>
       </c>
       <c r="O22">
-        <v>-4.527299390767156</v>
+        <v>-6.277154360305511</v>
       </c>
       <c r="P22">
-        <v>-13.02037266646988</v>
+        <v>-18.05290129979337</v>
       </c>
       <c r="Q22">
-        <v>432.0796273335301</v>
+        <v>427.0470987002067</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09216621113062487</v>
+        <v>0.0927531251955695</v>
       </c>
       <c r="T22">
-        <v>1.070813190083715</v>
+        <v>1.084367787426547</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.2246245699457574</v>
+        <v>0.2139281618531023</v>
       </c>
       <c r="W22">
-        <v>0.1138251131319628</v>
+        <v>0.1153953458399646</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.8706378680068116</v>
+        <v>0.8291789219112492</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09750799153089246</v>
+        <v>0.1108672059880318</v>
       </c>
       <c r="C23">
-        <v>1636.304625019791</v>
+        <v>1062.602614196754</v>
       </c>
       <c r="D23">
-        <v>2569.236611805206</v>
+        <v>2041.736124162427</v>
       </c>
       <c r="E23">
-        <v>-2107.020331240369</v>
+        <v>-2060.818808060111</v>
       </c>
       <c r="F23">
-        <v>970.2319867854147</v>
+        <v>1016.433509965673</v>
       </c>
       <c r="G23">
         <v>37.3</v>
@@ -3173,45 +3173,45 @@
         <v>118.1</v>
       </c>
       <c r="M23">
-        <v>142.4300556600989</v>
+        <v>204.099848801107</v>
       </c>
       <c r="N23">
-        <v>-24.33005566009888</v>
+        <v>-85.99984880110702</v>
       </c>
       <c r="O23">
-        <v>-6.277154360305511</v>
+        <v>-22.18796099068561</v>
       </c>
       <c r="P23">
-        <v>-18.05290129979337</v>
+        <v>-63.81188781042141</v>
       </c>
       <c r="Q23">
-        <v>427.0470987002067</v>
+        <v>381.2881121895786</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0927531251955695</v>
+        <v>0.09395664533543496</v>
       </c>
       <c r="T23">
-        <v>1.084367787426547</v>
+        <v>1.112162709825288</v>
       </c>
       <c r="U23">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.2139281618531023</v>
+        <v>0.1492886946216823</v>
       </c>
       <c r="W23">
-        <v>0.1153953458399646</v>
+        <v>0.1708228301199662</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y23">
-        <v>0.8291789219112492</v>
+        <v>0.5786383512468307</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1108672059880318</v>
+        <v>0.1124172059880318</v>
       </c>
       <c r="C24">
-        <v>1062.602614196754</v>
+        <v>968.8954812342381</v>
       </c>
       <c r="D24">
-        <v>2041.736124162427</v>
+        <v>1994.230514380169</v>
       </c>
       <c r="E24">
-        <v>-2060.818808060111</v>
+        <v>-2014.617284879854</v>
       </c>
       <c r="F24">
-        <v>1016.433509965673</v>
+        <v>1062.63503314593</v>
       </c>
       <c r="G24">
         <v>37.3</v>
@@ -3255,37 +3255,37 @@
         <v>118.1</v>
       </c>
       <c r="M24">
-        <v>204.099848801107</v>
+        <v>213.3771146557029</v>
       </c>
       <c r="N24">
-        <v>-85.99984880110702</v>
+        <v>-95.27711465570283</v>
       </c>
       <c r="O24">
-        <v>-22.18796099068561</v>
+        <v>-24.58149558117133</v>
       </c>
       <c r="P24">
-        <v>-63.81188781042141</v>
+        <v>-70.69561907453149</v>
       </c>
       <c r="Q24">
-        <v>381.2881121895786</v>
+        <v>374.4043809254686</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09395664533543496</v>
+        <v>0.09458205631381725</v>
       </c>
       <c r="T24">
-        <v>1.112162709825288</v>
+        <v>1.126606381381461</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1492886946216823</v>
+        <v>0.1427978818120439</v>
       </c>
       <c r="W24">
-        <v>0.1708228301199662</v>
+        <v>0.1721261853321416</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5786383512468307</v>
+        <v>0.5534801620621859</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1124172059880318</v>
+        <v>0.1139672059880318</v>
       </c>
       <c r="C25">
-        <v>968.8954812342381</v>
+        <v>877.3487329932384</v>
       </c>
       <c r="D25">
-        <v>1994.230514380169</v>
+        <v>1948.885289319427</v>
       </c>
       <c r="E25">
-        <v>-2014.617284879854</v>
+        <v>-1968.415761699596</v>
       </c>
       <c r="F25">
-        <v>1062.63503314593</v>
+        <v>1108.836556326188</v>
       </c>
       <c r="G25">
         <v>37.3</v>
@@ -3337,37 +3337,37 @@
         <v>118.1</v>
       </c>
       <c r="M25">
-        <v>213.3771146557029</v>
+        <v>222.6543805102986</v>
       </c>
       <c r="N25">
-        <v>-95.27711465570283</v>
+        <v>-104.5543805102986</v>
       </c>
       <c r="O25">
-        <v>-24.58149558117133</v>
+        <v>-26.97503017165704</v>
       </c>
       <c r="P25">
-        <v>-70.69561907453149</v>
+        <v>-77.57935033864158</v>
       </c>
       <c r="Q25">
-        <v>374.4043809254686</v>
+        <v>367.5206496613584</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09458205631381725</v>
+        <v>0.09522392547584116</v>
       </c>
       <c r="T25">
-        <v>1.126606381381461</v>
+        <v>1.141430149557533</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1427978818120439</v>
+        <v>0.1368479700698755</v>
       </c>
       <c r="W25">
-        <v>0.1721261853321416</v>
+        <v>0.173320927609969</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5534801620621859</v>
+        <v>0.5304184886429281</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1139672059880318</v>
+        <v>0.1155172059880318</v>
       </c>
       <c r="C26">
-        <v>877.3487329932386</v>
+        <v>787.8182760779757</v>
       </c>
       <c r="D26">
-        <v>1948.885289319427</v>
+        <v>1905.556355584422</v>
       </c>
       <c r="E26">
-        <v>-1968.415761699596</v>
+        <v>-1922.214238519338</v>
       </c>
       <c r="F26">
-        <v>1108.836556326188</v>
+        <v>1155.038079506446</v>
       </c>
       <c r="G26">
         <v>37.3</v>
@@ -3419,37 +3419,37 @@
         <v>118.1</v>
       </c>
       <c r="M26">
-        <v>222.6543805102986</v>
+        <v>231.9316463648944</v>
       </c>
       <c r="N26">
-        <v>-104.5543805102986</v>
+        <v>-113.8316463648944</v>
       </c>
       <c r="O26">
-        <v>-26.97503017165704</v>
+        <v>-29.36856476214275</v>
       </c>
       <c r="P26">
-        <v>-77.57935033864155</v>
+        <v>-84.46308160275163</v>
       </c>
       <c r="Q26">
-        <v>367.5206496613584</v>
+        <v>360.6369183972484</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09522392547584116</v>
+        <v>0.09588291114885236</v>
       </c>
       <c r="T26">
-        <v>1.141430149557533</v>
+        <v>1.156649218218299</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1368479700698755</v>
+        <v>0.1313740512670804</v>
       </c>
       <c r="W26">
-        <v>0.173320927609969</v>
+        <v>0.1744200905055703</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5304184886429282</v>
+        <v>0.5092017490972109</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1155172059880318</v>
+        <v>0.1263565396889697</v>
       </c>
       <c r="C27">
-        <v>787.8182760779757</v>
+        <v>485.213470136669</v>
       </c>
       <c r="D27">
-        <v>1905.556355584422</v>
+        <v>1649.153072823373</v>
       </c>
       <c r="E27">
-        <v>-1922.214238519338</v>
+        <v>-1876.01271533908</v>
       </c>
       <c r="F27">
-        <v>1155.038079506446</v>
+        <v>1201.239602686704</v>
       </c>
       <c r="G27">
         <v>37.3</v>
@@ -3501,45 +3501,45 @@
         <v>118.1</v>
       </c>
       <c r="M27">
-        <v>231.9316463648944</v>
+        <v>283.2522983135248</v>
       </c>
       <c r="N27">
-        <v>-113.8316463648944</v>
+        <v>-165.1522983135248</v>
       </c>
       <c r="O27">
-        <v>-29.36856476214275</v>
+        <v>-42.6092929648894</v>
       </c>
       <c r="P27">
-        <v>-84.46308160275163</v>
+        <v>-122.5430053486354</v>
       </c>
       <c r="Q27">
-        <v>360.6369183972484</v>
+        <v>322.5569946513646</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09588291114885236</v>
+        <v>0.09681556359807723</v>
       </c>
       <c r="T27">
-        <v>1.156649218218299</v>
+        <v>1.178188535752361</v>
       </c>
       <c r="U27">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.1313740512670804</v>
+        <v>0.1075712366021961</v>
       </c>
       <c r="W27">
-        <v>0.1744200905055703</v>
+        <v>0.2104347024092021</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y27">
-        <v>0.5092017490972109</v>
+        <v>0.4169427775278918</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1263565396889697</v>
+        <v>0.1282565396889697</v>
       </c>
       <c r="C28">
-        <v>485.213470136669</v>
+        <v>401.0114335928404</v>
       </c>
       <c r="D28">
-        <v>1649.153072823373</v>
+        <v>1611.152559459802</v>
       </c>
       <c r="E28">
-        <v>-1876.01271533908</v>
+        <v>-1829.811192158822</v>
       </c>
       <c r="F28">
-        <v>1201.239602686704</v>
+        <v>1247.441125866962</v>
       </c>
       <c r="G28">
         <v>37.3</v>
@@ -3583,37 +3583,37 @@
         <v>118.1</v>
       </c>
       <c r="M28">
-        <v>283.2522983135248</v>
+        <v>294.1466174794297</v>
       </c>
       <c r="N28">
-        <v>-165.1522983135248</v>
+        <v>-176.0466174794296</v>
       </c>
       <c r="O28">
-        <v>-42.6092929648894</v>
+        <v>-45.42002730969285</v>
       </c>
       <c r="P28">
-        <v>-122.5430053486354</v>
+        <v>-130.6265901697368</v>
       </c>
       <c r="Q28">
-        <v>322.5569946513646</v>
+        <v>314.4734098302632</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09681556359807723</v>
+        <v>0.09751440693503721</v>
       </c>
       <c r="T28">
-        <v>1.178188535752361</v>
+        <v>1.19432810473527</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1075712366021961</v>
+        <v>0.1035871167280407</v>
       </c>
       <c r="W28">
-        <v>0.2104347024092021</v>
+        <v>0.211374157875528</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4169427775278918</v>
+        <v>0.4015004524342661</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1282565396889697</v>
+        <v>0.1301565396889697</v>
       </c>
       <c r="C29">
-        <v>401.0114335928404</v>
+        <v>318.5212021006905</v>
       </c>
       <c r="D29">
-        <v>1611.152559459802</v>
+        <v>1574.86385114791</v>
       </c>
       <c r="E29">
-        <v>-1829.811192158822</v>
+        <v>-1783.609668978564</v>
       </c>
       <c r="F29">
-        <v>1247.441125866962</v>
+        <v>1293.64264904722</v>
       </c>
       <c r="G29">
         <v>37.3</v>
@@ -3665,37 +3665,37 @@
         <v>118.1</v>
       </c>
       <c r="M29">
-        <v>294.1466174794297</v>
+        <v>305.0409366453344</v>
       </c>
       <c r="N29">
-        <v>-176.0466174794296</v>
+        <v>-186.9409366453344</v>
       </c>
       <c r="O29">
-        <v>-45.42002730969285</v>
+        <v>-48.23076165449627</v>
       </c>
       <c r="P29">
-        <v>-130.6265901697368</v>
+        <v>-138.7101749908381</v>
       </c>
       <c r="Q29">
-        <v>314.4734098302632</v>
+        <v>306.3898250091619</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09751440693503721</v>
+        <v>0.09823266258691271</v>
       </c>
       <c r="T29">
-        <v>1.19432810473527</v>
+        <v>1.210915995078816</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.1035871167280407</v>
+        <v>0.09988757684489638</v>
       </c>
       <c r="W29">
-        <v>0.211374157875528</v>
+        <v>0.2122465093799734</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4015004524342661</v>
+        <v>0.3871611505616138</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1301565396889697</v>
+        <v>0.1320565396889697</v>
       </c>
       <c r="C30">
-        <v>318.5212021006905</v>
+        <v>237.6296562511873</v>
       </c>
       <c r="D30">
-        <v>1574.86385114791</v>
+        <v>1540.173828478665</v>
       </c>
       <c r="E30">
-        <v>-1783.609668978564</v>
+        <v>-1737.408145798306</v>
       </c>
       <c r="F30">
-        <v>1293.64264904722</v>
+        <v>1339.844172227478</v>
       </c>
       <c r="G30">
         <v>37.3</v>
@@ -3747,37 +3747,37 @@
         <v>118.1</v>
       </c>
       <c r="M30">
-        <v>305.0409366453344</v>
+        <v>315.9352558112392</v>
       </c>
       <c r="N30">
-        <v>-186.9409366453344</v>
+        <v>-197.8352558112392</v>
       </c>
       <c r="O30">
-        <v>-48.23076165449627</v>
+        <v>-51.04149599929972</v>
       </c>
       <c r="P30">
-        <v>-138.7101749908381</v>
+        <v>-146.7937598119395</v>
       </c>
       <c r="Q30">
-        <v>306.3898250091619</v>
+        <v>298.3062401880605</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09823266258691271</v>
+        <v>0.09897115079236218</v>
       </c>
       <c r="T30">
-        <v>1.210915995078816</v>
+        <v>1.227971149939081</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.09988757684489638</v>
+        <v>0.09644317764334821</v>
       </c>
       <c r="W30">
-        <v>0.2122465093799734</v>
+        <v>0.2130586987116985</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3871611505616138</v>
+        <v>0.3738107660594892</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1320565396889697</v>
+        <v>0.1339565396889697</v>
       </c>
       <c r="C31">
-        <v>237.629656251188</v>
+        <v>158.2334286912653</v>
       </c>
       <c r="D31">
-        <v>1540.173828478665</v>
+        <v>1506.979124099001</v>
       </c>
       <c r="E31">
-        <v>-1737.408145798307</v>
+        <v>-1691.206622618049</v>
       </c>
       <c r="F31">
-        <v>1339.844172227477</v>
+        <v>1386.045695407735</v>
       </c>
       <c r="G31">
         <v>37.3</v>
@@ -3829,37 +3829,37 @@
         <v>118.1</v>
       </c>
       <c r="M31">
-        <v>315.9352558112392</v>
+        <v>326.829574977144</v>
       </c>
       <c r="N31">
-        <v>-197.8352558112392</v>
+        <v>-208.729574977144</v>
       </c>
       <c r="O31">
-        <v>-51.04149599929971</v>
+        <v>-53.85223034410316</v>
       </c>
       <c r="P31">
-        <v>-146.7937598119395</v>
+        <v>-154.8773446330408</v>
       </c>
       <c r="Q31">
-        <v>298.3062401880605</v>
+        <v>290.2226553669592</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09897115079236218</v>
+        <v>0.09973073866082451</v>
       </c>
       <c r="T31">
-        <v>1.227971149939081</v>
+        <v>1.24551359493821</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.09644317764334823</v>
+        <v>0.09322840505523661</v>
       </c>
       <c r="W31">
-        <v>0.2130586987116985</v>
+        <v>0.2138167420879752</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3738107660594893</v>
+        <v>0.3613504071908396</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1339565396889697</v>
+        <v>0.1358565396889697</v>
       </c>
       <c r="C32">
-        <v>158.2334286912653</v>
+        <v>80.23787538641045</v>
       </c>
       <c r="D32">
-        <v>1506.979124099001</v>
+        <v>1475.185093974404</v>
       </c>
       <c r="E32">
-        <v>-1691.206622618049</v>
+        <v>-1645.005099437791</v>
       </c>
       <c r="F32">
-        <v>1386.045695407735</v>
+        <v>1432.247218587993</v>
       </c>
       <c r="G32">
         <v>37.3</v>
@@ -3911,37 +3911,37 @@
         <v>118.1</v>
       </c>
       <c r="M32">
-        <v>326.829574977144</v>
+        <v>337.7238941430488</v>
       </c>
       <c r="N32">
-        <v>-208.729574977144</v>
+        <v>-219.6238941430488</v>
       </c>
       <c r="O32">
-        <v>-53.85223034410316</v>
+        <v>-56.66296468890659</v>
       </c>
       <c r="P32">
-        <v>-154.8773446330408</v>
+        <v>-162.9609294541422</v>
       </c>
       <c r="Q32">
-        <v>290.2226553669592</v>
+        <v>282.1390705458578</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09973073866082451</v>
+        <v>0.1005123435689524</v>
       </c>
       <c r="T32">
-        <v>1.24551359493821</v>
+        <v>1.263564516603982</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.09322840505523661</v>
+        <v>0.09022103715022899</v>
       </c>
       <c r="W32">
-        <v>0.2138167420879752</v>
+        <v>0.214525879439976</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3613504071908396</v>
+        <v>0.349693942442748</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1358565396889697</v>
+        <v>0.1377565396889697</v>
       </c>
       <c r="C33">
-        <v>80.23787538641045</v>
+        <v>3.556174417474949</v>
       </c>
       <c r="D33">
-        <v>1475.185093974404</v>
+        <v>1444.704916185726</v>
       </c>
       <c r="E33">
-        <v>-1645.005099437791</v>
+        <v>-1598.803576257533</v>
       </c>
       <c r="F33">
-        <v>1432.247218587993</v>
+        <v>1478.448741768251</v>
       </c>
       <c r="G33">
         <v>37.3</v>
@@ -3993,37 +3993,37 @@
         <v>118.1</v>
       </c>
       <c r="M33">
-        <v>337.7238941430488</v>
+        <v>348.6182133089536</v>
       </c>
       <c r="N33">
-        <v>-219.6238941430488</v>
+        <v>-230.5182133089536</v>
       </c>
       <c r="O33">
-        <v>-56.66296468890659</v>
+        <v>-59.47369903371003</v>
       </c>
       <c r="P33">
-        <v>-162.9609294541422</v>
+        <v>-171.0445142752436</v>
       </c>
       <c r="Q33">
-        <v>282.1390705458578</v>
+        <v>274.0554857247565</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1005123435689524</v>
+        <v>0.1013169368567311</v>
       </c>
       <c r="T33">
-        <v>1.263564516603982</v>
+        <v>1.282146347730511</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.09022103715022899</v>
+        <v>0.08740162973928432</v>
       </c>
       <c r="W33">
-        <v>0.214525879439976</v>
+        <v>0.2151906957074768</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.349693942442748</v>
+        <v>0.3387660067414121</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1377565396889697</v>
+        <v>0.1396565396889697</v>
       </c>
       <c r="C34">
-        <v>3.556174417474949</v>
+        <v>-71.89146576058943</v>
       </c>
       <c r="D34">
-        <v>1444.704916185726</v>
+        <v>1415.45879918792</v>
       </c>
       <c r="E34">
-        <v>-1598.803576257533</v>
+        <v>-1552.602053077275</v>
       </c>
       <c r="F34">
-        <v>1478.448741768251</v>
+        <v>1524.650264948509</v>
       </c>
       <c r="G34">
         <v>37.3</v>
@@ -4075,37 +4075,37 @@
         <v>118.1</v>
       </c>
       <c r="M34">
-        <v>348.6182133089536</v>
+        <v>359.5125324748584</v>
       </c>
       <c r="N34">
-        <v>-230.5182133089536</v>
+        <v>-241.4125324748584</v>
       </c>
       <c r="O34">
-        <v>-59.47369903371003</v>
+        <v>-62.28443337851346</v>
       </c>
       <c r="P34">
-        <v>-171.0445142752436</v>
+        <v>-179.1280990963449</v>
       </c>
       <c r="Q34">
-        <v>274.0554857247565</v>
+        <v>265.9719009036551</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1013169368567311</v>
+        <v>0.1021455478545928</v>
       </c>
       <c r="T34">
-        <v>1.282146347730511</v>
+        <v>1.301282860383205</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.08740162973928432</v>
+        <v>0.08475309550476057</v>
       </c>
       <c r="W34">
-        <v>0.2151906957074768</v>
+        <v>0.2158152200799774</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3387660067414121</v>
+        <v>0.3285003701734905</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1396565396889697</v>
+        <v>0.1415565396889697</v>
       </c>
       <c r="C35">
-        <v>-71.89146576058943</v>
+        <v>-146.178503801686</v>
       </c>
       <c r="D35">
-        <v>1415.45879918792</v>
+        <v>1387.373284327081</v>
       </c>
       <c r="E35">
-        <v>-1552.602053077275</v>
+        <v>-1506.400529897017</v>
       </c>
       <c r="F35">
-        <v>1524.650264948509</v>
+        <v>1570.851788128767</v>
       </c>
       <c r="G35">
         <v>37.3</v>
@@ -4157,37 +4157,37 @@
         <v>118.1</v>
       </c>
       <c r="M35">
-        <v>359.5125324748584</v>
+        <v>370.4068516407633</v>
       </c>
       <c r="N35">
-        <v>-241.4125324748584</v>
+        <v>-252.3068516407632</v>
       </c>
       <c r="O35">
-        <v>-62.28443337851346</v>
+        <v>-65.09516772331692</v>
       </c>
       <c r="P35">
-        <v>-179.1280990963449</v>
+        <v>-187.2116839174463</v>
       </c>
       <c r="Q35">
-        <v>265.9719009036551</v>
+        <v>257.8883160825537</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1021455478545928</v>
+        <v>0.1029992682766321</v>
       </c>
       <c r="T35">
-        <v>1.301282860383205</v>
+        <v>1.320999267358708</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.08475309550476057</v>
+        <v>0.08226035740167935</v>
       </c>
       <c r="W35">
-        <v>0.2158152200799774</v>
+        <v>0.216403007724684</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3285003701734905</v>
+        <v>0.3188385945801525</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1415565396889697</v>
+        <v>0.1434565396889697</v>
       </c>
       <c r="C36">
-        <v>-146.178503801686</v>
+        <v>-219.3726815303946</v>
       </c>
       <c r="D36">
-        <v>1387.373284327081</v>
+        <v>1360.38062977863</v>
       </c>
       <c r="E36">
-        <v>-1506.400529897017</v>
+        <v>-1460.199006716759</v>
       </c>
       <c r="F36">
-        <v>1570.851788128767</v>
+        <v>1617.053311309025</v>
       </c>
       <c r="G36">
         <v>37.3</v>
@@ -4239,37 +4239,37 @@
         <v>118.1</v>
       </c>
       <c r="M36">
-        <v>370.4068516407633</v>
+        <v>381.301170806668</v>
       </c>
       <c r="N36">
-        <v>-252.3068516407632</v>
+        <v>-263.201170806668</v>
       </c>
       <c r="O36">
-        <v>-65.09516772331692</v>
+        <v>-67.90590206812035</v>
       </c>
       <c r="P36">
-        <v>-187.2116839174463</v>
+        <v>-195.2952687385477</v>
       </c>
       <c r="Q36">
-        <v>257.8883160825537</v>
+        <v>249.8047312614524</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1029992682766321</v>
+        <v>0.1038792570193495</v>
       </c>
       <c r="T36">
-        <v>1.320999267358708</v>
+        <v>1.341322333010381</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.08226035740167935</v>
+        <v>0.0799100614759171</v>
       </c>
       <c r="W36">
-        <v>0.216403007724684</v>
+        <v>0.2169572075039788</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3188385945801525</v>
+        <v>0.309728920449291</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1434565396889697</v>
+        <v>0.1453565396889697</v>
       </c>
       <c r="C37">
-        <v>-219.3726815303946</v>
+        <v>-291.5365694599143</v>
       </c>
       <c r="D37">
-        <v>1360.38062977863</v>
+        <v>1334.418265029368</v>
       </c>
       <c r="E37">
-        <v>-1460.199006716759</v>
+        <v>-1413.997483536501</v>
       </c>
       <c r="F37">
-        <v>1617.053311309025</v>
+        <v>1663.254834489283</v>
       </c>
       <c r="G37">
         <v>37.3</v>
@@ -4321,37 +4321,37 @@
         <v>118.1</v>
       </c>
       <c r="M37">
-        <v>381.301170806668</v>
+        <v>392.1954899725728</v>
       </c>
       <c r="N37">
-        <v>-263.201170806668</v>
+        <v>-274.0954899725728</v>
       </c>
       <c r="O37">
-        <v>-67.90590206812035</v>
+        <v>-70.71663641292379</v>
       </c>
       <c r="P37">
-        <v>-195.2952687385477</v>
+        <v>-203.378853559649</v>
       </c>
       <c r="Q37">
-        <v>249.8047312614524</v>
+        <v>241.721146440351</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1038792570193495</v>
+        <v>0.1047867454102768</v>
       </c>
       <c r="T37">
-        <v>1.341322333010381</v>
+        <v>1.362280494463668</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0799100614759171</v>
+        <v>0.07769033754603051</v>
       </c>
       <c r="W37">
-        <v>0.2169572075039788</v>
+        <v>0.217480618406646</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.309728920449291</v>
+        <v>0.3011253393256996</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1453565396889697</v>
+        <v>0.1472565396889697</v>
       </c>
       <c r="C38">
-        <v>-291.5365694599141</v>
+        <v>-362.7280510137621</v>
       </c>
       <c r="D38">
-        <v>1334.418265029368</v>
+        <v>1309.428306655778</v>
       </c>
       <c r="E38">
-        <v>-1413.997483536502</v>
+        <v>-1367.795960356244</v>
       </c>
       <c r="F38">
-        <v>1663.254834489282</v>
+        <v>1709.45635766954</v>
       </c>
       <c r="G38">
         <v>37.3</v>
@@ -4403,37 +4403,37 @@
         <v>118.1</v>
       </c>
       <c r="M38">
-        <v>392.1954899725728</v>
+        <v>403.0898091384776</v>
       </c>
       <c r="N38">
-        <v>-274.0954899725728</v>
+        <v>-284.9898091384776</v>
       </c>
       <c r="O38">
-        <v>-70.71663641292378</v>
+        <v>-73.52737075772723</v>
       </c>
       <c r="P38">
-        <v>-203.378853559649</v>
+        <v>-211.4624383807504</v>
       </c>
       <c r="Q38">
-        <v>241.721146440351</v>
+        <v>233.6375616192497</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1047867454102768</v>
+        <v>0.1057230429564717</v>
       </c>
       <c r="T38">
-        <v>1.362280494463668</v>
+        <v>1.383903994375789</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07769033754603052</v>
+        <v>0.0755905986934351</v>
       </c>
       <c r="W38">
-        <v>0.217480618406646</v>
+        <v>0.217975736828088</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3011253393256996</v>
+        <v>0.2929868166412213</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1472565396889697</v>
+        <v>0.1491565396889697</v>
       </c>
       <c r="C39">
-        <v>-362.7280510137621</v>
+        <v>-433.0007533388793</v>
       </c>
       <c r="D39">
-        <v>1309.428306655778</v>
+        <v>1285.357127510919</v>
       </c>
       <c r="E39">
-        <v>-1367.795960356244</v>
+        <v>-1321.594437175986</v>
       </c>
       <c r="F39">
-        <v>1709.45635766954</v>
+        <v>1755.657880849798</v>
       </c>
       <c r="G39">
         <v>37.3</v>
@@ -4485,37 +4485,37 @@
         <v>118.1</v>
       </c>
       <c r="M39">
-        <v>403.0898091384776</v>
+        <v>413.9841283043824</v>
       </c>
       <c r="N39">
-        <v>-284.9898091384776</v>
+        <v>-295.8841283043824</v>
       </c>
       <c r="O39">
-        <v>-73.52737075772723</v>
+        <v>-76.33810510253066</v>
       </c>
       <c r="P39">
-        <v>-211.4624383807504</v>
+        <v>-219.5460232018517</v>
       </c>
       <c r="Q39">
-        <v>233.6375616192497</v>
+        <v>225.5539767981483</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1057230429564717</v>
+        <v>0.106689543649318</v>
       </c>
       <c r="T39">
-        <v>1.383903994375789</v>
+        <v>1.406225026543141</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0755905986934351</v>
+        <v>0.07360137241202891</v>
       </c>
       <c r="W39">
-        <v>0.217975736828088</v>
+        <v>0.2184447963852436</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2929868166412213</v>
+        <v>0.285276637255926</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1491565396889697</v>
+        <v>0.1510565396889697</v>
       </c>
       <c r="C40">
-        <v>-433.0007533388793</v>
+        <v>-502.4044314587477</v>
       </c>
       <c r="D40">
-        <v>1285.357127510919</v>
+        <v>1262.154972571308</v>
       </c>
       <c r="E40">
-        <v>-1321.594437175986</v>
+        <v>-1275.392913995728</v>
       </c>
       <c r="F40">
-        <v>1755.657880849798</v>
+        <v>1801.859404030056</v>
       </c>
       <c r="G40">
         <v>37.3</v>
@@ -4567,37 +4567,37 @@
         <v>118.1</v>
       </c>
       <c r="M40">
-        <v>413.9841283043824</v>
+        <v>424.8784474702873</v>
       </c>
       <c r="N40">
-        <v>-295.8841283043824</v>
+        <v>-306.7784474702872</v>
       </c>
       <c r="O40">
-        <v>-76.33810510253066</v>
+        <v>-79.14883944733411</v>
       </c>
       <c r="P40">
-        <v>-219.5460232018517</v>
+        <v>-227.6296080229531</v>
       </c>
       <c r="Q40">
-        <v>225.5539767981483</v>
+        <v>217.4703919770469</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.106689543649318</v>
+        <v>0.1076877328894707</v>
       </c>
       <c r="T40">
-        <v>1.406225026543141</v>
+        <v>1.429277895830733</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07360137241202891</v>
+        <v>0.07171415773479738</v>
       </c>
       <c r="W40">
-        <v>0.2184447963852436</v>
+        <v>0.2188898016061348</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.285276637255926</v>
+        <v>0.2779618516852612</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1510565396889697</v>
+        <v>0.1529565396889697</v>
       </c>
       <c r="C41">
-        <v>-502.4044314587477</v>
+        <v>-570.9853115578285</v>
       </c>
       <c r="D41">
-        <v>1262.154972571308</v>
+        <v>1239.775615652485</v>
       </c>
       <c r="E41">
-        <v>-1275.392913995728</v>
+        <v>-1229.19139081547</v>
       </c>
       <c r="F41">
-        <v>1801.859404030056</v>
+        <v>1848.060927210314</v>
       </c>
       <c r="G41">
         <v>37.3</v>
@@ -4649,37 +4649,37 @@
         <v>118.1</v>
       </c>
       <c r="M41">
-        <v>424.8784474702873</v>
+        <v>435.772766636192</v>
       </c>
       <c r="N41">
-        <v>-306.7784474702872</v>
+        <v>-317.672766636192</v>
       </c>
       <c r="O41">
-        <v>-79.14883944733411</v>
+        <v>-81.95957379213753</v>
       </c>
       <c r="P41">
-        <v>-227.6296080229531</v>
+        <v>-235.7131928440544</v>
       </c>
       <c r="Q41">
-        <v>217.4703919770469</v>
+        <v>209.3868071559456</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1076877328894707</v>
+        <v>0.1087191951042953</v>
       </c>
       <c r="T41">
-        <v>1.429277895830733</v>
+        <v>1.453099194094579</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07171415773479738</v>
+        <v>0.06992130379142747</v>
       </c>
       <c r="W41">
-        <v>0.2188898016061348</v>
+        <v>0.2193125565659814</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2779618516852612</v>
+        <v>0.2710128053931297</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1529565396889697</v>
+        <v>0.1548565396889697</v>
       </c>
       <c r="C42">
-        <v>-570.9853115578285</v>
+        <v>-638.7863983814759</v>
       </c>
       <c r="D42">
-        <v>1239.775615652485</v>
+        <v>1218.176052009096</v>
       </c>
       <c r="E42">
-        <v>-1229.19139081547</v>
+        <v>-1182.989867635212</v>
       </c>
       <c r="F42">
-        <v>1848.060927210314</v>
+        <v>1894.262450390572</v>
       </c>
       <c r="G42">
         <v>37.3</v>
@@ -4731,37 +4731,37 @@
         <v>118.1</v>
       </c>
       <c r="M42">
-        <v>435.772766636192</v>
+        <v>446.6670858020968</v>
       </c>
       <c r="N42">
-        <v>-317.672766636192</v>
+        <v>-328.5670858020968</v>
       </c>
       <c r="O42">
-        <v>-81.95957379213753</v>
+        <v>-84.77030813694098</v>
       </c>
       <c r="P42">
-        <v>-235.7131928440544</v>
+        <v>-243.7967776651558</v>
       </c>
       <c r="Q42">
-        <v>209.3868071559456</v>
+        <v>201.3032223348442</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1087191951042953</v>
+        <v>0.1097856221399613</v>
       </c>
       <c r="T42">
-        <v>1.453099194094579</v>
+        <v>1.477727993994487</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06992130379142747</v>
+        <v>0.068215906137978</v>
       </c>
       <c r="W42">
-        <v>0.2193125565659814</v>
+        <v>0.2197146893326648</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2710128053931297</v>
+        <v>0.264402736968907</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1548565396889697</v>
+        <v>0.1567565396889697</v>
       </c>
       <c r="C43">
-        <v>-638.7863983814759</v>
+        <v>-705.84775105268</v>
       </c>
       <c r="D43">
-        <v>1218.176052009096</v>
+        <v>1197.31622251815</v>
       </c>
       <c r="E43">
-        <v>-1182.989867635212</v>
+        <v>-1136.788344454954</v>
       </c>
       <c r="F43">
-        <v>1894.262450390572</v>
+        <v>1940.46397357083</v>
       </c>
       <c r="G43">
         <v>37.3</v>
@@ -4813,37 +4813,37 @@
         <v>118.1</v>
       </c>
       <c r="M43">
-        <v>446.6670858020968</v>
+        <v>457.5614049680017</v>
       </c>
       <c r="N43">
-        <v>-328.5670858020968</v>
+        <v>-339.4614049680017</v>
       </c>
       <c r="O43">
-        <v>-84.77030813694098</v>
+        <v>-87.58104248174443</v>
       </c>
       <c r="P43">
-        <v>-243.7967776651558</v>
+        <v>-251.8803624862572</v>
       </c>
       <c r="Q43">
-        <v>201.3032223348442</v>
+        <v>193.2196375137428</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1097856221399613</v>
+        <v>0.1108888225216847</v>
       </c>
       <c r="T43">
-        <v>1.477727993994487</v>
+        <v>1.503206062856461</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.068215906137978</v>
+        <v>0.06659171789659757</v>
       </c>
       <c r="W43">
-        <v>0.2197146893326648</v>
+        <v>0.2200976729199823</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.264402736968907</v>
+        <v>0.2581074337077425</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1567565396889697</v>
+        <v>0.1586565396889697</v>
       </c>
       <c r="C44">
-        <v>-705.8477510526798</v>
+        <v>-772.2067310276793</v>
       </c>
       <c r="D44">
-        <v>1197.31622251815</v>
+        <v>1177.158765723408</v>
       </c>
       <c r="E44">
-        <v>-1136.788344454955</v>
+        <v>-1090.586821274697</v>
       </c>
       <c r="F44">
-        <v>1940.463973570829</v>
+        <v>1986.665496751087</v>
       </c>
       <c r="G44">
         <v>37.3</v>
@@ -4895,37 +4895,37 @@
         <v>118.1</v>
       </c>
       <c r="M44">
-        <v>457.5614049680016</v>
+        <v>468.4557241339064</v>
       </c>
       <c r="N44">
-        <v>-339.4614049680016</v>
+        <v>-350.3557241339064</v>
       </c>
       <c r="O44">
-        <v>-87.58104248174442</v>
+        <v>-90.39177682654785</v>
       </c>
       <c r="P44">
-        <v>-251.8803624862572</v>
+        <v>-259.9639473073585</v>
       </c>
       <c r="Q44">
-        <v>193.2196375137428</v>
+        <v>185.1360526926415</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1108888225216847</v>
+        <v>0.1120307316887318</v>
       </c>
       <c r="T44">
-        <v>1.503206062856461</v>
+        <v>1.529578099046925</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06659171789659757</v>
+        <v>0.06504307329435112</v>
       </c>
       <c r="W44">
-        <v>0.2200976729199823</v>
+        <v>0.220462843317192</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2581074337077426</v>
+        <v>0.252104935249423</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1586565396889697</v>
+        <v>0.1605565396889697</v>
       </c>
       <c r="C45">
-        <v>-772.2067310276793</v>
+        <v>-837.8982254194816</v>
       </c>
       <c r="D45">
-        <v>1177.158765723408</v>
+        <v>1157.668794511864</v>
       </c>
       <c r="E45">
-        <v>-1090.586821274697</v>
+        <v>-1044.385298094439</v>
       </c>
       <c r="F45">
-        <v>1986.665496751087</v>
+        <v>2032.867019931345</v>
       </c>
       <c r="G45">
         <v>37.3</v>
@@ -4977,37 +4977,37 @@
         <v>118.1</v>
       </c>
       <c r="M45">
-        <v>468.4557241339064</v>
+        <v>479.3500432998112</v>
       </c>
       <c r="N45">
-        <v>-350.3557241339064</v>
+        <v>-361.2500432998112</v>
       </c>
       <c r="O45">
-        <v>-90.39177682654785</v>
+        <v>-93.20251117135129</v>
       </c>
       <c r="P45">
-        <v>-259.9639473073585</v>
+        <v>-268.0475321284599</v>
       </c>
       <c r="Q45">
-        <v>185.1360526926415</v>
+        <v>177.0524678715401</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1120307316887318</v>
+        <v>0.1132134233260306</v>
       </c>
       <c r="T45">
-        <v>1.529578099046925</v>
+        <v>1.556891993672763</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06504307329435112</v>
+        <v>0.06356482162857043</v>
       </c>
       <c r="W45">
-        <v>0.220462843317192</v>
+        <v>0.2208114150599831</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.252104935249423</v>
+        <v>0.2463752776301179</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1605565396889697</v>
+        <v>0.1624565396889697</v>
       </c>
       <c r="C46">
-        <v>-837.8982254194816</v>
+        <v>-902.9548484975858</v>
       </c>
       <c r="D46">
-        <v>1157.668794511864</v>
+        <v>1138.813694614017</v>
       </c>
       <c r="E46">
-        <v>-1044.385298094439</v>
+        <v>-998.183774914181</v>
       </c>
       <c r="F46">
-        <v>2032.867019931345</v>
+        <v>2079.068543111603</v>
       </c>
       <c r="G46">
         <v>37.3</v>
@@ -5059,37 +5059,37 @@
         <v>118.1</v>
       </c>
       <c r="M46">
-        <v>479.3500432998112</v>
+        <v>490.244362465716</v>
       </c>
       <c r="N46">
-        <v>-361.2500432998112</v>
+        <v>-372.144362465716</v>
       </c>
       <c r="O46">
-        <v>-93.20251117135129</v>
+        <v>-96.01324551615473</v>
       </c>
       <c r="P46">
-        <v>-268.0475321284599</v>
+        <v>-276.1311169495613</v>
       </c>
       <c r="Q46">
-        <v>177.0524678715401</v>
+        <v>168.9688830504388</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1132134233260306</v>
+        <v>0.1144391219319585</v>
       </c>
       <c r="T46">
-        <v>1.556891993672763</v>
+        <v>1.58519912083045</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06356482162857043</v>
+        <v>0.06215227003682441</v>
       </c>
       <c r="W46">
-        <v>0.2208114150599831</v>
+        <v>0.2211444947253168</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2463752776301179</v>
+        <v>0.2409002714605597</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1624565396889697</v>
+        <v>0.1643565396889697</v>
       </c>
       <c r="C47">
-        <v>-902.9548484975858</v>
+        <v>-967.4071238121685</v>
       </c>
       <c r="D47">
-        <v>1138.813694614017</v>
+        <v>1120.562942479693</v>
       </c>
       <c r="E47">
-        <v>-998.183774914181</v>
+        <v>-951.982251733923</v>
       </c>
       <c r="F47">
-        <v>2079.068543111603</v>
+        <v>2125.270066291861</v>
       </c>
       <c r="G47">
         <v>37.3</v>
@@ -5141,37 +5141,37 @@
         <v>118.1</v>
       </c>
       <c r="M47">
-        <v>490.244362465716</v>
+        <v>501.1386816316208</v>
       </c>
       <c r="N47">
-        <v>-372.144362465716</v>
+        <v>-383.0386816316208</v>
       </c>
       <c r="O47">
-        <v>-96.01324551615473</v>
+        <v>-98.82397986095818</v>
       </c>
       <c r="P47">
-        <v>-276.1311169495613</v>
+        <v>-284.2147017706627</v>
       </c>
       <c r="Q47">
-        <v>168.9688830504388</v>
+        <v>160.8852982293374</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1144391219319585</v>
+        <v>0.1157102167825503</v>
       </c>
       <c r="T47">
-        <v>1.58519912083045</v>
+        <v>1.614554660105088</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06215227003682441</v>
+        <v>0.06080113373167605</v>
       </c>
       <c r="W47">
-        <v>0.2211444947253168</v>
+        <v>0.2214630926660708</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2409002714605597</v>
+        <v>0.2356633090375041</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1643565396889697</v>
+        <v>0.1662565396889698</v>
       </c>
       <c r="C48">
-        <v>-967.4071238121685</v>
+        <v>-1031.28364908205</v>
       </c>
       <c r="D48">
-        <v>1120.562942479693</v>
+        <v>1102.887940390068</v>
       </c>
       <c r="E48">
-        <v>-951.982251733923</v>
+        <v>-905.7807285536651</v>
       </c>
       <c r="F48">
-        <v>2125.270066291861</v>
+        <v>2171.471589472119</v>
       </c>
       <c r="G48">
         <v>37.3</v>
@@ -5223,37 +5223,37 @@
         <v>118.1</v>
       </c>
       <c r="M48">
-        <v>501.1386816316208</v>
+        <v>512.0330007975257</v>
       </c>
       <c r="N48">
-        <v>-383.0386816316208</v>
+        <v>-393.9330007975257</v>
       </c>
       <c r="O48">
-        <v>-98.82397986095818</v>
+        <v>-101.6347142057616</v>
       </c>
       <c r="P48">
-        <v>-284.2147017706627</v>
+        <v>-292.2982865917641</v>
       </c>
       <c r="Q48">
-        <v>160.8852982293374</v>
+        <v>152.801713408236</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1157102167825503</v>
+        <v>0.1170292774765607</v>
       </c>
       <c r="T48">
-        <v>1.614554660105088</v>
+        <v>1.645017955578769</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06080113373167605</v>
+        <v>0.0595074925884489</v>
       </c>
       <c r="W48">
-        <v>0.2214630926660708</v>
+        <v>0.2217681332476438</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2356633090375041</v>
+        <v>0.2306491960792593</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1662565396889698</v>
+        <v>0.1681565396889697</v>
       </c>
       <c r="C49">
-        <v>-1031.28364908205</v>
+        <v>-1094.611245719991</v>
       </c>
       <c r="D49">
-        <v>1102.887940390068</v>
+        <v>1085.761866932386</v>
       </c>
       <c r="E49">
-        <v>-905.7807285536651</v>
+        <v>-859.5792053734071</v>
       </c>
       <c r="F49">
-        <v>2171.471589472119</v>
+        <v>2217.673112652377</v>
       </c>
       <c r="G49">
         <v>37.3</v>
@@ -5305,37 +5305,37 @@
         <v>118.1</v>
       </c>
       <c r="M49">
-        <v>512.0330007975257</v>
+        <v>522.9273199634305</v>
       </c>
       <c r="N49">
-        <v>-393.9330007975257</v>
+        <v>-404.8273199634305</v>
       </c>
       <c r="O49">
-        <v>-101.6347142057616</v>
+        <v>-104.4454485505651</v>
       </c>
       <c r="P49">
-        <v>-292.2982865917641</v>
+        <v>-300.3818714128654</v>
       </c>
       <c r="Q49">
-        <v>152.801713408236</v>
+        <v>144.7181285871346</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1170292774765607</v>
+        <v>0.1183990712741868</v>
       </c>
       <c r="T49">
-        <v>1.645017955578769</v>
+        <v>1.676652916262976</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0595074925884489</v>
+        <v>0.05826775315952288</v>
       </c>
       <c r="W49">
-        <v>0.2217681332476438</v>
+        <v>0.2220604638049845</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2306491960792593</v>
+        <v>0.2258440044942747</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1681565396889697</v>
+        <v>0.1700565396889697</v>
       </c>
       <c r="C50">
-        <v>-1094.61124571999</v>
+        <v>-1157.415094639685</v>
       </c>
       <c r="D50">
-        <v>1085.761866932386</v>
+        <v>1069.159541192949</v>
       </c>
       <c r="E50">
-        <v>-859.5792053734076</v>
+        <v>-813.3776821931497</v>
       </c>
       <c r="F50">
-        <v>2217.673112652376</v>
+        <v>2263.874635832634</v>
       </c>
       <c r="G50">
         <v>37.3</v>
@@ -5387,37 +5387,37 @@
         <v>118.1</v>
       </c>
       <c r="M50">
-        <v>522.9273199634304</v>
+        <v>533.8216391293352</v>
       </c>
       <c r="N50">
-        <v>-404.8273199634303</v>
+        <v>-415.7216391293351</v>
       </c>
       <c r="O50">
-        <v>-104.445448550565</v>
+        <v>-107.2561828953685</v>
       </c>
       <c r="P50">
-        <v>-300.3818714128653</v>
+        <v>-308.4654562339667</v>
       </c>
       <c r="Q50">
-        <v>144.7181285871347</v>
+        <v>136.6345437660333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1183990712741868</v>
+        <v>0.1198225824756415</v>
       </c>
       <c r="T50">
-        <v>1.676652916262976</v>
+        <v>1.709528463640681</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05826775315952289</v>
+        <v>0.05707861533994079</v>
       </c>
       <c r="W50">
-        <v>0.2220604638049845</v>
+        <v>0.222340862502842</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2258440044942748</v>
+        <v>0.221234943178065</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1700565396889697</v>
+        <v>0.1719565396889697</v>
       </c>
       <c r="C51">
-        <v>-1157.415094639685</v>
+        <v>-1219.718859790711</v>
       </c>
       <c r="D51">
-        <v>1069.159541192949</v>
+        <v>1053.057299222181</v>
       </c>
       <c r="E51">
-        <v>-813.3776821931497</v>
+        <v>-767.1761590128917</v>
       </c>
       <c r="F51">
-        <v>2263.874635832634</v>
+        <v>2310.076159012892</v>
       </c>
       <c r="G51">
         <v>37.3</v>
@@ -5469,37 +5469,37 @@
         <v>118.1</v>
       </c>
       <c r="M51">
-        <v>533.8216391293352</v>
+        <v>544.7159582952401</v>
       </c>
       <c r="N51">
-        <v>-415.7216391293351</v>
+        <v>-426.61595829524</v>
       </c>
       <c r="O51">
-        <v>-107.2561828953685</v>
+        <v>-110.0669172401719</v>
       </c>
       <c r="P51">
-        <v>-308.4654562339667</v>
+        <v>-316.5490410550681</v>
       </c>
       <c r="Q51">
-        <v>136.6345437660333</v>
+        <v>128.5509589449319</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1198225824756415</v>
+        <v>0.1213030341251543</v>
       </c>
       <c r="T51">
-        <v>1.709528463640681</v>
+        <v>1.743719032913494</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05707861533994079</v>
+        <v>0.05593704303314197</v>
       </c>
       <c r="W51">
-        <v>0.222340862502842</v>
+        <v>0.2226100452527851</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.221234943178065</v>
+        <v>0.2168102443145037</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1719565396889697</v>
+        <v>0.1738565396889697</v>
       </c>
       <c r="C52">
-        <v>-1219.718859790711</v>
+        <v>-1281.544800695997</v>
       </c>
       <c r="D52">
-        <v>1053.057299222181</v>
+        <v>1037.432881497153</v>
       </c>
       <c r="E52">
-        <v>-767.1761590128917</v>
+        <v>-720.9746358326338</v>
       </c>
       <c r="F52">
-        <v>2310.076159012892</v>
+        <v>2356.27768219315</v>
       </c>
       <c r="G52">
         <v>37.3</v>
@@ -5551,37 +5551,37 @@
         <v>118.1</v>
       </c>
       <c r="M52">
-        <v>544.7159582952401</v>
+        <v>555.6102774611448</v>
       </c>
       <c r="N52">
-        <v>-426.61595829524</v>
+        <v>-437.5102774611448</v>
       </c>
       <c r="O52">
-        <v>-110.0669172401719</v>
+        <v>-112.8776515849754</v>
       </c>
       <c r="P52">
-        <v>-316.5490410550681</v>
+        <v>-324.6326258761695</v>
       </c>
       <c r="Q52">
-        <v>128.5509589449319</v>
+        <v>120.4673741238306</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1213030341251543</v>
+        <v>0.1228439123726064</v>
       </c>
       <c r="T52">
-        <v>1.743719032913494</v>
+        <v>1.779305135626015</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05593704303314197</v>
+        <v>0.05484023826778624</v>
       </c>
       <c r="W52">
-        <v>0.2226100452527851</v>
+        <v>0.222868671816456</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2168102443145037</v>
+        <v>0.2125590630534351</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1738565396889697</v>
+        <v>0.1757565396889697</v>
       </c>
       <c r="C53">
-        <v>-1281.544800695997</v>
+        <v>-1342.913875117325</v>
       </c>
       <c r="D53">
-        <v>1037.432881497153</v>
+        <v>1022.265330256083</v>
       </c>
       <c r="E53">
-        <v>-720.9746358326338</v>
+        <v>-674.7731126523759</v>
       </c>
       <c r="F53">
-        <v>2356.27768219315</v>
+        <v>2402.479205373408</v>
       </c>
       <c r="G53">
         <v>37.3</v>
@@ -5633,37 +5633,37 @@
         <v>118.1</v>
       </c>
       <c r="M53">
-        <v>555.6102774611448</v>
+        <v>566.5045966270496</v>
       </c>
       <c r="N53">
-        <v>-437.5102774611448</v>
+        <v>-448.4045966270496</v>
       </c>
       <c r="O53">
-        <v>-112.8776515849754</v>
+        <v>-115.6883859297788</v>
       </c>
       <c r="P53">
-        <v>-324.6326258761695</v>
+        <v>-332.7162106972708</v>
       </c>
       <c r="Q53">
-        <v>120.4673741238306</v>
+        <v>112.3837893027292</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1228439123726064</v>
+        <v>0.1244489938803691</v>
       </c>
       <c r="T53">
-        <v>1.779305135626015</v>
+        <v>1.816373992618224</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05484023826778624</v>
+        <v>0.05378561830109805</v>
       </c>
       <c r="W53">
-        <v>0.222868671816456</v>
+        <v>0.2231173512046011</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2125590630534351</v>
+        <v>0.2084713887639459</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1757565396889697</v>
+        <v>0.1776565396889697</v>
       </c>
       <c r="C54">
-        <v>-1342.913875117325</v>
+        <v>-1403.845832844616</v>
       </c>
       <c r="D54">
-        <v>1022.265330256083</v>
+        <v>1007.53489570905</v>
       </c>
       <c r="E54">
-        <v>-674.7731126523759</v>
+        <v>-628.5715894721179</v>
       </c>
       <c r="F54">
-        <v>2402.479205373408</v>
+        <v>2448.680728553666</v>
       </c>
       <c r="G54">
         <v>37.3</v>
@@ -5715,37 +5715,37 @@
         <v>118.1</v>
       </c>
       <c r="M54">
-        <v>566.5045966270496</v>
+        <v>577.3989157929545</v>
       </c>
       <c r="N54">
-        <v>-448.4045966270496</v>
+        <v>-459.2989157929545</v>
       </c>
       <c r="O54">
-        <v>-115.6883859297788</v>
+        <v>-118.4991202745823</v>
       </c>
       <c r="P54">
-        <v>-332.7162106972708</v>
+        <v>-340.7997955183723</v>
       </c>
       <c r="Q54">
-        <v>112.3837893027292</v>
+        <v>104.3002044816278</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1244489938803691</v>
+        <v>0.1261223767288876</v>
       </c>
       <c r="T54">
-        <v>1.816373992618224</v>
+        <v>1.855020247780313</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05378561830109805</v>
+        <v>0.05277079531428486</v>
       </c>
       <c r="W54">
-        <v>0.2231173512046011</v>
+        <v>0.2233566464648916</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2084713887639459</v>
+        <v>0.2045379663344374</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1776565396889697</v>
+        <v>0.1795565396889697</v>
       </c>
       <c r="C55">
-        <v>-1403.845832844616</v>
+        <v>-1464.359301491605</v>
       </c>
       <c r="D55">
-        <v>1007.53489570905</v>
+        <v>993.2229502423194</v>
       </c>
       <c r="E55">
-        <v>-628.5715894721179</v>
+        <v>-582.37006629186</v>
       </c>
       <c r="F55">
-        <v>2448.680728553666</v>
+        <v>2494.882251733924</v>
       </c>
       <c r="G55">
         <v>37.3</v>
@@ -5797,37 +5797,37 @@
         <v>118.1</v>
       </c>
       <c r="M55">
-        <v>577.3989157929545</v>
+        <v>588.2932349588593</v>
       </c>
       <c r="N55">
-        <v>-459.2989157929545</v>
+        <v>-470.1932349588593</v>
       </c>
       <c r="O55">
-        <v>-118.4991202745823</v>
+        <v>-121.3098546193857</v>
       </c>
       <c r="P55">
-        <v>-340.7997955183723</v>
+        <v>-348.8833803394736</v>
       </c>
       <c r="Q55">
-        <v>104.3002044816278</v>
+        <v>96.21661966052642</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1261223767288876</v>
+        <v>0.1278685153534286</v>
       </c>
       <c r="T55">
-        <v>1.855020247780313</v>
+        <v>1.895346774905972</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05277079531428486</v>
+        <v>0.05179355836402033</v>
       </c>
       <c r="W55">
-        <v>0.2233566464648916</v>
+        <v>0.223587078937764</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2045379663344374</v>
+        <v>0.200750226217133</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1795565396889697</v>
+        <v>0.1814565396889697</v>
       </c>
       <c r="C56">
-        <v>-1464.359301491605</v>
+        <v>-1524.471865081614</v>
       </c>
       <c r="D56">
-        <v>993.2229502423194</v>
+        <v>979.3119098325673</v>
       </c>
       <c r="E56">
-        <v>-582.37006629186</v>
+        <v>-536.1685431116025</v>
       </c>
       <c r="F56">
-        <v>2494.882251733924</v>
+        <v>2541.083774914182</v>
       </c>
       <c r="G56">
         <v>37.3</v>
@@ -5879,37 +5879,37 @@
         <v>118.1</v>
       </c>
       <c r="M56">
-        <v>588.2932349588593</v>
+        <v>599.187554124764</v>
       </c>
       <c r="N56">
-        <v>-470.1932349588593</v>
+        <v>-481.087554124764</v>
       </c>
       <c r="O56">
-        <v>-121.3098546193857</v>
+        <v>-124.1205889641891</v>
       </c>
       <c r="P56">
-        <v>-348.8833803394736</v>
+        <v>-356.9669651605749</v>
       </c>
       <c r="Q56">
-        <v>96.21661966052642</v>
+        <v>88.13303483942514</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1278685153534286</v>
+        <v>0.1296922601390604</v>
       </c>
       <c r="T56">
-        <v>1.895346774905972</v>
+        <v>1.937465592126105</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05179355836402033</v>
+        <v>0.05085185730285633</v>
       </c>
       <c r="W56">
-        <v>0.223587078937764</v>
+        <v>0.2238091320479865</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.200750226217133</v>
+        <v>0.1971002221040943</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1814565396889697</v>
+        <v>0.1833565396889697</v>
       </c>
       <c r="C57">
-        <v>-1524.471865081614</v>
+        <v>-1584.200136120528</v>
       </c>
       <c r="D57">
-        <v>979.3119098325673</v>
+        <v>965.7851619739114</v>
       </c>
       <c r="E57">
-        <v>-536.1685431116025</v>
+        <v>-489.9670199313446</v>
       </c>
       <c r="F57">
-        <v>2541.083774914182</v>
+        <v>2587.285298094439</v>
       </c>
       <c r="G57">
         <v>37.3</v>
@@ -5961,37 +5961,37 @@
         <v>118.1</v>
       </c>
       <c r="M57">
-        <v>599.187554124764</v>
+        <v>610.0818732906688</v>
       </c>
       <c r="N57">
-        <v>-481.087554124764</v>
+        <v>-491.9818732906688</v>
       </c>
       <c r="O57">
-        <v>-124.1205889641891</v>
+        <v>-126.9313233089925</v>
       </c>
       <c r="P57">
-        <v>-356.9669651605749</v>
+        <v>-365.0505499816762</v>
       </c>
       <c r="Q57">
-        <v>88.13303483942514</v>
+        <v>80.0494500183238</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1296922601390604</v>
+        <v>0.1315989024149481</v>
       </c>
       <c r="T57">
-        <v>1.937465592126105</v>
+        <v>1.981498901038062</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05085185730285633</v>
+        <v>0.04994378842244819</v>
       </c>
       <c r="W57">
-        <v>0.2238091320479865</v>
+        <v>0.2240232546899867</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1971002221040943</v>
+        <v>0.193580575280807</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1833565396889697</v>
+        <v>0.1852565396889697</v>
       </c>
       <c r="C58">
-        <v>-1584.200136120528</v>
+        <v>-1643.559821778093</v>
       </c>
       <c r="D58">
-        <v>965.7851619739114</v>
+        <v>952.6269994966045</v>
       </c>
       <c r="E58">
-        <v>-489.9670199313446</v>
+        <v>-443.7654967510866</v>
       </c>
       <c r="F58">
-        <v>2587.285298094439</v>
+        <v>2633.486821274697</v>
       </c>
       <c r="G58">
         <v>37.3</v>
@@ -6043,37 +6043,37 @@
         <v>118.1</v>
       </c>
       <c r="M58">
-        <v>610.0818732906688</v>
+        <v>620.9761924565737</v>
       </c>
       <c r="N58">
-        <v>-491.9818732906688</v>
+        <v>-502.8761924565737</v>
       </c>
       <c r="O58">
-        <v>-126.9313233089925</v>
+        <v>-129.742057653796</v>
       </c>
       <c r="P58">
-        <v>-365.0505499816762</v>
+        <v>-373.1341348027777</v>
       </c>
       <c r="Q58">
-        <v>80.0494500183238</v>
+        <v>71.96586519722234</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1315989024149481</v>
+        <v>0.1335942257269236</v>
       </c>
       <c r="T58">
-        <v>1.981498901038062</v>
+        <v>2.027580270829645</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04994378842244819</v>
+        <v>0.04906758160801926</v>
       </c>
       <c r="W58">
-        <v>0.2240232546899867</v>
+        <v>0.2242298642568291</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.193580575280807</v>
+        <v>0.1901844248372839</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1852565396889697</v>
+        <v>0.1871565396889697</v>
       </c>
       <c r="C59">
-        <v>-1643.559821778093</v>
+        <v>-1702.565784731892</v>
       </c>
       <c r="D59">
-        <v>952.6269994966045</v>
+        <v>939.8225597230636</v>
       </c>
       <c r="E59">
-        <v>-443.7654967510866</v>
+        <v>-397.5639735708287</v>
       </c>
       <c r="F59">
-        <v>2633.486821274697</v>
+        <v>2679.688344454955</v>
       </c>
       <c r="G59">
         <v>37.3</v>
@@ -6125,37 +6125,37 @@
         <v>118.1</v>
       </c>
       <c r="M59">
-        <v>620.9761924565737</v>
+        <v>631.8705116224785</v>
       </c>
       <c r="N59">
-        <v>-502.8761924565737</v>
+        <v>-513.7705116224785</v>
       </c>
       <c r="O59">
-        <v>-129.742057653796</v>
+        <v>-132.5527919985994</v>
       </c>
       <c r="P59">
-        <v>-373.1341348027777</v>
+        <v>-381.217719623879</v>
       </c>
       <c r="Q59">
-        <v>71.96586519722234</v>
+        <v>63.882280376121</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1335942257269236</v>
+        <v>0.1356845644347075</v>
       </c>
       <c r="T59">
-        <v>2.027580270829645</v>
+        <v>2.075855991563684</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04906758160801926</v>
+        <v>0.04822158882167411</v>
       </c>
       <c r="W59">
-        <v>0.2242298642568291</v>
+        <v>0.2244293493558492</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1901844248372839</v>
+        <v>0.1869053830297446</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1871565396889697</v>
+        <v>0.1890565396889697</v>
       </c>
       <c r="C60">
-        <v>-1702.565784731891</v>
+        <v>-1761.232099169503</v>
       </c>
       <c r="D60">
-        <v>939.8225597230642</v>
+        <v>927.3577684657101</v>
       </c>
       <c r="E60">
-        <v>-397.5639735708291</v>
+        <v>-351.3624503905712</v>
       </c>
       <c r="F60">
-        <v>2679.688344454955</v>
+        <v>2725.889867635213</v>
       </c>
       <c r="G60">
         <v>37.3</v>
@@ -6207,37 +6207,37 @@
         <v>118.1</v>
       </c>
       <c r="M60">
-        <v>631.8705116224784</v>
+        <v>642.7648307883832</v>
       </c>
       <c r="N60">
-        <v>-513.7705116224784</v>
+        <v>-524.6648307883831</v>
       </c>
       <c r="O60">
-        <v>-132.5527919985994</v>
+        <v>-135.3635263434029</v>
       </c>
       <c r="P60">
-        <v>-381.2177196238789</v>
+        <v>-389.3013044449802</v>
       </c>
       <c r="Q60">
-        <v>63.88228037612112</v>
+        <v>55.79869555501978</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1356845644347075</v>
+        <v>0.1378768708843345</v>
       </c>
       <c r="T60">
-        <v>2.075855991563684</v>
+        <v>2.126486625504262</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04822158882167411</v>
+        <v>0.04740427375689998</v>
       </c>
       <c r="W60">
-        <v>0.2244293493558492</v>
+        <v>0.224622072248123</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1869053830297446</v>
+        <v>0.1837374951817828</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1890565396889697</v>
+        <v>0.1909565396889697</v>
       </c>
       <c r="C61">
-        <v>-1761.232099169503</v>
+        <v>-1819.572102392481</v>
       </c>
       <c r="D61">
-        <v>927.3577684657101</v>
+        <v>915.21928842299</v>
       </c>
       <c r="E61">
-        <v>-351.3624503905712</v>
+        <v>-305.1609272103133</v>
       </c>
       <c r="F61">
-        <v>2725.889867635213</v>
+        <v>2772.091390815471</v>
       </c>
       <c r="G61">
         <v>37.3</v>
@@ -6289,37 +6289,37 @@
         <v>118.1</v>
       </c>
       <c r="M61">
-        <v>642.7648307883832</v>
+        <v>653.6591499542881</v>
       </c>
       <c r="N61">
-        <v>-524.6648307883831</v>
+        <v>-535.559149954288</v>
       </c>
       <c r="O61">
-        <v>-135.3635263434029</v>
+        <v>-138.1742606882063</v>
       </c>
       <c r="P61">
-        <v>-389.3013044449802</v>
+        <v>-397.3848892660817</v>
       </c>
       <c r="Q61">
-        <v>55.79869555501978</v>
+        <v>47.71511073391832</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1378768708843345</v>
+        <v>0.1401787926564429</v>
       </c>
       <c r="T61">
-        <v>2.126486625504262</v>
+        <v>2.179648791141868</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04740427375689998</v>
+        <v>0.0466142025276183</v>
       </c>
       <c r="W61">
-        <v>0.224622072248123</v>
+        <v>0.2248083710439876</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1837374951817828</v>
+        <v>0.1806752035954198</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1909565396889697</v>
+        <v>0.1928565396889697</v>
       </c>
       <c r="C62">
-        <v>-1819.572102392481</v>
+        <v>-1877.598442419929</v>
       </c>
       <c r="D62">
-        <v>915.21928842299</v>
+        <v>903.3944715757998</v>
       </c>
       <c r="E62">
-        <v>-305.1609272103133</v>
+        <v>-258.9594040300553</v>
       </c>
       <c r="F62">
-        <v>2772.091390815471</v>
+        <v>2818.292913995729</v>
       </c>
       <c r="G62">
         <v>37.3</v>
@@ -6371,37 +6371,37 @@
         <v>118.1</v>
       </c>
       <c r="M62">
-        <v>653.6591499542881</v>
+        <v>664.5534691201929</v>
       </c>
       <c r="N62">
-        <v>-535.559149954288</v>
+        <v>-546.4534691201928</v>
       </c>
       <c r="O62">
-        <v>-138.1742606882063</v>
+        <v>-140.9849950330098</v>
       </c>
       <c r="P62">
-        <v>-397.3848892660817</v>
+        <v>-405.468474087183</v>
       </c>
       <c r="Q62">
-        <v>47.71511073391832</v>
+        <v>39.63152591281698</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1401787926564429</v>
+        <v>0.1425987616989158</v>
       </c>
       <c r="T62">
-        <v>2.179648791141868</v>
+        <v>2.235537221683967</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0466142025276183</v>
+        <v>0.04585003527306718</v>
       </c>
       <c r="W62">
-        <v>0.2248083710439876</v>
+        <v>0.2249885616826108</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1806752035954198</v>
+        <v>0.1777133150118884</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1928565396889697</v>
+        <v>0.1947565396889697</v>
       </c>
       <c r="C63">
-        <v>-1877.598442419929</v>
+        <v>-1935.323121948865</v>
       </c>
       <c r="D63">
-        <v>903.3944715757998</v>
+        <v>891.8713152271218</v>
       </c>
       <c r="E63">
-        <v>-258.9594040300553</v>
+        <v>-212.7578808497974</v>
       </c>
       <c r="F63">
-        <v>2818.292913995729</v>
+        <v>2864.494437175987</v>
       </c>
       <c r="G63">
         <v>37.3</v>
@@ -6453,37 +6453,37 @@
         <v>118.1</v>
       </c>
       <c r="M63">
-        <v>664.5534691201929</v>
+        <v>675.4477882860976</v>
       </c>
       <c r="N63">
-        <v>-546.4534691201928</v>
+        <v>-557.3477882860976</v>
       </c>
       <c r="O63">
-        <v>-140.9849950330098</v>
+        <v>-143.7957293778132</v>
       </c>
       <c r="P63">
-        <v>-405.468474087183</v>
+        <v>-413.5520589082844</v>
       </c>
       <c r="Q63">
-        <v>39.63152591281698</v>
+        <v>31.54794109171559</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1425987616989158</v>
+        <v>0.1451460975330978</v>
       </c>
       <c r="T63">
-        <v>2.235537221683967</v>
+        <v>2.294367148570387</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04585003527306718</v>
+        <v>0.04511051857511449</v>
       </c>
       <c r="W63">
-        <v>0.2249885616826108</v>
+        <v>0.225162939719988</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1777133150118884</v>
+        <v>0.1748469712213739</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1947565396889697</v>
+        <v>0.1966565396889697</v>
       </c>
       <c r="C64">
-        <v>-1935.323121948865</v>
+        <v>-1992.757538992559</v>
       </c>
       <c r="D64">
-        <v>891.8713152271218</v>
+        <v>880.6384213636848</v>
       </c>
       <c r="E64">
-        <v>-212.7578808497974</v>
+        <v>-166.5563576695399</v>
       </c>
       <c r="F64">
-        <v>2864.494437175987</v>
+        <v>2910.695960356244</v>
       </c>
       <c r="G64">
         <v>37.3</v>
@@ -6535,37 +6535,37 @@
         <v>118.1</v>
       </c>
       <c r="M64">
-        <v>675.4477882860976</v>
+        <v>686.3421074520024</v>
       </c>
       <c r="N64">
-        <v>-557.3477882860976</v>
+        <v>-568.2421074520024</v>
       </c>
       <c r="O64">
-        <v>-143.7957293778132</v>
+        <v>-146.6064637226166</v>
       </c>
       <c r="P64">
-        <v>-413.5520589082844</v>
+        <v>-421.6356437293858</v>
       </c>
       <c r="Q64">
-        <v>31.54794109171559</v>
+        <v>23.46435627061425</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1451460975330978</v>
+        <v>0.1478311271961545</v>
       </c>
       <c r="T64">
-        <v>2.294367148570387</v>
+        <v>2.356377071504722</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04511051857511449</v>
+        <v>0.04439447859773172</v>
       </c>
       <c r="W64">
-        <v>0.225162939719988</v>
+        <v>0.2253317819466549</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1748469712213739</v>
+        <v>0.1720716224718284</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1966565396889697</v>
+        <v>0.1985565396889697</v>
       </c>
       <c r="C65">
-        <v>-1992.757538992559</v>
+        <v>-2049.912524486102</v>
       </c>
       <c r="D65">
-        <v>880.6384213636848</v>
+        <v>869.6849590503996</v>
       </c>
       <c r="E65">
-        <v>-166.5563576695399</v>
+        <v>-120.354834489282</v>
       </c>
       <c r="F65">
-        <v>2910.695960356244</v>
+        <v>2956.897483536502</v>
       </c>
       <c r="G65">
         <v>37.3</v>
@@ -6617,37 +6617,37 @@
         <v>118.1</v>
       </c>
       <c r="M65">
-        <v>686.3421074520024</v>
+        <v>697.2364266179072</v>
       </c>
       <c r="N65">
-        <v>-568.2421074520024</v>
+        <v>-579.1364266179072</v>
       </c>
       <c r="O65">
-        <v>-146.6064637226166</v>
+        <v>-149.4171980674201</v>
       </c>
       <c r="P65">
-        <v>-421.6356437293858</v>
+        <v>-429.7192285504872</v>
       </c>
       <c r="Q65">
-        <v>23.46435627061425</v>
+        <v>15.38077144951285</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1478311271961545</v>
+        <v>0.1506653251738254</v>
       </c>
       <c r="T65">
-        <v>2.356377071504722</v>
+        <v>2.421831990157632</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04439447859773172</v>
+        <v>0.04370081486964216</v>
       </c>
       <c r="W65">
-        <v>0.2253317819466549</v>
+        <v>0.2254953478537384</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1720716224718284</v>
+        <v>0.169383003370706</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1985565396889697</v>
+        <v>0.2004565396889697</v>
       </c>
       <c r="C66">
-        <v>-2049.912524486102</v>
+        <v>-2106.798377119993</v>
       </c>
       <c r="D66">
-        <v>869.6849590503996</v>
+        <v>859.0006295967671</v>
       </c>
       <c r="E66">
-        <v>-120.354834489282</v>
+        <v>-74.15331130902405</v>
       </c>
       <c r="F66">
-        <v>2956.897483536502</v>
+        <v>3003.09900671676</v>
       </c>
       <c r="G66">
         <v>37.3</v>
@@ -6699,37 +6699,37 @@
         <v>118.1</v>
       </c>
       <c r="M66">
-        <v>697.2364266179072</v>
+        <v>708.130745783812</v>
       </c>
       <c r="N66">
-        <v>-579.1364266179072</v>
+        <v>-590.030745783812</v>
       </c>
       <c r="O66">
-        <v>-149.4171980674201</v>
+        <v>-152.2279324122235</v>
       </c>
       <c r="P66">
-        <v>-429.7192285504872</v>
+        <v>-437.8028133715885</v>
       </c>
       <c r="Q66">
-        <v>15.38077144951285</v>
+        <v>7.297186628411509</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1506653251738254</v>
+        <v>0.153661477321649</v>
       </c>
       <c r="T66">
-        <v>2.421831990157632</v>
+        <v>2.491027189876421</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04370081486964216</v>
+        <v>0.04302849464087843</v>
       </c>
       <c r="W66">
-        <v>0.2254953478537384</v>
+        <v>0.2256538809636809</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.169383003370706</v>
+        <v>0.1667771110111568</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2004565396889697</v>
+        <v>0.2023565396889697</v>
       </c>
       <c r="C67">
-        <v>-2106.798377119993</v>
+        <v>-2163.424895637248</v>
       </c>
       <c r="D67">
-        <v>859.0006295967671</v>
+        <v>848.5756342597703</v>
       </c>
       <c r="E67">
-        <v>-74.15331130902405</v>
+        <v>-27.95178812876611</v>
       </c>
       <c r="F67">
-        <v>3003.09900671676</v>
+        <v>3049.300529897018</v>
       </c>
       <c r="G67">
         <v>37.3</v>
@@ -6781,37 +6781,37 @@
         <v>118.1</v>
       </c>
       <c r="M67">
-        <v>708.130745783812</v>
+        <v>719.0250649497168</v>
       </c>
       <c r="N67">
-        <v>-590.030745783812</v>
+        <v>-600.9250649497168</v>
       </c>
       <c r="O67">
-        <v>-152.2279324122235</v>
+        <v>-155.0386667570269</v>
       </c>
       <c r="P67">
-        <v>-437.8028133715885</v>
+        <v>-445.8863981926899</v>
       </c>
       <c r="Q67">
-        <v>7.297186628411509</v>
+        <v>-0.7863981926898305</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.153661477321649</v>
+        <v>0.1568338737134622</v>
       </c>
       <c r="T67">
-        <v>2.491027189876421</v>
+        <v>2.564292695461021</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04302849464087843</v>
+        <v>0.04237654775238028</v>
       </c>
       <c r="W67">
-        <v>0.2256538809636809</v>
+        <v>0.2258076100399887</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1667771110111568</v>
+        <v>0.1642501850867453</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2023565396889697</v>
+        <v>0.2042565396889697</v>
       </c>
       <c r="C68">
-        <v>-2163.424895637248</v>
+        <v>-2219.801408806926</v>
       </c>
       <c r="D68">
-        <v>848.5756342597703</v>
+        <v>838.4006442703495</v>
       </c>
       <c r="E68">
-        <v>-27.95178812876611</v>
+        <v>18.24973505149183</v>
       </c>
       <c r="F68">
-        <v>3049.300529897018</v>
+        <v>3095.502053077276</v>
       </c>
       <c r="G68">
         <v>37.3</v>
@@ -6863,37 +6863,37 @@
         <v>118.1</v>
       </c>
       <c r="M68">
-        <v>719.0250649497168</v>
+        <v>729.9193841156217</v>
       </c>
       <c r="N68">
-        <v>-600.9250649497168</v>
+        <v>-611.8193841156217</v>
       </c>
       <c r="O68">
-        <v>-155.0386667570269</v>
+        <v>-157.8494011018304</v>
       </c>
       <c r="P68">
-        <v>-445.8863981926899</v>
+        <v>-453.9699830137913</v>
       </c>
       <c r="Q68">
-        <v>-0.7863981926898305</v>
+        <v>-8.869983013791284</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1568338737134622</v>
+        <v>0.1601985365532641</v>
       </c>
       <c r="T68">
-        <v>2.564292695461021</v>
+        <v>2.641998534717416</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04237654775238028</v>
+        <v>0.04174406196503132</v>
       </c>
       <c r="W68">
-        <v>0.2258076100399887</v>
+        <v>0.2259567501886456</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1642501850867453</v>
+        <v>0.1617986897869431</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2042565396889697</v>
+        <v>0.2061565396889697</v>
       </c>
       <c r="C69">
-        <v>-2219.801408806926</v>
+        <v>-2275.936803266793</v>
       </c>
       <c r="D69">
-        <v>838.4006442703495</v>
+        <v>828.4667729907407</v>
       </c>
       <c r="E69">
-        <v>18.24973505149183</v>
+        <v>64.45125823174976</v>
       </c>
       <c r="F69">
-        <v>3095.502053077276</v>
+        <v>3141.703576257534</v>
       </c>
       <c r="G69">
         <v>37.3</v>
@@ -6945,37 +6945,37 @@
         <v>118.1</v>
       </c>
       <c r="M69">
-        <v>729.9193841156217</v>
+        <v>740.8137032815265</v>
       </c>
       <c r="N69">
-        <v>-611.8193841156217</v>
+        <v>-622.7137032815265</v>
       </c>
       <c r="O69">
-        <v>-157.8494011018304</v>
+        <v>-160.6601354466338</v>
       </c>
       <c r="P69">
-        <v>-453.9699830137913</v>
+        <v>-462.0535678348926</v>
       </c>
       <c r="Q69">
-        <v>-8.869983013791284</v>
+        <v>-16.95356783489262</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1601985365532641</v>
+        <v>0.1637734908205536</v>
       </c>
       <c r="T69">
-        <v>2.641998534717416</v>
+        <v>2.724560988927335</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04174406196503132</v>
+        <v>0.04113017870083967</v>
       </c>
       <c r="W69">
-        <v>0.2259567501886456</v>
+        <v>0.226101503862342</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1617986897869431</v>
+        <v>0.1594192972900763</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2061565396889697</v>
+        <v>0.2080565396889698</v>
       </c>
       <c r="C70">
-        <v>-2275.936803266793</v>
+        <v>-2331.839549409773</v>
       </c>
       <c r="D70">
-        <v>828.4667729907407</v>
+        <v>818.7655500280188</v>
       </c>
       <c r="E70">
-        <v>64.45125823174976</v>
+        <v>110.6527814120077</v>
       </c>
       <c r="F70">
-        <v>3141.703576257534</v>
+        <v>3187.905099437792</v>
       </c>
       <c r="G70">
         <v>37.3</v>
@@ -7027,37 +7027,37 @@
         <v>118.1</v>
       </c>
       <c r="M70">
-        <v>740.8137032815265</v>
+        <v>751.7080224474313</v>
       </c>
       <c r="N70">
-        <v>-622.7137032815265</v>
+        <v>-633.6080224474313</v>
       </c>
       <c r="O70">
-        <v>-160.6601354466338</v>
+        <v>-163.4708697914373</v>
       </c>
       <c r="P70">
-        <v>-462.0535678348926</v>
+        <v>-470.137152655994</v>
       </c>
       <c r="Q70">
-        <v>-16.95356783489262</v>
+        <v>-25.03715265599396</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1637734908205536</v>
+        <v>0.167579087298636</v>
       </c>
       <c r="T70">
-        <v>2.724560988927335</v>
+        <v>2.812450053086282</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04113017870083967</v>
+        <v>0.0405340891544507</v>
       </c>
       <c r="W70">
-        <v>0.226101503862342</v>
+        <v>0.2262420617773805</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1594192972900763</v>
+        <v>0.1571088726916694</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2080565396889698</v>
+        <v>0.2099565396889697</v>
       </c>
       <c r="C71">
-        <v>-2331.839549409773</v>
+        <v>-2387.517725472705</v>
       </c>
       <c r="D71">
-        <v>818.7655500280188</v>
+        <v>809.2888971453448</v>
       </c>
       <c r="E71">
-        <v>110.6527814120077</v>
+        <v>156.8543045922656</v>
       </c>
       <c r="F71">
-        <v>3187.905099437792</v>
+        <v>3234.10662261805</v>
       </c>
       <c r="G71">
         <v>37.3</v>
@@ -7109,37 +7109,37 @@
         <v>118.1</v>
       </c>
       <c r="M71">
-        <v>751.7080224474313</v>
+        <v>762.6023416133361</v>
       </c>
       <c r="N71">
-        <v>-633.6080224474313</v>
+        <v>-644.5023416133361</v>
       </c>
       <c r="O71">
-        <v>-163.4708697914373</v>
+        <v>-166.2816041362407</v>
       </c>
       <c r="P71">
-        <v>-470.137152655994</v>
+        <v>-478.2207374770953</v>
       </c>
       <c r="Q71">
-        <v>-25.03715265599396</v>
+        <v>-33.1207374770953</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.167579087298636</v>
+        <v>0.1716383902085905</v>
       </c>
       <c r="T71">
-        <v>2.812450053086282</v>
+        <v>2.906198388189158</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0405340891544507</v>
+        <v>0.03995503073795855</v>
       </c>
       <c r="W71">
-        <v>0.2262420617773805</v>
+        <v>0.2263786037519894</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1571088726916694</v>
+        <v>0.1548644602246455</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2099565396889697</v>
+        <v>0.2118565396889697</v>
       </c>
       <c r="C72">
-        <v>-2387.517725472705</v>
+        <v>-2442.979039971367</v>
       </c>
       <c r="D72">
-        <v>809.2888971453448</v>
+        <v>800.0291058269412</v>
       </c>
       <c r="E72">
-        <v>156.8543045922656</v>
+        <v>203.0558277725236</v>
       </c>
       <c r="F72">
-        <v>3234.10662261805</v>
+        <v>3280.308145798308</v>
       </c>
       <c r="G72">
         <v>37.3</v>
@@ -7191,37 +7191,37 @@
         <v>118.1</v>
       </c>
       <c r="M72">
-        <v>762.6023416133361</v>
+        <v>773.496660779241</v>
       </c>
       <c r="N72">
-        <v>-644.5023416133361</v>
+        <v>-655.396660779241</v>
       </c>
       <c r="O72">
-        <v>-166.2816041362407</v>
+        <v>-169.0923384810442</v>
       </c>
       <c r="P72">
-        <v>-478.2207374770953</v>
+        <v>-486.3043222981968</v>
       </c>
       <c r="Q72">
-        <v>-33.1207374770953</v>
+        <v>-41.20432229819676</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1716383902085905</v>
+        <v>0.1759776450433695</v>
       </c>
       <c r="T72">
-        <v>2.906198388189158</v>
+        <v>3.006412125712922</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03995503073795855</v>
+        <v>0.0393922838261563</v>
       </c>
       <c r="W72">
-        <v>0.2263786037519894</v>
+        <v>0.2265112994737923</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1548644602246455</v>
+        <v>0.1526832706440167</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2118565396889697</v>
+        <v>0.2137565396889697</v>
       </c>
       <c r="C73">
-        <v>-2442.979039971366</v>
+        <v>-2498.230852612731</v>
       </c>
       <c r="D73">
-        <v>800.0291058269412</v>
+        <v>790.9788163658334</v>
       </c>
       <c r="E73">
-        <v>203.0558277725227</v>
+        <v>249.2573509527806</v>
       </c>
       <c r="F73">
-        <v>3280.308145798307</v>
+        <v>3326.509668978565</v>
       </c>
       <c r="G73">
         <v>37.3</v>
@@ -7273,37 +7273,37 @@
         <v>118.1</v>
       </c>
       <c r="M73">
-        <v>773.4966607792408</v>
+        <v>784.3909799451455</v>
       </c>
       <c r="N73">
-        <v>-655.3966607792407</v>
+        <v>-666.2909799451455</v>
       </c>
       <c r="O73">
-        <v>-169.0923384810441</v>
+        <v>-171.9030728258475</v>
       </c>
       <c r="P73">
-        <v>-486.3043222981966</v>
+        <v>-494.387907119298</v>
       </c>
       <c r="Q73">
-        <v>-41.20432229819659</v>
+        <v>-49.28790711929798</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1759776450433695</v>
+        <v>0.1806268466520613</v>
       </c>
       <c r="T73">
-        <v>3.006412125712921</v>
+        <v>3.113783987345526</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03939228382615632</v>
+        <v>0.03884516877301526</v>
       </c>
       <c r="W73">
-        <v>0.2265112994737923</v>
+        <v>0.226640309203323</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1526832706440168</v>
+        <v>0.1505626696628498</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2137565396889697</v>
+        <v>0.2156565396889697</v>
       </c>
       <c r="C74">
-        <v>-2498.230852612731</v>
+        <v>-2553.280193803688</v>
       </c>
       <c r="D74">
-        <v>790.9788163658334</v>
+        <v>782.1309983551344</v>
       </c>
       <c r="E74">
-        <v>249.2573509527806</v>
+        <v>295.4588741330385</v>
       </c>
       <c r="F74">
-        <v>3326.509668978565</v>
+        <v>3372.711192158823</v>
       </c>
       <c r="G74">
         <v>37.3</v>
@@ -7355,37 +7355,37 @@
         <v>118.1</v>
       </c>
       <c r="M74">
-        <v>784.3909799451455</v>
+        <v>795.2852991110503</v>
       </c>
       <c r="N74">
-        <v>-666.2909799451455</v>
+        <v>-677.1852991110503</v>
       </c>
       <c r="O74">
-        <v>-171.9030728258475</v>
+        <v>-174.713807170651</v>
       </c>
       <c r="P74">
-        <v>-494.387907119298</v>
+        <v>-502.4714919403993</v>
       </c>
       <c r="Q74">
-        <v>-49.28790711929798</v>
+        <v>-57.37149194039932</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1806268466520613</v>
+        <v>0.1856204335651006</v>
       </c>
       <c r="T74">
-        <v>3.113783987345526</v>
+        <v>3.229109320210175</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03884516877301526</v>
+        <v>0.03831304317338492</v>
       </c>
       <c r="W74">
-        <v>0.226640309203323</v>
+        <v>0.2267657844197158</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1505626696628498</v>
+        <v>0.1485001673387012</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2156565396889697</v>
+        <v>0.2175565396889697</v>
       </c>
       <c r="C75">
-        <v>-2553.280193803688</v>
+        <v>-2608.133782864907</v>
       </c>
       <c r="D75">
-        <v>782.1309983551344</v>
+        <v>773.478932474174</v>
       </c>
       <c r="E75">
-        <v>295.4588741330385</v>
+        <v>341.6603973132965</v>
       </c>
       <c r="F75">
-        <v>3372.711192158823</v>
+        <v>3418.91271533908</v>
       </c>
       <c r="G75">
         <v>37.3</v>
@@ -7437,37 +7437,37 @@
         <v>118.1</v>
       </c>
       <c r="M75">
-        <v>795.2852991110503</v>
+        <v>806.1796182769552</v>
       </c>
       <c r="N75">
-        <v>-677.1852991110503</v>
+        <v>-688.0796182769552</v>
       </c>
       <c r="O75">
-        <v>-174.713807170651</v>
+        <v>-177.5245415154544</v>
       </c>
       <c r="P75">
-        <v>-502.4714919403993</v>
+        <v>-510.5550767615008</v>
       </c>
       <c r="Q75">
-        <v>-57.37149194039932</v>
+        <v>-65.45507676150078</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1856204335651006</v>
+        <v>0.1909981425483737</v>
       </c>
       <c r="T75">
-        <v>3.229109320210175</v>
+        <v>3.353305832525951</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03831304317338492</v>
+        <v>0.03779529934671755</v>
       </c>
       <c r="W75">
-        <v>0.2267657844197158</v>
+        <v>0.226887868414044</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1485001673387012</v>
+        <v>0.1464934083206106</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2175565396889697</v>
+        <v>0.2194565396889697</v>
       </c>
       <c r="C76">
-        <v>-2608.133782864907</v>
+        <v>-2662.798045049023</v>
       </c>
       <c r="D76">
-        <v>773.478932474174</v>
+        <v>765.0161934703154</v>
       </c>
       <c r="E76">
-        <v>341.6603973132965</v>
+        <v>387.8619204935544</v>
       </c>
       <c r="F76">
-        <v>3418.91271533908</v>
+        <v>3465.114238519338</v>
       </c>
       <c r="G76">
         <v>37.3</v>
@@ -7519,37 +7519,37 @@
         <v>118.1</v>
       </c>
       <c r="M76">
-        <v>806.1796182769552</v>
+        <v>817.07393744286</v>
       </c>
       <c r="N76">
-        <v>-688.0796182769552</v>
+        <v>-698.97393744286</v>
       </c>
       <c r="O76">
-        <v>-177.5245415154544</v>
+        <v>-180.3352758602579</v>
       </c>
       <c r="P76">
-        <v>-510.5550767615008</v>
+        <v>-518.6386615826021</v>
       </c>
       <c r="Q76">
-        <v>-65.45507676150078</v>
+        <v>-73.53866158260212</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1909981425483737</v>
+        <v>0.1968060682503086</v>
       </c>
       <c r="T76">
-        <v>3.353305832525951</v>
+        <v>3.487438065826989</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03779529934671755</v>
+        <v>0.03729136202209465</v>
       </c>
       <c r="W76">
-        <v>0.226887868414044</v>
+        <v>0.2270066968351901</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1464934083206106</v>
+        <v>0.1445401628763359</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2194565396889697</v>
+        <v>0.2213565396889697</v>
       </c>
       <c r="C77">
-        <v>-2662.798045049023</v>
+        <v>-2717.279127453727</v>
       </c>
       <c r="D77">
-        <v>765.0161934703154</v>
+        <v>756.7366342458698</v>
       </c>
       <c r="E77">
-        <v>387.8619204935544</v>
+        <v>434.0634436738123</v>
       </c>
       <c r="F77">
-        <v>3465.114238519338</v>
+        <v>3511.315761699596</v>
       </c>
       <c r="G77">
         <v>37.3</v>
@@ -7601,37 +7601,37 @@
         <v>118.1</v>
       </c>
       <c r="M77">
-        <v>817.07393744286</v>
+        <v>827.9682566087648</v>
       </c>
       <c r="N77">
-        <v>-698.97393744286</v>
+        <v>-709.8682566087648</v>
       </c>
       <c r="O77">
-        <v>-180.3352758602579</v>
+        <v>-183.1460102050613</v>
       </c>
       <c r="P77">
-        <v>-518.6386615826021</v>
+        <v>-526.7222464037035</v>
       </c>
       <c r="Q77">
-        <v>-73.53866158260212</v>
+        <v>-81.62224640370346</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1968060682503086</v>
+        <v>0.2030979877607382</v>
       </c>
       <c r="T77">
-        <v>3.487438065826989</v>
+        <v>3.632747985236448</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03729136202209465</v>
+        <v>0.03680068620601445</v>
       </c>
       <c r="W77">
-        <v>0.2270066968351901</v>
+        <v>0.2271223981926218</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1445401628763359</v>
+        <v>0.1426383186279629</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2213565396889697</v>
+        <v>0.2232565396889697</v>
       </c>
       <c r="C78">
-        <v>-2717.279127453727</v>
+        <v>-2771.582913912572</v>
       </c>
       <c r="D78">
-        <v>756.7366342458698</v>
+        <v>748.6343709672823</v>
       </c>
       <c r="E78">
-        <v>434.0634436738123</v>
+        <v>480.2649668540703</v>
       </c>
       <c r="F78">
-        <v>3511.315761699596</v>
+        <v>3557.517284879854</v>
       </c>
       <c r="G78">
         <v>37.3</v>
@@ -7683,37 +7683,37 @@
         <v>118.1</v>
       </c>
       <c r="M78">
-        <v>827.9682566087648</v>
+        <v>838.8625757746697</v>
       </c>
       <c r="N78">
-        <v>-709.8682566087648</v>
+        <v>-720.7625757746697</v>
       </c>
       <c r="O78">
-        <v>-183.1460102050613</v>
+        <v>-185.9567445498648</v>
       </c>
       <c r="P78">
-        <v>-526.7222464037035</v>
+        <v>-534.8058312248049</v>
       </c>
       <c r="Q78">
-        <v>-81.62224640370346</v>
+        <v>-89.70583122480491</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2030979877607382</v>
+        <v>0.2099370307068572</v>
       </c>
       <c r="T78">
-        <v>3.632747985236448</v>
+        <v>3.790693549811945</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03680068620601445</v>
+        <v>0.03632275521632595</v>
       </c>
       <c r="W78">
-        <v>0.2271223981926218</v>
+        <v>0.2272350943199903</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1426383186279629</v>
+        <v>0.1407858729314959</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2232565396889697</v>
+        <v>0.2251565396889697</v>
       </c>
       <c r="C79">
-        <v>-2771.582913912572</v>
+        <v>-2825.715038939323</v>
       </c>
       <c r="D79">
-        <v>748.6343709672823</v>
+        <v>740.7037691207896</v>
       </c>
       <c r="E79">
-        <v>480.2649668540703</v>
+        <v>526.4664900343282</v>
       </c>
       <c r="F79">
-        <v>3557.517284879854</v>
+        <v>3603.718808060112</v>
       </c>
       <c r="G79">
         <v>37.3</v>
@@ -7765,37 +7765,37 @@
         <v>118.1</v>
       </c>
       <c r="M79">
-        <v>838.8625757746697</v>
+        <v>849.7568949405745</v>
       </c>
       <c r="N79">
-        <v>-720.7625757746697</v>
+        <v>-731.6568949405745</v>
       </c>
       <c r="O79">
-        <v>-185.9567445498648</v>
+        <v>-188.7674788946682</v>
       </c>
       <c r="P79">
-        <v>-534.8058312248049</v>
+        <v>-542.8894160459063</v>
       </c>
       <c r="Q79">
-        <v>-89.70583122480491</v>
+        <v>-97.78941604590625</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2099370307068572</v>
+        <v>0.2173978048298962</v>
       </c>
       <c r="T79">
-        <v>3.790693549811945</v>
+        <v>3.962997802076124</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03632275521632595</v>
+        <v>0.03585707886739869</v>
       </c>
       <c r="W79">
-        <v>0.2272350943199903</v>
+        <v>0.2273449008030674</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1407858729314959</v>
+        <v>0.1389809258426306</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2251565396889697</v>
+        <v>0.2270565396889697</v>
       </c>
       <c r="C80">
-        <v>-2825.715038939323</v>
+        <v>-2879.680900795274</v>
       </c>
       <c r="D80">
-        <v>740.7037691207896</v>
+        <v>732.939430445096</v>
       </c>
       <c r="E80">
-        <v>526.4664900343282</v>
+        <v>572.6680132145862</v>
       </c>
       <c r="F80">
-        <v>3603.718808060112</v>
+        <v>3649.92033124037</v>
       </c>
       <c r="G80">
         <v>37.3</v>
@@ -7847,37 +7847,37 @@
         <v>118.1</v>
       </c>
       <c r="M80">
-        <v>849.7568949405745</v>
+        <v>860.6512141064793</v>
       </c>
       <c r="N80">
-        <v>-731.6568949405745</v>
+        <v>-742.5512141064793</v>
       </c>
       <c r="O80">
-        <v>-188.7674788946682</v>
+        <v>-191.5782132394717</v>
       </c>
       <c r="P80">
-        <v>-542.8894160459063</v>
+        <v>-550.9730008670076</v>
       </c>
       <c r="Q80">
-        <v>-97.78941604590625</v>
+        <v>-105.8730008670076</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2173978048298962</v>
+        <v>0.225569128869415</v>
       </c>
       <c r="T80">
-        <v>3.962997802076124</v>
+        <v>4.151711983127369</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03585707886739869</v>
+        <v>0.03540319179312782</v>
       </c>
       <c r="W80">
-        <v>0.2273449008030674</v>
+        <v>0.2274519273751805</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1389809258426306</v>
+        <v>0.1372216736167745</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2270565396889697</v>
+        <v>0.2289565396889697</v>
       </c>
       <c r="C81">
-        <v>-2879.680900795274</v>
+        <v>-2933.485673743247</v>
       </c>
       <c r="D81">
-        <v>732.939430445096</v>
+        <v>725.3361806773808</v>
       </c>
       <c r="E81">
-        <v>572.6680132145862</v>
+        <v>618.8695363948436</v>
       </c>
       <c r="F81">
-        <v>3649.92033124037</v>
+        <v>3696.121854420628</v>
       </c>
       <c r="G81">
         <v>37.3</v>
@@ -7929,37 +7929,37 @@
         <v>118.1</v>
       </c>
       <c r="M81">
-        <v>860.6512141064793</v>
+        <v>871.545533272384</v>
       </c>
       <c r="N81">
-        <v>-742.5512141064793</v>
+        <v>-753.445533272384</v>
       </c>
       <c r="O81">
-        <v>-191.5782132394717</v>
+        <v>-194.3889475842751</v>
       </c>
       <c r="P81">
-        <v>-550.9730008670076</v>
+        <v>-559.056585688109</v>
       </c>
       <c r="Q81">
-        <v>-105.8730008670076</v>
+        <v>-113.9565856881089</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.225569128869415</v>
+        <v>0.2345575853128858</v>
       </c>
       <c r="T81">
-        <v>4.151711983127369</v>
+        <v>4.359297582283737</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03540319179312782</v>
+        <v>0.03496065189571373</v>
       </c>
       <c r="W81">
-        <v>0.2274519273751805</v>
+        <v>0.2275562782829907</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1372216736167745</v>
+        <v>0.1355064026965649</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2289565396889697</v>
+        <v>0.2308565396889697</v>
       </c>
       <c r="C82">
-        <v>-2933.485673743247</v>
+        <v>-2987.134319546695</v>
       </c>
       <c r="D82">
-        <v>725.3361806773808</v>
+        <v>717.8890580541903</v>
       </c>
       <c r="E82">
-        <v>618.8695363948436</v>
+        <v>665.0710595751016</v>
       </c>
       <c r="F82">
-        <v>3696.121854420628</v>
+        <v>3742.323377600886</v>
       </c>
       <c r="G82">
         <v>37.3</v>
@@ -8011,37 +8011,37 @@
         <v>118.1</v>
       </c>
       <c r="M82">
-        <v>871.545533272384</v>
+        <v>882.4398524382889</v>
       </c>
       <c r="N82">
-        <v>-753.445533272384</v>
+        <v>-764.3398524382889</v>
       </c>
       <c r="O82">
-        <v>-194.3889475842751</v>
+        <v>-197.1996819290785</v>
       </c>
       <c r="P82">
-        <v>-559.056585688109</v>
+        <v>-567.1401705092103</v>
       </c>
       <c r="Q82">
-        <v>-113.9565856881089</v>
+        <v>-122.0401705092103</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2345575853128858</v>
+        <v>0.2444921950661956</v>
       </c>
       <c r="T82">
-        <v>4.359297582283737</v>
+        <v>4.588734297140777</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03496065189571373</v>
+        <v>0.03452903890934689</v>
       </c>
       <c r="W82">
-        <v>0.2275562782829907</v>
+        <v>0.227658052625176</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1355064026965649</v>
+        <v>0.1338334841447554</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2308565396889697</v>
+        <v>0.2327565396889697</v>
       </c>
       <c r="C83">
-        <v>-2987.134319546695</v>
+        <v>-3040.631598267637</v>
       </c>
       <c r="D83">
-        <v>717.8890580541903</v>
+        <v>710.5933025135062</v>
       </c>
       <c r="E83">
-        <v>665.0710595751016</v>
+        <v>711.2725827553595</v>
       </c>
       <c r="F83">
-        <v>3742.323377600886</v>
+        <v>3788.524900781144</v>
       </c>
       <c r="G83">
         <v>37.3</v>
@@ -8093,37 +8093,37 @@
         <v>118.1</v>
       </c>
       <c r="M83">
-        <v>882.4398524382889</v>
+        <v>893.3341716041937</v>
       </c>
       <c r="N83">
-        <v>-764.3398524382889</v>
+        <v>-775.2341716041936</v>
       </c>
       <c r="O83">
-        <v>-197.1996819290785</v>
+        <v>-200.010416273882</v>
       </c>
       <c r="P83">
-        <v>-567.1401705092103</v>
+        <v>-575.2237553303116</v>
       </c>
       <c r="Q83">
-        <v>-122.0401705092103</v>
+        <v>-130.1237553303116</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2444921950661956</v>
+        <v>0.2555306503476509</v>
       </c>
       <c r="T83">
-        <v>4.588734297140777</v>
+        <v>4.843663980315265</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03452903890934689</v>
+        <v>0.034107953068989</v>
       </c>
       <c r="W83">
-        <v>0.227658052625176</v>
+        <v>0.2277573446663324</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1338334841447554</v>
+        <v>0.1322013684844535</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2327565396889697</v>
+        <v>0.2346565396889698</v>
       </c>
       <c r="C84">
-        <v>-3040.631598267637</v>
+        <v>-3093.982078412791</v>
       </c>
       <c r="D84">
-        <v>710.5933025135062</v>
+        <v>703.44434554861</v>
       </c>
       <c r="E84">
-        <v>711.2725827553595</v>
+        <v>757.4741059356174</v>
       </c>
       <c r="F84">
-        <v>3788.524900781144</v>
+        <v>3834.726423961401</v>
       </c>
       <c r="G84">
         <v>37.3</v>
@@ -8175,37 +8175,37 @@
         <v>118.1</v>
       </c>
       <c r="M84">
-        <v>893.3341716041937</v>
+        <v>904.2284907700985</v>
       </c>
       <c r="N84">
-        <v>-775.2341716041936</v>
+        <v>-786.1284907700984</v>
       </c>
       <c r="O84">
-        <v>-200.010416273882</v>
+        <v>-202.8211506186854</v>
       </c>
       <c r="P84">
-        <v>-575.2237553303116</v>
+        <v>-583.307340151413</v>
       </c>
       <c r="Q84">
-        <v>-130.1237553303116</v>
+        <v>-138.207340151413</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2555306503476509</v>
+        <v>0.2678677474269245</v>
       </c>
       <c r="T84">
-        <v>4.843663980315265</v>
+        <v>5.128585390922045</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.034107953068989</v>
+        <v>0.03369701387538673</v>
       </c>
       <c r="W84">
-        <v>0.2277573446663324</v>
+        <v>0.2278542441281838</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1322013684844535</v>
+        <v>0.1306085809123516</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2346565396889698</v>
+        <v>0.2365565396889697</v>
       </c>
       <c r="C85">
-        <v>-3093.982078412791</v>
+        <v>-3147.190146473354</v>
       </c>
       <c r="D85">
-        <v>703.44434554861</v>
+        <v>696.4378006683053</v>
       </c>
       <c r="E85">
-        <v>757.4741059356174</v>
+        <v>803.6756291158754</v>
       </c>
       <c r="F85">
-        <v>3834.726423961401</v>
+        <v>3880.927947141659</v>
       </c>
       <c r="G85">
         <v>37.3</v>
@@ -8257,37 +8257,37 @@
         <v>118.1</v>
       </c>
       <c r="M85">
-        <v>904.2284907700985</v>
+        <v>915.1228099360034</v>
       </c>
       <c r="N85">
-        <v>-786.1284907700984</v>
+        <v>-797.0228099360033</v>
       </c>
       <c r="O85">
-        <v>-202.8211506186854</v>
+        <v>-205.6318849634889</v>
       </c>
       <c r="P85">
-        <v>-583.307340151413</v>
+        <v>-591.3909249725145</v>
       </c>
       <c r="Q85">
-        <v>-138.207340151413</v>
+        <v>-146.2909249725145</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2678677474269245</v>
+        <v>0.2817469816411073</v>
       </c>
       <c r="T85">
-        <v>5.128585390922045</v>
+        <v>5.449121977854673</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03369701387538673</v>
+        <v>0.03329585894829878</v>
       </c>
       <c r="W85">
-        <v>0.2278542441281838</v>
+        <v>0.2279488364599911</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1306085809123516</v>
+        <v>0.1290537168538712</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2365565396889697</v>
+        <v>0.2384565396889697</v>
       </c>
       <c r="C86">
-        <v>-3147.190146473353</v>
+        <v>-3200.260015900285</v>
       </c>
       <c r="D86">
-        <v>696.4378006683057</v>
+        <v>689.5694544216323</v>
       </c>
       <c r="E86">
-        <v>803.6756291158749</v>
+        <v>849.8771522961329</v>
       </c>
       <c r="F86">
-        <v>3880.927947141659</v>
+        <v>3927.129470321917</v>
       </c>
       <c r="G86">
         <v>37.3</v>
@@ -8339,37 +8339,37 @@
         <v>118.1</v>
       </c>
       <c r="M86">
-        <v>915.1228099360033</v>
+        <v>926.017129101908</v>
       </c>
       <c r="N86">
-        <v>-797.0228099360032</v>
+        <v>-807.917129101908</v>
       </c>
       <c r="O86">
-        <v>-205.6318849634888</v>
+        <v>-208.4426193082923</v>
       </c>
       <c r="P86">
-        <v>-591.3909249725144</v>
+        <v>-599.4745097936158</v>
       </c>
       <c r="Q86">
-        <v>-146.2909249725144</v>
+        <v>-154.3745097936157</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2817469816411072</v>
+        <v>0.297476780417181</v>
       </c>
       <c r="T86">
-        <v>5.44912197785467</v>
+        <v>5.812396776378314</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03329585894829878</v>
+        <v>0.03290414296067175</v>
       </c>
       <c r="W86">
-        <v>0.2279488364599911</v>
+        <v>0.2280412030898736</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1290537168538712</v>
+        <v>0.127535437832061</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2384565396889697</v>
+        <v>0.2403565396889697</v>
       </c>
       <c r="C87">
-        <v>-3200.260015900285</v>
+        <v>-3253.19573555369</v>
       </c>
       <c r="D87">
-        <v>689.5694544216323</v>
+        <v>682.8352579484854</v>
       </c>
       <c r="E87">
-        <v>849.8771522961329</v>
+        <v>896.0786754763908</v>
       </c>
       <c r="F87">
-        <v>3927.129470321917</v>
+        <v>3973.330993502175</v>
       </c>
       <c r="G87">
         <v>37.3</v>
@@ -8421,37 +8421,37 @@
         <v>118.1</v>
       </c>
       <c r="M87">
-        <v>926.017129101908</v>
+        <v>936.9114482678128</v>
       </c>
       <c r="N87">
-        <v>-807.917129101908</v>
+        <v>-818.8114482678128</v>
       </c>
       <c r="O87">
-        <v>-208.4426193082923</v>
+        <v>-211.2533536530957</v>
       </c>
       <c r="P87">
-        <v>-599.4745097936158</v>
+        <v>-607.5580946147171</v>
       </c>
       <c r="Q87">
-        <v>-154.3745097936157</v>
+        <v>-162.4580946147171</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.297476780417181</v>
+        <v>0.3154536933041225</v>
       </c>
       <c r="T87">
-        <v>5.812396776378314</v>
+        <v>6.227567974691051</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03290414296067175</v>
+        <v>0.03252153664717556</v>
       </c>
       <c r="W87">
-        <v>0.2280412030898736</v>
+        <v>0.228131421658596</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.127535437832061</v>
+        <v>0.1260524676247115</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2403565396889697</v>
+        <v>0.2422565396889698</v>
       </c>
       <c r="C88">
-        <v>-3253.19573555369</v>
+        <v>-3306.001197661896</v>
       </c>
       <c r="D88">
-        <v>682.8352579484854</v>
+        <v>676.2313190205364</v>
       </c>
       <c r="E88">
-        <v>896.0786754763908</v>
+        <v>942.2801986566487</v>
       </c>
       <c r="F88">
-        <v>3973.330993502175</v>
+        <v>4019.532516682433</v>
       </c>
       <c r="G88">
         <v>37.3</v>
@@ -8503,37 +8503,37 @@
         <v>118.1</v>
       </c>
       <c r="M88">
-        <v>936.9114482678128</v>
+        <v>947.8057674337177</v>
       </c>
       <c r="N88">
-        <v>-818.8114482678128</v>
+        <v>-829.7057674337177</v>
       </c>
       <c r="O88">
-        <v>-211.2533536530957</v>
+        <v>-214.0640879978992</v>
       </c>
       <c r="P88">
-        <v>-607.5580946147171</v>
+        <v>-615.6416794358186</v>
       </c>
       <c r="Q88">
-        <v>-162.4580946147171</v>
+        <v>-170.5416794358185</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3154536933041225</v>
+        <v>0.3361962850967473</v>
       </c>
       <c r="T88">
-        <v>6.227567974691051</v>
+        <v>6.706611665051901</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03252153664717556</v>
+        <v>0.03214772588111607</v>
       </c>
       <c r="W88">
-        <v>0.228131421658596</v>
+        <v>0.2282195662372329</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1260524676247115</v>
+        <v>0.1246035886864963</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2422565396889698</v>
+        <v>0.2441565396889697</v>
       </c>
       <c r="C89">
-        <v>-3306.001197661896</v>
+        <v>-3358.68014532311</v>
       </c>
       <c r="D89">
-        <v>676.2313190205364</v>
+        <v>669.7538945395806</v>
       </c>
       <c r="E89">
-        <v>942.2801986566487</v>
+        <v>988.4817218369062</v>
       </c>
       <c r="F89">
-        <v>4019.532516682433</v>
+        <v>4065.73403986269</v>
       </c>
       <c r="G89">
         <v>37.3</v>
@@ -8585,37 +8585,37 @@
         <v>118.1</v>
       </c>
       <c r="M89">
-        <v>947.8057674337177</v>
+        <v>958.7000865996224</v>
       </c>
       <c r="N89">
-        <v>-829.7057674337177</v>
+        <v>-840.6000865996224</v>
       </c>
       <c r="O89">
-        <v>-214.0640879978992</v>
+        <v>-216.8748223427026</v>
       </c>
       <c r="P89">
-        <v>-615.6416794358186</v>
+        <v>-623.7252642569198</v>
       </c>
       <c r="Q89">
-        <v>-170.5416794358185</v>
+        <v>-178.6252642569198</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3361962850967473</v>
+        <v>0.3603959755214763</v>
       </c>
       <c r="T89">
-        <v>6.706611665051901</v>
+        <v>7.265495970472894</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03214772588111607</v>
+        <v>0.03178241081428521</v>
       </c>
       <c r="W89">
-        <v>0.2282195662372329</v>
+        <v>0.2283057075299915</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1246035886864963</v>
+        <v>0.1231876388150589</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2441565396889697</v>
+        <v>0.2460565396889697</v>
       </c>
       <c r="C90">
-        <v>-3358.68014532311</v>
+        <v>-3411.236179580018</v>
       </c>
       <c r="D90">
-        <v>669.7538945395806</v>
+        <v>663.3993834629305</v>
       </c>
       <c r="E90">
-        <v>988.4817218369062</v>
+        <v>1034.683245017164</v>
       </c>
       <c r="F90">
-        <v>4065.73403986269</v>
+        <v>4111.935563042948</v>
       </c>
       <c r="G90">
         <v>37.3</v>
@@ -8667,37 +8667,37 @@
         <v>118.1</v>
       </c>
       <c r="M90">
-        <v>958.7000865996224</v>
+        <v>969.5944057655272</v>
       </c>
       <c r="N90">
-        <v>-840.6000865996224</v>
+        <v>-851.4944057655272</v>
       </c>
       <c r="O90">
-        <v>-216.8748223427026</v>
+        <v>-219.685556687506</v>
       </c>
       <c r="P90">
-        <v>-623.7252642569198</v>
+        <v>-631.8088490780211</v>
       </c>
       <c r="Q90">
-        <v>-178.6252642569198</v>
+        <v>-186.7088490780211</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3603959755214763</v>
+        <v>0.3889956096597924</v>
       </c>
       <c r="T90">
-        <v>7.265495970472894</v>
+        <v>7.925995604152249</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03178241081428521</v>
+        <v>0.03142530507479886</v>
       </c>
       <c r="W90">
-        <v>0.2283057075299915</v>
+        <v>0.2283899130633624</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1231876388150589</v>
+        <v>0.121803508041856</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2460565396889697</v>
+        <v>0.2479565396889697</v>
       </c>
       <c r="C91">
-        <v>-3411.236179580018</v>
+        <v>-3463.672766095446</v>
       </c>
       <c r="D91">
-        <v>663.3993834629305</v>
+        <v>657.1643201277604</v>
       </c>
       <c r="E91">
-        <v>1034.683245017164</v>
+        <v>1080.884768197422</v>
       </c>
       <c r="F91">
-        <v>4111.935563042948</v>
+        <v>4158.137086223206</v>
       </c>
       <c r="G91">
         <v>37.3</v>
@@ -8749,37 +8749,37 @@
         <v>118.1</v>
       </c>
       <c r="M91">
-        <v>969.5944057655272</v>
+        <v>980.488724931432</v>
       </c>
       <c r="N91">
-        <v>-851.4944057655272</v>
+        <v>-862.388724931432</v>
       </c>
       <c r="O91">
-        <v>-219.685556687506</v>
+        <v>-222.4962910323094</v>
       </c>
       <c r="P91">
-        <v>-631.8088490780211</v>
+        <v>-639.8924338991226</v>
       </c>
       <c r="Q91">
-        <v>-186.7088490780211</v>
+        <v>-194.7924338991226</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3889956096597924</v>
+        <v>0.4233151706257717</v>
       </c>
       <c r="T91">
-        <v>7.925995604152249</v>
+        <v>8.718595164567475</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03142530507479886</v>
+        <v>0.03107613501841221</v>
       </c>
       <c r="W91">
-        <v>0.2283899130633624</v>
+        <v>0.2284722473626584</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.121803508041856</v>
+        <v>0.1204501357302799</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2479565396889697</v>
+        <v>0.2498565396889697</v>
       </c>
       <c r="C92">
-        <v>-3463.672766095446</v>
+        <v>-3515.993241455065</v>
       </c>
       <c r="D92">
-        <v>657.1643201277604</v>
+        <v>651.0453679483988</v>
       </c>
       <c r="E92">
-        <v>1080.884768197422</v>
+        <v>1127.08629137768</v>
       </c>
       <c r="F92">
-        <v>4158.137086223206</v>
+        <v>4204.338609403464</v>
       </c>
       <c r="G92">
         <v>37.3</v>
@@ -8831,37 +8831,37 @@
         <v>118.1</v>
       </c>
       <c r="M92">
-        <v>980.488724931432</v>
+        <v>991.3830440973369</v>
       </c>
       <c r="N92">
-        <v>-862.388724931432</v>
+        <v>-873.2830440973369</v>
       </c>
       <c r="O92">
-        <v>-222.4962910323094</v>
+        <v>-225.3070253771129</v>
       </c>
       <c r="P92">
-        <v>-639.8924338991226</v>
+        <v>-647.9760187202239</v>
       </c>
       <c r="Q92">
-        <v>-194.7924338991226</v>
+        <v>-202.8760187202239</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4233151706257717</v>
+        <v>0.4652613006953019</v>
       </c>
       <c r="T92">
-        <v>8.718595164567475</v>
+        <v>9.687327960630528</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03107613501841221</v>
+        <v>0.03073463902919888</v>
       </c>
       <c r="W92">
-        <v>0.2284722473626584</v>
+        <v>0.2285527721169149</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1204501357302799</v>
+        <v>0.1191265078651119</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2498565396889697</v>
+        <v>0.2517565396889697</v>
       </c>
       <c r="C93">
-        <v>-3515.993241455065</v>
+        <v>-3568.200819121235</v>
       </c>
       <c r="D93">
-        <v>651.0453679483988</v>
+        <v>645.0393134624866</v>
       </c>
       <c r="E93">
-        <v>1127.08629137768</v>
+        <v>1173.287814557938</v>
       </c>
       <c r="F93">
-        <v>4204.338609403464</v>
+        <v>4250.540132583722</v>
       </c>
       <c r="G93">
         <v>37.3</v>
@@ -8913,37 +8913,37 @@
         <v>118.1</v>
       </c>
       <c r="M93">
-        <v>991.3830440973369</v>
+        <v>1002.277363263242</v>
       </c>
       <c r="N93">
-        <v>-873.2830440973369</v>
+        <v>-884.1773632632417</v>
       </c>
       <c r="O93">
-        <v>-225.3070253771129</v>
+        <v>-228.1177597219163</v>
       </c>
       <c r="P93">
-        <v>-647.9760187202239</v>
+        <v>-656.0596035413253</v>
       </c>
       <c r="Q93">
-        <v>-202.8760187202239</v>
+        <v>-210.9596035413252</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4652613006953019</v>
+        <v>0.5176939632822146</v>
       </c>
       <c r="T93">
-        <v>9.687327960630528</v>
+        <v>10.89824395570935</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03073463902919888</v>
+        <v>0.03040056686583803</v>
       </c>
       <c r="W93">
-        <v>0.2285527721169149</v>
+        <v>0.2286315463330354</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1191265078651119</v>
+        <v>0.117831654518752</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2517565396889697</v>
+        <v>0.2536565396889697</v>
       </c>
       <c r="C94">
-        <v>-3568.200819121235</v>
+        <v>-3620.298595060308</v>
       </c>
       <c r="D94">
-        <v>645.0393134624866</v>
+        <v>639.1430607036717</v>
       </c>
       <c r="E94">
-        <v>1173.287814557938</v>
+        <v>1219.489337738196</v>
       </c>
       <c r="F94">
-        <v>4250.540132583722</v>
+        <v>4296.74165576398</v>
       </c>
       <c r="G94">
         <v>37.3</v>
@@ -8995,37 +8995,37 @@
         <v>118.1</v>
       </c>
       <c r="M94">
-        <v>1002.277363263242</v>
+        <v>1013.171682429146</v>
       </c>
       <c r="N94">
-        <v>-884.1773632632417</v>
+        <v>-895.0716824291464</v>
       </c>
       <c r="O94">
-        <v>-228.1177597219163</v>
+        <v>-230.9284940667198</v>
       </c>
       <c r="P94">
-        <v>-656.0596035413253</v>
+        <v>-664.1431883624266</v>
       </c>
       <c r="Q94">
-        <v>-210.9596035413252</v>
+        <v>-219.0431883624266</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5176939632822146</v>
+        <v>0.5851073866082455</v>
       </c>
       <c r="T94">
-        <v>10.89824395570935</v>
+        <v>12.45513594938211</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03040056686583803</v>
+        <v>0.03007367905007633</v>
       </c>
       <c r="W94">
-        <v>0.2286315463330354</v>
+        <v>0.228708626479992</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.117831654518752</v>
+        <v>0.116564647480916</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2536565396889697</v>
+        <v>0.2555565396889697</v>
       </c>
       <c r="C95">
-        <v>-3620.298595060308</v>
+        <v>-3672.289553064089</v>
       </c>
       <c r="D95">
-        <v>639.1430607036717</v>
+        <v>633.3536258801493</v>
       </c>
       <c r="E95">
-        <v>1219.489337738196</v>
+        <v>1265.690860918454</v>
       </c>
       <c r="F95">
-        <v>4296.74165576398</v>
+        <v>4342.943178944238</v>
       </c>
       <c r="G95">
         <v>37.3</v>
@@ -9077,37 +9077,37 @@
         <v>118.1</v>
       </c>
       <c r="M95">
-        <v>1013.171682429146</v>
+        <v>1024.066001595051</v>
       </c>
       <c r="N95">
-        <v>-895.0716824291464</v>
+        <v>-905.9660015950514</v>
       </c>
       <c r="O95">
-        <v>-230.9284940667198</v>
+        <v>-233.7392284115232</v>
       </c>
       <c r="P95">
-        <v>-664.1431883624266</v>
+        <v>-672.2267731835282</v>
       </c>
       <c r="Q95">
-        <v>-219.0431883624266</v>
+        <v>-227.1267731835281</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5851073866082455</v>
+        <v>0.6749919510429531</v>
       </c>
       <c r="T95">
-        <v>12.45513594938211</v>
+        <v>14.5309919409458</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03007367905007633</v>
+        <v>0.02975374629422445</v>
       </c>
       <c r="W95">
-        <v>0.228708626479992</v>
+        <v>0.2287840666238219</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.116564647480916</v>
+        <v>0.1153245980396297</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2555565396889697</v>
+        <v>0.2574565396889698</v>
       </c>
       <c r="C96">
-        <v>-3672.289553064089</v>
+        <v>-3724.176569784687</v>
       </c>
       <c r="D96">
-        <v>633.3536258801493</v>
+        <v>627.6681323398093</v>
       </c>
       <c r="E96">
-        <v>1265.690860918454</v>
+        <v>1311.892384098712</v>
       </c>
       <c r="F96">
-        <v>4342.943178944238</v>
+        <v>4389.144702124496</v>
       </c>
       <c r="G96">
         <v>37.3</v>
@@ -9159,37 +9159,37 @@
         <v>118.1</v>
       </c>
       <c r="M96">
-        <v>1024.066001595051</v>
+        <v>1034.960320760956</v>
       </c>
       <c r="N96">
-        <v>-905.9660015950514</v>
+        <v>-916.8603207609561</v>
       </c>
       <c r="O96">
-        <v>-233.7392284115232</v>
+        <v>-236.5499627563267</v>
       </c>
       <c r="P96">
-        <v>-672.2267731835282</v>
+        <v>-680.3103580046295</v>
       </c>
       <c r="Q96">
-        <v>-227.1267731835281</v>
+        <v>-235.2103580046295</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6749919510429531</v>
+        <v>0.8008303412515442</v>
       </c>
       <c r="T96">
-        <v>14.5309919409458</v>
+        <v>17.43719032913497</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02975374629422445</v>
+        <v>0.02944054896481156</v>
       </c>
       <c r="W96">
-        <v>0.2287840666238219</v>
+        <v>0.2288579185540975</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1153245980396297</v>
+        <v>0.1141106549023704</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2574565396889698</v>
+        <v>0.2593565396889698</v>
       </c>
       <c r="C97">
-        <v>-3724.176569784687</v>
+        <v>-3775.962419500589</v>
       </c>
       <c r="D97">
-        <v>627.6681323398093</v>
+        <v>622.0838058041645</v>
       </c>
       <c r="E97">
-        <v>1311.892384098712</v>
+        <v>1358.09390727897</v>
       </c>
       <c r="F97">
-        <v>4389.144702124496</v>
+        <v>4435.346225304754</v>
       </c>
       <c r="G97">
         <v>37.3</v>
@@ -9241,37 +9241,37 @@
         <v>118.1</v>
       </c>
       <c r="M97">
-        <v>1034.960320760956</v>
+        <v>1045.854639926861</v>
       </c>
       <c r="N97">
-        <v>-916.8603207609561</v>
+        <v>-927.7546399268609</v>
       </c>
       <c r="O97">
-        <v>-236.5499627563267</v>
+        <v>-239.3606971011301</v>
       </c>
       <c r="P97">
-        <v>-680.3103580046295</v>
+        <v>-688.3939428257308</v>
       </c>
       <c r="Q97">
-        <v>-235.2103580046295</v>
+        <v>-243.2939428257308</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8008303412515442</v>
+        <v>0.9895879265644306</v>
       </c>
       <c r="T97">
-        <v>17.43719032913497</v>
+        <v>21.79648791141872</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02944054896481156</v>
+        <v>0.02913387657976144</v>
       </c>
       <c r="W97">
-        <v>0.2288579185540975</v>
+        <v>0.2289302319024923</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1141106549023704</v>
+        <v>0.1129220022471373</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2593565396889697</v>
+        <v>0.2612565396889697</v>
       </c>
       <c r="C98">
-        <v>-3775.962419500588</v>
+        <v>-3827.649778630565</v>
       </c>
       <c r="D98">
-        <v>622.0838058041645</v>
+        <v>616.5979698544452</v>
       </c>
       <c r="E98">
-        <v>1358.093907278969</v>
+        <v>1404.295430459227</v>
       </c>
       <c r="F98">
-        <v>4435.346225304753</v>
+        <v>4481.547748485011</v>
       </c>
       <c r="G98">
         <v>37.3</v>
@@ -9323,37 +9323,37 @@
         <v>118.1</v>
       </c>
       <c r="M98">
-        <v>1045.854639926861</v>
+        <v>1056.748959092766</v>
       </c>
       <c r="N98">
-        <v>-927.7546399268607</v>
+        <v>-938.6489590927655</v>
       </c>
       <c r="O98">
-        <v>-239.3606971011301</v>
+        <v>-242.1714314459335</v>
       </c>
       <c r="P98">
-        <v>-688.3939428257306</v>
+        <v>-696.477527646832</v>
       </c>
       <c r="Q98">
-        <v>-243.2939428257306</v>
+        <v>-251.3775276468319</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.989587926564428</v>
+        <v>1.304183902085905</v>
       </c>
       <c r="T98">
-        <v>21.79648791141866</v>
+        <v>29.06198388189156</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02913387657976144</v>
+        <v>0.02883352733667112</v>
       </c>
       <c r="W98">
-        <v>0.2289302319024923</v>
+        <v>0.229001054254013</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1129220022471373</v>
+        <v>0.1117578578940741</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2612565396889697</v>
+        <v>0.2631565396889697</v>
       </c>
       <c r="C99">
-        <v>-3827.649778630565</v>
+        <v>-3879.241230010821</v>
       </c>
       <c r="D99">
-        <v>616.5979698544452</v>
+        <v>611.2080416544474</v>
       </c>
       <c r="E99">
-        <v>1404.295430459227</v>
+        <v>1450.496953639485</v>
       </c>
       <c r="F99">
-        <v>4481.547748485011</v>
+        <v>4527.749271665269</v>
       </c>
       <c r="G99">
         <v>37.3</v>
@@ -9405,37 +9405,37 @@
         <v>118.1</v>
       </c>
       <c r="M99">
-        <v>1056.748959092766</v>
+        <v>1067.64327825867</v>
       </c>
       <c r="N99">
-        <v>-938.6489590927655</v>
+        <v>-949.5432782586703</v>
       </c>
       <c r="O99">
-        <v>-242.1714314459335</v>
+        <v>-244.9821657907369</v>
       </c>
       <c r="P99">
-        <v>-696.477527646832</v>
+        <v>-704.5611124679333</v>
       </c>
       <c r="Q99">
-        <v>-251.3775276468319</v>
+        <v>-259.4611124679333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.304183902085905</v>
+        <v>1.933375853128856</v>
       </c>
       <c r="T99">
-        <v>29.06198388189156</v>
+        <v>43.59297582283732</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02883352733667112</v>
+        <v>0.0285393076699704</v>
       </c>
       <c r="W99">
-        <v>0.229001054254013</v>
+        <v>0.229070431251421</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1117578578940741</v>
+        <v>0.1106174715890326</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2631565396889697</v>
+        <v>0.2650565396889697</v>
       </c>
       <c r="C100">
-        <v>-3879.241230010821</v>
+        <v>-3930.73926694976</v>
       </c>
       <c r="D100">
-        <v>611.2080416544474</v>
+        <v>605.9115278957663</v>
       </c>
       <c r="E100">
-        <v>1450.496953639485</v>
+        <v>1496.698476819743</v>
       </c>
       <c r="F100">
-        <v>4527.749271665269</v>
+        <v>4573.950794845527</v>
       </c>
       <c r="G100">
         <v>37.3</v>
@@ -9487,37 +9487,37 @@
         <v>118.1</v>
       </c>
       <c r="M100">
-        <v>1067.64327825867</v>
+        <v>1078.537597424575</v>
       </c>
       <c r="N100">
-        <v>-949.5432782586703</v>
+        <v>-960.4375974245753</v>
       </c>
       <c r="O100">
-        <v>-244.9821657907369</v>
+        <v>-247.7929001355404</v>
       </c>
       <c r="P100">
-        <v>-704.5611124679333</v>
+        <v>-712.6446972890349</v>
       </c>
       <c r="Q100">
-        <v>-259.4611124679333</v>
+        <v>-267.5446972890348</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.933375853128856</v>
+        <v>3.820951706257712</v>
       </c>
       <c r="T100">
-        <v>43.59297582283732</v>
+        <v>87.18595164567465</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0285393076699704</v>
+        <v>0.02825103183492018</v>
       </c>
       <c r="W100">
-        <v>0.229070431251421</v>
+        <v>0.2291384066933258</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1106174715890326</v>
+        <v>0.1095001233911636</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2650565396889697</v>
-      </c>
-      <c r="C101">
-        <v>-3930.73926694976</v>
-      </c>
-      <c r="D101">
-        <v>605.9115278957663</v>
-      </c>
-      <c r="E101">
-        <v>1496.698476819743</v>
-      </c>
-      <c r="F101">
-        <v>4573.950794845527</v>
-      </c>
-      <c r="G101">
-        <v>37.3</v>
-      </c>
-      <c r="H101">
-        <v>1542.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>563.2</v>
-      </c>
-      <c r="K101">
-        <v>445.1</v>
-      </c>
-      <c r="L101">
-        <v>118.1</v>
-      </c>
-      <c r="M101">
-        <v>1078.537597424575</v>
-      </c>
-      <c r="N101">
-        <v>-960.4375974245753</v>
-      </c>
-      <c r="O101">
-        <v>-247.7929001355404</v>
-      </c>
-      <c r="P101">
-        <v>-712.6446972890349</v>
-      </c>
-      <c r="Q101">
-        <v>-267.5446972890348</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.820951706257712</v>
-      </c>
-      <c r="T101">
-        <v>87.18595164567465</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02825103183492018</v>
-      </c>
-      <c r="W101">
-        <v>0.2291384066933258</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1095001233911636</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
